--- a/source/downloads/skill-magic-synthesis.xlsx
+++ b/source/downloads/skill-magic-synthesis.xlsx
@@ -58,7 +58,7 @@
     <t>雅</t>
   </si>
   <si>
-    <t>備考</t>
+    <t>备注</t>
   </si>
   <si>
     <t>最终破击</t>
@@ -433,13 +433,13 @@
     <t>缩小</t>
   </si>
   <si>
-    <t>テ</t>
-  </si>
-  <si>
-    <t>ヴ</t>
-  </si>
-  <si>
-    <t>ア</t>
+    <t>泰</t>
+  </si>
+  <si>
+    <t>维</t>
+  </si>
+  <si>
+    <t>雅</t>
   </si>
   <si>
     <t>连击滑行</t>
@@ -4122,7 +4122,7 @@
       <c r="H109" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="202">
+  <mergeCells count="204">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
@@ -4158,7 +4158,9 @@
     <mergeCell ref="A106:A109"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B19:B20"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="B28:B29"/>

--- a/source/downloads/skill-magic-synthesis.xlsx
+++ b/source/downloads/skill-magic-synthesis.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="攻击" sheetId="1" r:id="Ra112a51f3cb84797"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魔法" sheetId="2" r:id="R66061b0234cd4b9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="其他" sheetId="3" r:id="R694ffc307b7b44ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合成能力" sheetId="5" r:id="R980b7083fdcd400c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="攻击" sheetId="1" r:id="Read1d70889664f53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="魔法" sheetId="2" r:id="R1f61b606143f4310"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="其他" sheetId="3" r:id="Rf47137515b944657"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合成能力" sheetId="5" r:id="R98603b26e39943a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -886,18 +886,21 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="40" customHeight="1">
+    <x:row r="2" ht="56" customHeight="1">
       <x:c r="A2" s="39" t="str">
         <x:v>最终破击
-ファイナルブレイク</x:v>
+ファイナルブレイク
+Blitz</x:v>
       </x:c>
       <x:c r="B2" s="39" t="str">
         <x:v>轮盘之刃
-スロットブレード</x:v>
+スロットブレード
+Slot Edge</x:v>
       </x:c>
       <x:c r="C2" s="39" t="str">
         <x:v>空中破击
-エリアルブレイク</x:v>
+エリアルブレイク
+Quick Blitz</x:v>
       </x:c>
       <x:c r="D2" s="7" t="s">
         <x:v>8</x:v>
@@ -913,12 +916,13 @@
       </x:c>
       <x:c r="H2" s="30"/>
     </x:row>
-    <x:row r="3" ht="40" customHeight="1">
+    <x:row r="3" ht="56" customHeight="1">
       <x:c r="A3" s="23"/>
       <x:c r="B3" s="23"/>
       <x:c r="C3" s="39" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
         <x:v>10</x:v>
@@ -928,15 +932,17 @@
       <x:c r="G3" s="29"/>
       <x:c r="H3" s="30"/>
     </x:row>
-    <x:row r="4" ht="40" customHeight="1">
+    <x:row r="4" ht="56" customHeight="1">
       <x:c r="A4" s="23"/>
       <x:c r="B4" s="39" t="str">
         <x:v>反射闪击
-リフレクブリッツ</x:v>
+リフレクブリッツ
+Barrier Surge</x:v>
       </x:c>
       <x:c r="C4" s="39" t="str">
         <x:v>祈愿之刃
-ウィッシュブレード</x:v>
+ウィッシュブレード
+Wishing Edge</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
         <x:v>11</x:v>
@@ -950,18 +956,21 @@
       <x:c r="G4" s="29"/>
       <x:c r="H4" s="30"/>
     </x:row>
-    <x:row r="5" ht="40" customHeight="1">
+    <x:row r="5" ht="56" customHeight="1">
       <x:c r="A5" s="39" t="str">
         <x:v>陨石爆发
-メテオバースト</x:v>
+メテオバースト
+Meteor Crash</x:v>
       </x:c>
       <x:c r="B5" s="39" t="str">
         <x:v>火焰强击
-ファイアストライク</x:v>
+ファイアストライク
+Fire Strike</x:v>
       </x:c>
       <x:c r="C5" s="39" t="str">
         <x:v>残暴冲击
-ブルータルブラスト</x:v>
+ブルータルブラスト
+Brutal Blast</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
         <x:v>13</x:v>
@@ -977,15 +986,17 @@
       </x:c>
       <x:c r="H5" s="30"/>
     </x:row>
-    <x:row r="6" ht="40" customHeight="1">
+    <x:row r="6" ht="56" customHeight="1">
       <x:c r="A6" s="23"/>
       <x:c r="B6" s="39" t="str">
         <x:v>最终破击
-ファイナルブレイク</x:v>
+ファイナルブレイク
+Blitz</x:v>
       </x:c>
       <x:c r="C6" s="39" t="str">
         <x:v>地震
-クエイク</x:v>
+クエイク
+Quake</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
         <x:v>14</x:v>
@@ -995,18 +1006,21 @@
       <x:c r="G6" s="29"/>
       <x:c r="H6" s="30"/>
     </x:row>
-    <x:row r="7" ht="40" customHeight="1">
+    <x:row r="7" ht="56" customHeight="1">
       <x:c r="A7" s="39" t="str">
         <x:v>魔法时刻
-マジックアワー</x:v>
+マジックアワー
+Magic Hour</x:v>
       </x:c>
       <x:c r="B7" s="39" t="str">
         <x:v>最终破击
-ファイナルブレイク</x:v>
+ファイナルブレイク
+Blitz</x:v>
       </x:c>
       <x:c r="C7" s="39" t="str">
         <x:v>大零重力
-ゼログラビガ</x:v>
+ゼログラビガ
+Zero Graviga</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
         <x:v>8</x:v>
@@ -1022,15 +1036,17 @@
       </x:c>
       <x:c r="H7" s="30"/>
     </x:row>
-    <x:row r="8" ht="40" customHeight="1">
+    <x:row r="8" ht="56" customHeight="1">
       <x:c r="A8" s="23"/>
       <x:c r="B8" s="39" t="str">
         <x:v>反射闪击
-リフレクブリッツ</x:v>
+リフレクブリッツ
+Barrier Surge</x:v>
       </x:c>
       <x:c r="C8" s="39" t="str">
         <x:v>大劲风
-エアロガ</x:v>
+エアロガ
+Aeroga</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
         <x:v>14</x:v>
@@ -1040,18 +1056,21 @@
       <x:c r="G8" s="29"/>
       <x:c r="H8" s="30"/>
     </x:row>
-    <x:row r="9" ht="40" customHeight="1">
+    <x:row r="9" ht="56" customHeight="1">
       <x:c r="A9" s="39" t="str">
         <x:v>火焰冲刺
-ファイアダッシュ</x:v>
+ファイアダッシュ
+Fire Dash</x:v>
       </x:c>
       <x:c r="B9" s="39" t="str">
         <x:v>滑行冲刺
-スライドダッシュ</x:v>
+スライドダッシュ
+Sliding Dash</x:v>
       </x:c>
       <x:c r="C9" s="39" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
         <x:v>15</x:v>
@@ -1067,12 +1086,13 @@
       </x:c>
       <x:c r="H9" s="30"/>
     </x:row>
-    <x:row r="10" ht="40" customHeight="1">
+    <x:row r="10" ht="56" customHeight="1">
       <x:c r="A10" s="23"/>
       <x:c r="B10" s="23"/>
       <x:c r="C10" s="39" t="str">
         <x:v>火焰
-ファイア</x:v>
+ファイア
+Fire</x:v>
       </x:c>
       <x:c r="D10" s="7" t="s">
         <x:v>13</x:v>
@@ -1082,11 +1102,12 @@
       <x:c r="G10" s="29"/>
       <x:c r="H10" s="30"/>
     </x:row>
-    <x:row r="11" ht="40" customHeight="1">
+    <x:row r="11" ht="56" customHeight="1">
       <x:c r="A11" s="23"/>
       <x:c r="B11" s="39" t="str">
         <x:v>混乱强击
-コンフュストライク</x:v>
+コンフュストライク
+Confusion Strike</x:v>
       </x:c>
       <x:c r="C11" s="23"/>
       <x:c r="D11" s="7" t="s">
@@ -1097,18 +1118,21 @@
       <x:c r="G11" s="29"/>
       <x:c r="H11" s="30"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="56" customHeight="1">
       <x:c r="A12" s="39" t="str">
         <x:v>黑暗迷雾
-ダークヘイズ</x:v>
+ダークヘイズ
+Dark Haze</x:v>
       </x:c>
       <x:c r="B12" s="39" t="str">
         <x:v>火焰冲刺
-ファイアダッシュ</x:v>
+ファイアダッシュ
+Fire Dash</x:v>
       </x:c>
       <x:c r="C12" s="39" t="str">
         <x:v>中零重力
-ゼログラビラ</x:v>
+ゼログラビラ
+Zero Gravira</x:v>
       </x:c>
       <x:c r="D12" s="7" t="s">
         <x:v>13</x:v>
@@ -1124,12 +1148,13 @@
       </x:c>
       <x:c r="H12" s="30"/>
     </x:row>
-    <x:row r="13" ht="40" customHeight="1">
+    <x:row r="13" ht="56" customHeight="1">
       <x:c r="A13" s="23"/>
       <x:c r="B13" s="22"/>
       <x:c r="C13" s="39" t="str">
         <x:v>致盲
-ブラックアウト</x:v>
+ブラックアウト
+Blackout</x:v>
       </x:c>
       <x:c r="D13" s="7" t="s">
         <x:v>16</x:v>
@@ -1139,15 +1164,17 @@
       <x:c r="G13" s="29"/>
       <x:c r="H13" s="30"/>
     </x:row>
-    <x:row r="14" ht="40" customHeight="1">
+    <x:row r="14" ht="56" customHeight="1">
       <x:c r="A14" s="23"/>
       <x:c r="B14" s="39" t="str">
         <x:v>火焰闪击
-ファイアブリッツ</x:v>
+ファイアブリッツ
+Fire Surge</x:v>
       </x:c>
       <x:c r="C14" s="39" t="str">
         <x:v>零重力
-ゼログラビデ</x:v>
+ゼログラビデ
+Zero Gravity</x:v>
       </x:c>
       <x:c r="D14" s="7" t="s">
         <x:v>15</x:v>
@@ -1157,18 +1184,21 @@
       <x:c r="G14" s="29"/>
       <x:c r="H14" s="30"/>
     </x:row>
-    <x:row r="15" ht="40" customHeight="1">
+    <x:row r="15" ht="56" customHeight="1">
       <x:c r="A15" s="39" t="str">
         <x:v>音速猛攻
-ソニックレイヴ</x:v>
+ソニックレイヴ
+Sonic Blade</x:v>
       </x:c>
       <x:c r="B15" s="39" t="str">
         <x:v>火焰冲刺
-ファイアダッシュ</x:v>
+ファイアダッシュ
+Fire Dash</x:v>
       </x:c>
       <x:c r="C15" s="39" t="str">
         <x:v>雷电闪击
-サンダーブリッツ</x:v>
+サンダーブリッツ
+Thunder Surge</x:v>
       </x:c>
       <x:c r="D15" s="7" t="s">
         <x:v>10</x:v>
@@ -1184,15 +1214,17 @@
       </x:c>
       <x:c r="H15" s="30"/>
     </x:row>
-    <x:row r="16" ht="40" customHeight="1">
+    <x:row r="16" ht="56" customHeight="1">
       <x:c r="A16" s="23"/>
       <x:c r="B16" s="39" t="str">
         <x:v>最终破击
-ファイナルブレイク</x:v>
+ファイナルブレイク
+Blitz</x:v>
       </x:c>
       <x:c r="C16" s="39" t="str">
         <x:v>空中滑行
-エアスライド</x:v>
+エアスライド
+Air Slide</x:v>
       </x:c>
       <x:c r="D16" s="7" t="s">
         <x:v>14</x:v>
@@ -1202,12 +1234,13 @@
       <x:c r="G16" s="29"/>
       <x:c r="H16" s="30"/>
     </x:row>
-    <x:row r="17" ht="40" customHeight="1">
+    <x:row r="17" ht="56" customHeight="1">
       <x:c r="A17" s="23"/>
       <x:c r="B17" s="23"/>
       <x:c r="C17" s="39" t="str">
         <x:v>黑暗迷雾
-ダークヘイズ</x:v>
+ダークヘイズ
+Dark Haze</x:v>
       </x:c>
       <x:c r="D17" s="7" t="s">
         <x:v>13</x:v>
@@ -1221,18 +1254,21 @@
       </x:c>
       <x:c r="H17" s="30"/>
     </x:row>
-    <x:row r="18" ht="40" customHeight="1">
+    <x:row r="18" ht="56" customHeight="1">
       <x:c r="A18" s="39" t="str">
         <x:v>混沌猛攻
-カオスレイヴ</x:v>
+カオスレイヴ
+Chaos Blade</x:v>
       </x:c>
       <x:c r="B18" s="39" t="str">
         <x:v>音速猛攻
-ソニックレイヴ</x:v>
+ソニックレイヴ
+Sonic Blade</x:v>
       </x:c>
       <x:c r="C18" s="39" t="str">
         <x:v>黑暗迷雾
-ダークヘイズ</x:v>
+ダークヘイズ
+Dark Haze</x:v>
       </x:c>
       <x:c r="D18" s="7" t="s">
         <x:v>17</x:v>
@@ -1248,18 +1284,21 @@
       </x:c>
       <x:c r="H18" s="7"/>
     </x:row>
-    <x:row r="19" ht="40" customHeight="1">
+    <x:row r="19" ht="56" customHeight="1">
       <x:c r="A19" s="39" t="str">
         <x:v>斩铁剑
-ザンテツケン</x:v>
+ザンテツケン
+Zantetsuken</x:v>
       </x:c>
       <x:c r="B19" s="39" t="str">
         <x:v>大停止
-ストプガ</x:v>
+ストプガ
+Stopga</x:v>
       </x:c>
       <x:c r="C19" s="39" t="str">
         <x:v>黑暗迷雾
-ダークヘイズ</x:v>
+ダークヘイズ
+Dark Haze</x:v>
       </x:c>
       <x:c r="D19" s="7" t="s">
         <x:v>17</x:v>
@@ -1275,12 +1314,13 @@
       </x:c>
       <x:c r="H19" s="30"/>
     </x:row>
-    <x:row r="20" ht="40" customHeight="1">
+    <x:row r="20" ht="56" customHeight="1">
       <x:c r="A20" s="23"/>
       <x:c r="B20" s="22"/>
       <x:c r="C20" s="39" t="str">
         <x:v>音速猛攻
-ソニックレイヴ</x:v>
+ソニックレイヴ
+Sonic Blade</x:v>
       </x:c>
       <x:c r="D20" s="7" t="s">
         <x:v>18</x:v>
@@ -1290,18 +1330,21 @@
       <x:c r="G20" s="29"/>
       <x:c r="H20" s="30"/>
     </x:row>
-    <x:row r="21" ht="40" customHeight="1">
+    <x:row r="21" ht="56" customHeight="1">
       <x:c r="A21" s="39" t="str">
         <x:v>强击飞掷
-ストライクレイド</x:v>
+ストライクレイド
+Strike Raid</x:v>
       </x:c>
       <x:c r="B21" s="39" t="str">
         <x:v>空中破击
-エリアルブレイク</x:v>
+エリアルブレイク
+Quick Blitz</x:v>
       </x:c>
       <x:c r="C21" s="39" t="str">
         <x:v>滑行冲刺
-スライドダッシュ</x:v>
+スライドダッシュ
+Sliding Dash</x:v>
       </x:c>
       <x:c r="D21" s="7" t="s">
         <x:v>8</x:v>
@@ -1317,18 +1360,21 @@
       </x:c>
       <x:c r="H21" s="7"/>
     </x:row>
-    <x:row r="22" ht="40" customHeight="1">
+    <x:row r="22" ht="56" customHeight="1">
       <x:c r="A22" s="39" t="str">
         <x:v>冰冻飞掷
-フリーズレイド</x:v>
+フリーズレイド
+Freeze Raid</x:v>
       </x:c>
       <x:c r="B22" s="39" t="str">
         <x:v>强击飞掷
-ストライクレイド</x:v>
+ストライクレイド
+Strike Raid</x:v>
       </x:c>
       <x:c r="C22" s="39" t="str">
         <x:v>中冰雪
-ブリザラ</x:v>
+ブリザラ
+Blizzara</x:v>
       </x:c>
       <x:c r="D22" s="7" t="s">
         <x:v>19</x:v>
@@ -1344,15 +1390,17 @@
       </x:c>
       <x:c r="H22" s="30"/>
     </x:row>
-    <x:row r="23" ht="40" customHeight="1">
+    <x:row r="23" ht="56" customHeight="1">
       <x:c r="A23" s="23"/>
       <x:c r="B23" s="39" t="str">
         <x:v>冰雪之刃
-ブリザドブレード</x:v>
+ブリザドブレード
+Blizzard Edge</x:v>
       </x:c>
       <x:c r="C23" s="39" t="str">
         <x:v>束缚强击
-バインドストライク</x:v>
+バインドストライク
+Binding Strike</x:v>
       </x:c>
       <x:c r="D23" s="7" t="s">
         <x:v>10</x:v>
@@ -1362,18 +1410,21 @@
       <x:c r="G23" s="29"/>
       <x:c r="H23" s="30"/>
     </x:row>
-    <x:row r="24" ht="40" customHeight="1">
+    <x:row r="24" ht="56" customHeight="1">
       <x:c r="A24" s="39" t="str">
         <x:v>宝藏飞掷
-トレジャーレイド</x:v>
+トレジャーレイド
+Treasure Raid</x:v>
       </x:c>
       <x:c r="B24" s="39" t="str">
         <x:v>轮盘之刃
-スロットブレード</x:v>
+スロットブレード
+Slot Edge</x:v>
       </x:c>
       <x:c r="C24" s="39" t="str">
         <x:v>中磁力
-マグネラ</x:v>
+マグネラ
+Magnera</x:v>
       </x:c>
       <x:c r="D24" s="7" t="s">
         <x:v>10</x:v>
@@ -1389,12 +1440,13 @@
       </x:c>
       <x:c r="H24" s="30"/>
     </x:row>
-    <x:row r="25" ht="40" customHeight="1">
+    <x:row r="25" ht="56" customHeight="1">
       <x:c r="A25" s="23"/>
       <x:c r="B25" s="23"/>
       <x:c r="C25" s="39" t="str">
         <x:v>强击飞掷
-ストライクレイド</x:v>
+ストライクレイド
+Strike Raid</x:v>
       </x:c>
       <x:c r="D25" s="7" t="s">
         <x:v>8</x:v>
@@ -1404,18 +1456,21 @@
       <x:c r="G25" s="29"/>
       <x:c r="H25" s="30"/>
     </x:row>
-    <x:row r="26" ht="40" customHeight="1">
+    <x:row r="26" ht="56" customHeight="1">
       <x:c r="A26" s="39" t="str">
         <x:v>星火飞掷
-スパークレイド</x:v>
+スパークレイド
+Spark Raid</x:v>
       </x:c>
       <x:c r="B26" s="39" t="str">
         <x:v>大磁力
-マグネガ</x:v>
+マグネガ
+Magnega</x:v>
       </x:c>
       <x:c r="C26" s="39" t="str">
         <x:v>冰冻飞掷
-フリーズレイド</x:v>
+フリーズレイド
+Freeze Raid</x:v>
       </x:c>
       <x:c r="D26" s="7" t="s">
         <x:v>20</x:v>
@@ -1431,12 +1486,13 @@
       </x:c>
       <x:c r="H26" s="30"/>
     </x:row>
-    <x:row r="27" ht="40" customHeight="1">
+    <x:row r="27" ht="56" customHeight="1">
       <x:c r="A27" s="23"/>
       <x:c r="B27" s="23"/>
       <x:c r="C27" s="39" t="str">
         <x:v>宝藏飞掷
-トレジャーレイド</x:v>
+トレジャーレイド
+Treasure Raid</x:v>
       </x:c>
       <x:c r="D27" s="7" t="s">
         <x:v>14</x:v>
@@ -1446,15 +1502,17 @@
       <x:c r="G27" s="29"/>
       <x:c r="H27" s="30"/>
     </x:row>
-    <x:row r="28" ht="40" customHeight="1">
+    <x:row r="28" ht="56" customHeight="1">
       <x:c r="A28" s="23"/>
       <x:c r="B28" s="39" t="str">
         <x:v>闪避翻滚
-ドッジロール</x:v>
+ドッジロール
+Dodge Roll</x:v>
       </x:c>
       <x:c r="C28" s="39" t="str">
         <x:v>雷电闪击
-サンダーブリッツ</x:v>
+サンダーブリッツ
+Thunder Surge</x:v>
       </x:c>
       <x:c r="D28" s="7" t="s">
         <x:v>11</x:v>
@@ -1466,12 +1524,13 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="40" customHeight="1">
+    <x:row r="29" ht="56" customHeight="1">
       <x:c r="A29" s="23"/>
       <x:c r="B29" s="23"/>
       <x:c r="C29" s="39" t="str">
         <x:v>大雷电
-サンダガ</x:v>
+サンダガ
+Thundaga</x:v>
       </x:c>
       <x:c r="D29" s="7" t="s">
         <x:v>22</x:v>
@@ -1481,18 +1540,21 @@
       <x:c r="G29" s="29"/>
       <x:c r="H29" s="30"/>
     </x:row>
-    <x:row r="30" ht="40" customHeight="1">
+    <x:row r="30" ht="56" customHeight="1">
       <x:c r="A30" s="39" t="str">
         <x:v>疾风飞掷
-ウインドレイド</x:v>
+ウインドレイド
+Wind Raid</x:v>
       </x:c>
       <x:c r="B30" s="39" t="str">
         <x:v>大劲风
-エアロガ</x:v>
+エアロガ
+Aeroga</x:v>
       </x:c>
       <x:c r="C30" s="39" t="str">
         <x:v>冰冻飞掷
-フリーズレイド</x:v>
+フリーズレイド
+Freeze Raid</x:v>
       </x:c>
       <x:c r="D30" s="7" t="s">
         <x:v>17</x:v>
@@ -1508,12 +1570,13 @@
       </x:c>
       <x:c r="H30" s="30"/>
     </x:row>
-    <x:row r="31" ht="40" customHeight="1">
+    <x:row r="31" ht="56" customHeight="1">
       <x:c r="A31" s="23"/>
       <x:c r="B31" s="23"/>
       <x:c r="C31" s="39" t="str">
         <x:v>宝藏飞掷
-トレジャーレイド</x:v>
+トレジャーレイド
+Treasure Raid</x:v>
       </x:c>
       <x:c r="D31" s="7" t="s">
         <x:v>18</x:v>
@@ -1523,18 +1586,21 @@
       <x:c r="G31" s="29"/>
       <x:c r="H31" s="30"/>
     </x:row>
-    <x:row r="32" ht="40" customHeight="1">
+    <x:row r="32" ht="56" customHeight="1">
       <x:c r="A32" s="39" t="str">
         <x:v>火焰闪击
-ファイアブリッツ</x:v>
+ファイアブリッツ
+Fire Surge</x:v>
       </x:c>
       <x:c r="B32" s="39" t="str">
         <x:v>火焰冲刺
-ファイアダッシュ</x:v>
+ファイアダッシュ
+Fire Dash</x:v>
       </x:c>
       <x:c r="C32" s="39" t="str">
         <x:v>点燃
-スナイプバーニング</x:v>
+スナイプバーニング
+Ignite</x:v>
       </x:c>
       <x:c r="D32" s="7" t="s">
         <x:v>13</x:v>
@@ -1550,15 +1616,17 @@
       </x:c>
       <x:c r="H32" s="30"/>
     </x:row>
-    <x:row r="33" ht="40" customHeight="1">
+    <x:row r="33" ht="56" customHeight="1">
       <x:c r="A33" s="23"/>
       <x:c r="B33" s="40" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="C33" s="39" t="str">
         <x:v>火焰强击
-ファイアストライク</x:v>
+ファイアストライク
+Fire Strike</x:v>
       </x:c>
       <x:c r="D33" s="7" t="s">
         <x:v>16</x:v>
@@ -1568,12 +1636,13 @@
       <x:c r="G33" s="29"/>
       <x:c r="H33" s="30"/>
     </x:row>
-    <x:row r="34" ht="40" customHeight="1">
+    <x:row r="34" ht="56" customHeight="1">
       <x:c r="A34" s="23"/>
       <x:c r="B34" s="16"/>
       <x:c r="C34" s="39" t="str">
         <x:v>混乱强击
-コンフュストライク</x:v>
+コンフュストライク
+Confusion Strike</x:v>
       </x:c>
       <x:c r="D34" s="7" t="s">
         <x:v>8</x:v>
@@ -1583,12 +1652,13 @@
       <x:c r="G34" s="29"/>
       <x:c r="H34" s="30"/>
     </x:row>
-    <x:row r="35" ht="40" customHeight="1">
+    <x:row r="35" ht="56" customHeight="1">
       <x:c r="A35" s="23"/>
       <x:c r="B35" s="14"/>
       <x:c r="C35" s="39" t="str">
         <x:v>束缚强击
-バインドストライク</x:v>
+バインドストライク
+Binding Strike</x:v>
       </x:c>
       <x:c r="D35" s="7" t="s">
         <x:v>10</x:v>
@@ -1598,18 +1668,21 @@
       <x:c r="G35" s="29"/>
       <x:c r="H35" s="30"/>
     </x:row>
-    <x:row r="36" ht="40" customHeight="1">
+    <x:row r="36" ht="56" customHeight="1">
       <x:c r="A36" s="39" t="str">
         <x:v>反射闪击
-リフレクブリッツ</x:v>
+リフレクブリッツ
+Barrier Surge</x:v>
       </x:c>
       <x:c r="B36" s="40" t="str">
         <x:v>反射
-リフレク</x:v>
+リフレク
+Barrier</x:v>
       </x:c>
       <x:c r="C36" s="39" t="str">
         <x:v>火焰冲刺
-ファイアダッシュ</x:v>
+ファイアダッシュ
+Fire Dash</x:v>
       </x:c>
       <x:c r="D36" s="7" t="s">
         <x:v>13</x:v>
@@ -1625,12 +1698,13 @@
       </x:c>
       <x:c r="H36" s="30"/>
     </x:row>
-    <x:row r="37" ht="40" customHeight="1">
+    <x:row r="37" ht="56" customHeight="1">
       <x:c r="A37" s="23"/>
       <x:c r="B37" s="14"/>
       <x:c r="C37" s="39" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="D37" s="7" t="s">
         <x:v>10</x:v>
@@ -1640,18 +1714,21 @@
       <x:c r="G37" s="29"/>
       <x:c r="H37" s="30"/>
     </x:row>
-    <x:row r="38" ht="40" customHeight="1">
+    <x:row r="38" ht="56" customHeight="1">
       <x:c r="A38" s="39" t="str">
         <x:v>雷电闪击
-サンダーブリッツ</x:v>
+サンダーブリッツ
+Thunder Surge</x:v>
       </x:c>
       <x:c r="B38" s="40" t="str">
         <x:v>中雷电
-サンダラ</x:v>
+サンダラ
+Thundara</x:v>
       </x:c>
       <x:c r="C38" s="39" t="str">
         <x:v>混乱强击
-コンフュストライク</x:v>
+コンフュストライク
+Confusion Strike</x:v>
       </x:c>
       <x:c r="D38" s="7" t="s">
         <x:v>19</x:v>
@@ -1667,12 +1744,13 @@
       </x:c>
       <x:c r="H38" s="30"/>
     </x:row>
-    <x:row r="39" ht="40" customHeight="1">
+    <x:row r="39" ht="56" customHeight="1">
       <x:c r="A39" s="23"/>
       <x:c r="B39" s="16"/>
       <x:c r="C39" s="39" t="str">
         <x:v>火焰冲刺
-ファイアダッシュ</x:v>
+ファイアダッシュ
+Fire Dash</x:v>
       </x:c>
       <x:c r="D39" s="7" t="s">
         <x:v>13</x:v>
@@ -1682,12 +1760,13 @@
       <x:c r="G39" s="29"/>
       <x:c r="H39" s="30"/>
     </x:row>
-    <x:row r="40" ht="40" customHeight="1">
+    <x:row r="40" ht="56" customHeight="1">
       <x:c r="A40" s="23"/>
       <x:c r="B40" s="16"/>
       <x:c r="C40" s="39" t="str">
         <x:v>冰冻飞掷
-フリーズレイド</x:v>
+フリーズレイド
+Freeze Raid</x:v>
       </x:c>
       <x:c r="D40" s="7" t="s">
         <x:v>23</x:v>
@@ -1697,12 +1776,13 @@
       <x:c r="G40" s="29"/>
       <x:c r="H40" s="30"/>
     </x:row>
-    <x:row r="41" ht="40" customHeight="1">
+    <x:row r="41" ht="56" customHeight="1">
       <x:c r="A41" s="23"/>
       <x:c r="B41" s="14"/>
       <x:c r="C41" s="39" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="D41" s="7" t="s">
         <x:v>19</x:v>
@@ -1712,18 +1792,21 @@
       <x:c r="G41" s="29"/>
       <x:c r="H41" s="30"/>
     </x:row>
-    <x:row r="42" ht="40" customHeight="1">
+    <x:row r="42" ht="56" customHeight="1">
       <x:c r="A42" s="39" t="str">
         <x:v>空中猛击
-エリアルスラム</x:v>
+エリアルスラム
+Aerial Slam</x:v>
       </x:c>
       <x:c r="B42" s="39" t="str">
         <x:v>火焰强击
-ファイアストライク</x:v>
+ファイアストライク
+Fire Strike</x:v>
       </x:c>
       <x:c r="C42" s="39" t="str">
         <x:v>中劲风
-エアロラ</x:v>
+エアロラ
+Aerora</x:v>
       </x:c>
       <x:c r="D42" s="7" t="s">
         <x:v>15</x:v>
@@ -1739,15 +1822,17 @@
       </x:c>
       <x:c r="H42" s="30"/>
     </x:row>
-    <x:row r="43" ht="40" customHeight="1">
+    <x:row r="43" ht="56" customHeight="1">
       <x:c r="A43" s="23"/>
       <x:c r="B43" s="39" t="str">
         <x:v>火焰闪击
-ファイアブリッツ</x:v>
+ファイアブリッツ
+Fire Surge</x:v>
       </x:c>
       <x:c r="C43" s="39" t="str">
         <x:v>劲风
-エアロ</x:v>
+エアロ
+Aero</x:v>
       </x:c>
       <x:c r="D43" s="7" t="s">
         <x:v>13</x:v>
@@ -1757,15 +1842,17 @@
       <x:c r="G43" s="29"/>
       <x:c r="H43" s="30"/>
     </x:row>
-    <x:row r="44" ht="40" customHeight="1">
+    <x:row r="44" ht="56" customHeight="1">
       <x:c r="A44" s="23"/>
       <x:c r="B44" s="39" t="str">
         <x:v>火焰冲刺
-ファイアダッシュ</x:v>
+ファイアダッシュ
+Fire Dash</x:v>
       </x:c>
       <x:c r="C44" s="39" t="str">
         <x:v>高跳
-ハイジャンプ</x:v>
+ハイジャンプ
+High Jump</x:v>
       </x:c>
       <x:c r="D44" s="7" t="s">
         <x:v>16</x:v>
@@ -1775,18 +1862,21 @@
       <x:c r="G44" s="29"/>
       <x:c r="H44" s="30"/>
     </x:row>
-    <x:row r="45" ht="40" customHeight="1">
+    <x:row r="45" ht="56" customHeight="1">
       <x:c r="A45" s="39" t="str">
         <x:v>孤高奥义
-ソロアルカナム</x:v>
+ソロアルカナム
+Ars Solum</x:v>
       </x:c>
       <x:c r="B45" s="40" t="str">
         <x:v>黑暗迷雾
-ダークヘイズ</x:v>
+ダークヘイズ
+Dark Haze</x:v>
       </x:c>
       <x:c r="C45" s="39" t="str">
         <x:v>音速猛攻
-ソニックレイヴ</x:v>
+ソニックレイヴ
+Sonic Blade</x:v>
       </x:c>
       <x:c r="D45" s="7" t="s">
         <x:v>17</x:v>
@@ -1804,12 +1894,13 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="40" customHeight="1">
+    <x:row r="46" ht="56" customHeight="1">
       <x:c r="A46" s="23"/>
       <x:c r="B46" s="14"/>
       <x:c r="C46" s="40" t="str">
         <x:v>大停止
-ストプガ</x:v>
+ストプガ
+Stopga</x:v>
       </x:c>
       <x:c r="D46" s="7" t="s">
         <x:v>17</x:v>
@@ -1819,11 +1910,12 @@
       <x:c r="G46" s="29"/>
       <x:c r="H46" s="30"/>
     </x:row>
-    <x:row r="47" ht="40" customHeight="1">
+    <x:row r="47" ht="56" customHeight="1">
       <x:c r="A47" s="23"/>
       <x:c r="B47" s="39" t="str">
         <x:v>音速猛攻
-ソニックレイヴ</x:v>
+ソニックレイヴ
+Sonic Blade</x:v>
       </x:c>
       <x:c r="C47" s="14"/>
       <x:c r="D47" s="7" t="s">
@@ -1834,15 +1926,17 @@
       <x:c r="G47" s="29"/>
       <x:c r="H47" s="30"/>
     </x:row>
-    <x:row r="48" ht="40" customHeight="1">
+    <x:row r="48" ht="56" customHeight="1">
       <x:c r="A48" s="23"/>
       <x:c r="B48" s="39" t="str">
         <x:v>中雷电
-サンダラ</x:v>
+サンダラ
+Thundara</x:v>
       </x:c>
       <x:c r="C48" s="39" t="str">
         <x:v>强击飞掷
-ストライクレイド</x:v>
+ストライクレイド
+Strike Raid</x:v>
       </x:c>
       <x:c r="D48" s="7" t="s">
         <x:v>18</x:v>
@@ -1852,12 +1946,13 @@
       <x:c r="G48" s="29"/>
       <x:c r="H48" s="30"/>
     </x:row>
-    <x:row r="49" ht="40" customHeight="1">
+    <x:row r="49" ht="56" customHeight="1">
       <x:c r="A49" s="23"/>
       <x:c r="B49" s="23"/>
       <x:c r="C49" s="39" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="D49" s="7" t="s">
         <x:v>10</x:v>
@@ -1867,15 +1962,17 @@
       <x:c r="G49" s="29"/>
       <x:c r="H49" s="30"/>
     </x:row>
-    <x:row r="50" ht="40" customHeight="1">
+    <x:row r="50" ht="56" customHeight="1">
       <x:c r="A50" s="23"/>
       <x:c r="B50" s="39" t="str">
         <x:v>滑行冲刺
-スライドダッシュ</x:v>
+スライドダッシュ
+Sliding Dash</x:v>
       </x:c>
       <x:c r="C50" s="39" t="str">
         <x:v>雷电
-サンダー</x:v>
+サンダー
+Thunder</x:v>
       </x:c>
       <x:c r="D50" s="7" t="s">
         <x:v>10</x:v>
@@ -1885,18 +1982,21 @@
       <x:c r="G50" s="29"/>
       <x:c r="H50" s="30"/>
     </x:row>
-    <x:row r="51" ht="40" customHeight="1">
+    <x:row r="51" ht="56" customHeight="1">
       <x:c r="A51" s="39" t="str">
         <x:v>最终奥义
-ラストアルカナム</x:v>
+ラストアルカナム
+Ars Arcanum</x:v>
       </x:c>
       <x:c r="B51" s="39" t="str">
         <x:v>最终破击
-ファイナルブレイク</x:v>
+ファイナルブレイク
+Blitz</x:v>
       </x:c>
       <x:c r="C51" s="39" t="str">
         <x:v>空中猛击
-エリアルスラム</x:v>
+エリアルスラム
+Aerial Slam</x:v>
       </x:c>
       <x:c r="D51" s="7" t="s">
         <x:v>18</x:v>
@@ -1912,15 +2012,17 @@
       </x:c>
       <x:c r="H51" s="7"/>
     </x:row>
-    <x:row r="52" ht="40" customHeight="1">
+    <x:row r="52" ht="56" customHeight="1">
       <x:c r="A52" s="23"/>
       <x:c r="B52" s="39" t="str">
         <x:v>空中破击
-エリアルブレイク</x:v>
+エリアルブレイク
+Quick Blitz</x:v>
       </x:c>
       <x:c r="C52" s="39" t="str">
         <x:v>轮盘之刃
-スロットブレード</x:v>
+スロットブレード
+Slot Edge</x:v>
       </x:c>
       <x:c r="D52" s="7" t="s">
         <x:v>8</x:v>
@@ -1932,12 +2034,13 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="40" customHeight="1">
+    <x:row r="53" ht="56" customHeight="1">
       <x:c r="A53" s="23"/>
       <x:c r="B53" s="23"/>
       <x:c r="C53" s="39" t="str">
         <x:v>冰雪
-ブリザド</x:v>
+ブリザド
+Blizzard</x:v>
       </x:c>
       <x:c r="D53" s="7" t="s">
         <x:v>23</x:v>
@@ -1947,11 +2050,12 @@
       <x:c r="G53" s="29"/>
       <x:c r="H53" s="30"/>
     </x:row>
-    <x:row r="54" ht="40" customHeight="1">
+    <x:row r="54" ht="56" customHeight="1">
       <x:c r="A54" s="23"/>
       <x:c r="B54" s="39" t="str">
         <x:v>滑行冲刺
-スライドダッシュ</x:v>
+スライドダッシュ
+Sliding Dash</x:v>
       </x:c>
       <x:c r="C54" s="23"/>
       <x:c r="D54" s="7" t="s">
@@ -1962,15 +2066,17 @@
       <x:c r="G54" s="29"/>
       <x:c r="H54" s="30"/>
     </x:row>
-    <x:row r="55" ht="40" customHeight="1">
+    <x:row r="55" ht="56" customHeight="1">
       <x:c r="A55" s="23"/>
       <x:c r="B55" s="39" t="str">
         <x:v>火焰强击
-ファイアストライク</x:v>
+ファイアストライク
+Fire Strike</x:v>
       </x:c>
       <x:c r="C55" s="39" t="str">
         <x:v>中劲风
-エアロラ</x:v>
+エアロラ
+Aerora</x:v>
       </x:c>
       <x:c r="D55" s="7" t="s">
         <x:v>15</x:v>
@@ -1980,15 +2086,17 @@
       <x:c r="G55" s="29"/>
       <x:c r="H55" s="30"/>
     </x:row>
-    <x:row r="56" ht="40" customHeight="1">
+    <x:row r="56" ht="56" customHeight="1">
       <x:c r="A56" s="23"/>
       <x:c r="B56" s="39" t="str">
         <x:v>冰雪之刃
-ブリザドブレード</x:v>
+ブリザドブレード
+Blizzard Edge</x:v>
       </x:c>
       <x:c r="C56" s="39" t="str">
         <x:v>中恢复
-ケアルラ</x:v>
+ケアルラ
+Cura</x:v>
       </x:c>
       <x:c r="D56" s="7" t="s">
         <x:v>23</x:v>
@@ -1998,18 +2106,21 @@
       <x:c r="G56" s="29"/>
       <x:c r="H56" s="30"/>
     </x:row>
-    <x:row r="57" ht="40" customHeight="1">
+    <x:row r="57" ht="56" customHeight="1">
       <x:c r="A57" s="39" t="str">
         <x:v>时间剪接
-タイムスプライサー</x:v>
+タイムスプライサー
+Time Splicer</x:v>
       </x:c>
       <x:c r="B57" s="39" t="str">
         <x:v>大停止
-ストプガ</x:v>
+ストプガ
+Stopga</x:v>
       </x:c>
       <x:c r="C57" s="39" t="str">
         <x:v>空中猛击
-エリアルスラム</x:v>
+エリアルスラム
+Aerial Slam</x:v>
       </x:c>
       <x:c r="D57" s="7" t="s">
         <x:v>18</x:v>
@@ -2025,12 +2136,13 @@
       </x:c>
       <x:c r="H57" s="7"/>
     </x:row>
-    <x:row r="58" ht="40" customHeight="1">
+    <x:row r="58" ht="56" customHeight="1">
       <x:c r="A58" s="23"/>
       <x:c r="B58" s="23"/>
       <x:c r="C58" s="39" t="str">
         <x:v>反射
-リフレク</x:v>
+リフレク
+Barrier</x:v>
       </x:c>
       <x:c r="D58" s="7" t="s">
         <x:v>15</x:v>
@@ -2044,15 +2156,17 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="40" customHeight="1">
+    <x:row r="59" ht="56" customHeight="1">
       <x:c r="A59" s="23"/>
       <x:c r="B59" s="39" t="str">
         <x:v>反射闪击
-リフレクブリッツ</x:v>
+リフレクブリッツ
+Barrier Surge</x:v>
       </x:c>
       <x:c r="C59" s="39" t="str">
         <x:v>祈愿之刃
-ウィッシュブレード</x:v>
+ウィッシュブレード
+Wishing Edge</x:v>
       </x:c>
       <x:c r="D59" s="7" t="s">
         <x:v>11</x:v>
@@ -2062,15 +2176,17 @@
       <x:c r="G59" s="29"/>
       <x:c r="H59" s="30"/>
     </x:row>
-    <x:row r="60" ht="40" customHeight="1">
+    <x:row r="60" ht="56" customHeight="1">
       <x:c r="A60" s="23"/>
       <x:c r="B60" s="39" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="C60" s="39" t="str">
         <x:v>轮盘之刃
-スロットブレード</x:v>
+スロットブレード
+Slot Edge</x:v>
       </x:c>
       <x:c r="D60" s="7" t="s">
         <x:v>10</x:v>
@@ -2082,18 +2198,21 @@
       <x:c r="G60" s="29"/>
       <x:c r="H60" s="30"/>
     </x:row>
-    <x:row r="61" ht="40" customHeight="1">
+    <x:row r="61" ht="56" customHeight="1">
       <x:c r="A61" s="39" t="str">
         <x:v>剧毒之刃
-ポイズンブレード</x:v>
+ポイズンブレード
+Poison Edge</x:v>
       </x:c>
       <x:c r="B61" s="39" t="str">
         <x:v>剧毒
-ポイズン</x:v>
+ポイズン
+Poison</x:v>
       </x:c>
       <x:c r="C61" s="39" t="str">
         <x:v>空中破击
-エリアルブレイク</x:v>
+エリアルブレイク
+Quick Blitz</x:v>
       </x:c>
       <x:c r="D61" s="7" t="s">
         <x:v>8</x:v>
@@ -2109,12 +2228,13 @@
       </x:c>
       <x:c r="H61" s="30"/>
     </x:row>
-    <x:row r="62" ht="40" customHeight="1">
+    <x:row r="62" ht="56" customHeight="1">
       <x:c r="A62" s="23"/>
       <x:c r="B62" s="23"/>
       <x:c r="C62" s="39" t="str">
         <x:v>滑行冲刺
-スライドダッシュ</x:v>
+スライドダッシュ
+Sliding Dash</x:v>
       </x:c>
       <x:c r="D62" s="7" t="s">
         <x:v>10</x:v>
@@ -2124,12 +2244,13 @@
       <x:c r="G62" s="29"/>
       <x:c r="H62" s="30"/>
     </x:row>
-    <x:row r="63" ht="40" customHeight="1">
+    <x:row r="63" ht="56" customHeight="1">
       <x:c r="A63" s="23"/>
       <x:c r="B63" s="23"/>
       <x:c r="C63" s="39" t="str">
         <x:v>强击飞掷
-ストライクレイド</x:v>
+ストライクレイド
+Strike Raid</x:v>
       </x:c>
       <x:c r="D63" s="7" t="s">
         <x:v>13</x:v>
@@ -2139,18 +2260,21 @@
       <x:c r="G63" s="29"/>
       <x:c r="H63" s="30"/>
     </x:row>
-    <x:row r="64" ht="40" customHeight="1">
+    <x:row r="64" ht="56" customHeight="1">
       <x:c r="A64" s="39" t="str">
         <x:v>祈愿之刃
-ウィッシュブレード</x:v>
+ウィッシュブレード
+Wishing Edge</x:v>
       </x:c>
       <x:c r="B64" s="39" t="str">
         <x:v>反射闪击
-リフレクブリッツ</x:v>
+リフレクブリッツ
+Barrier Surge</x:v>
       </x:c>
       <x:c r="C64" s="39" t="str">
         <x:v>强击飞掷
-ストライクレイド</x:v>
+ストライクレイド
+Strike Raid</x:v>
       </x:c>
       <x:c r="D64" s="7" t="s">
         <x:v>8</x:v>
@@ -2166,12 +2290,13 @@
       </x:c>
       <x:c r="H64" s="30"/>
     </x:row>
-    <x:row r="65" ht="40" customHeight="1">
+    <x:row r="65" ht="56" customHeight="1">
       <x:c r="A65" s="23"/>
       <x:c r="B65" s="23"/>
       <x:c r="C65" s="39" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="D65" s="7" t="s">
         <x:v>10</x:v>
@@ -2181,11 +2306,12 @@
       <x:c r="G65" s="29"/>
       <x:c r="H65" s="30"/>
     </x:row>
-    <x:row r="66" ht="40" customHeight="1">
+    <x:row r="66" ht="56" customHeight="1">
       <x:c r="A66" s="23"/>
       <x:c r="B66" s="39" t="str">
         <x:v>束缚强击
-バインドストライク</x:v>
+バインドストライク
+Binding Strike</x:v>
       </x:c>
       <x:c r="C66" s="23"/>
       <x:c r="D66" s="7" t="s">
@@ -2196,18 +2322,21 @@
       <x:c r="G66" s="29"/>
       <x:c r="H66" s="30"/>
     </x:row>
-    <x:row r="67" ht="40" customHeight="1">
+    <x:row r="67" ht="56" customHeight="1">
       <x:c r="A67" s="39" t="str">
         <x:v>冰雪之刃
-ブリザドブレード</x:v>
+ブリザドブレード
+Blizzard Edge</x:v>
       </x:c>
       <x:c r="B67" s="41" t="str">
         <x:v>冰雪or中冰雪
-ブリザドorブリザラ</x:v>
+ブリザドorブリザラ
+Blizzard or Blizzara</x:v>
       </x:c>
       <x:c r="C67" s="39" t="str">
         <x:v>空中破击
-エリアルブレイク</x:v>
+エリアルブレイク
+Quick Blitz</x:v>
       </x:c>
       <x:c r="D67" s="7" t="s">
         <x:v>23</x:v>
@@ -2223,12 +2352,13 @@
       </x:c>
       <x:c r="H67" s="30"/>
     </x:row>
-    <x:row r="68" ht="40" customHeight="1">
+    <x:row r="68" ht="56" customHeight="1">
       <x:c r="A68" s="23"/>
       <x:c r="B68" s="23"/>
       <x:c r="C68" s="39" t="str">
         <x:v>滑行冲刺
-スライドダッシュ</x:v>
+スライドダッシュ
+Sliding Dash</x:v>
       </x:c>
       <x:c r="D68" s="7" t="s">
         <x:v>24</x:v>
@@ -2238,18 +2368,21 @@
       <x:c r="G68" s="29"/>
       <x:c r="H68" s="30"/>
     </x:row>
-    <x:row r="69" ht="40" customHeight="1">
+    <x:row r="69" ht="56" customHeight="1">
       <x:c r="A69" s="39" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="B69" s="39" t="str">
         <x:v>雷电
-サンダー</x:v>
+サンダー
+Thunder</x:v>
       </x:c>
       <x:c r="C69" s="39" t="str">
         <x:v>滑行冲刺
-スライドダッシュ</x:v>
+スライドダッシュ
+Sliding Dash</x:v>
       </x:c>
       <x:c r="D69" s="7" t="s">
         <x:v>10</x:v>
@@ -2265,12 +2398,13 @@
       </x:c>
       <x:c r="H69" s="30"/>
     </x:row>
-    <x:row r="70" ht="40" customHeight="1">
+    <x:row r="70" ht="56" customHeight="1">
       <x:c r="A70" s="23"/>
       <x:c r="B70" s="23"/>
       <x:c r="C70" s="39" t="str">
         <x:v>强击飞掷
-ストライクレイド</x:v>
+ストライクレイド
+Strike Raid</x:v>
       </x:c>
       <x:c r="D70" s="7" t="s">
         <x:v>22</x:v>
@@ -2280,11 +2414,12 @@
       <x:c r="G70" s="29"/>
       <x:c r="H70" s="30"/>
     </x:row>
-    <x:row r="71" ht="40" customHeight="1">
+    <x:row r="71" ht="56" customHeight="1">
       <x:c r="A71" s="23"/>
       <x:c r="B71" s="39" t="str">
         <x:v>中雷电
-サンダラ</x:v>
+サンダラ
+Thundara</x:v>
       </x:c>
       <x:c r="C71" s="23"/>
       <x:c r="D71" s="7" t="s">
@@ -2295,18 +2430,21 @@
       <x:c r="G71" s="29"/>
       <x:c r="H71" s="30"/>
     </x:row>
-    <x:row r="72" ht="40" customHeight="1">
+    <x:row r="72" ht="56" customHeight="1">
       <x:c r="A72" s="39" t="str">
         <x:v>轮盘之刃
-スロットブレード</x:v>
+スロットブレード
+Slot Edge</x:v>
       </x:c>
       <x:c r="B72" s="39" t="str">
         <x:v>中恢复
-ケアルラ</x:v>
+ケアルラ
+Cura</x:v>
       </x:c>
       <x:c r="C72" s="39" t="str">
         <x:v>剧毒之刃
-ポイズンブレード</x:v>
+ポイズンブレード
+Poison Edge</x:v>
       </x:c>
       <x:c r="D72" s="7" t="s">
         <x:v>11</x:v>
@@ -2322,12 +2460,13 @@
       </x:c>
       <x:c r="H72" s="30"/>
     </x:row>
-    <x:row r="73" ht="40" customHeight="1">
+    <x:row r="73" ht="56" customHeight="1">
       <x:c r="A73" s="23"/>
       <x:c r="B73" s="23"/>
       <x:c r="C73" s="39" t="str">
         <x:v>冰雪之刃
-ブリザドブレード</x:v>
+ブリザドブレード
+Blizzard Edge</x:v>
       </x:c>
       <x:c r="D73" s="7" t="s">
         <x:v>23</x:v>
@@ -2337,15 +2476,17 @@
       <x:c r="G73" s="29"/>
       <x:c r="H73" s="30"/>
     </x:row>
-    <x:row r="74" ht="40" customHeight="1">
+    <x:row r="74" ht="56" customHeight="1">
       <x:c r="A74" s="23"/>
       <x:c r="B74" s="39" t="str">
         <x:v>大恢复
-ケアルガ</x:v>
+ケアルガ
+Curaga</x:v>
       </x:c>
       <x:c r="C74" s="39" t="str">
         <x:v>恢复格挡
-レストアガード</x:v>
+レストアガード
+Renewal Block</x:v>
       </x:c>
       <x:c r="D74" s="7" t="s">
         <x:v>14</x:v>
@@ -2357,12 +2498,13 @@
       </x:c>
       <x:c r="H74" s="30"/>
     </x:row>
-    <x:row r="75" ht="40" customHeight="1">
+    <x:row r="75" ht="56" customHeight="1">
       <x:c r="A75" s="23"/>
       <x:c r="B75" s="23"/>
       <x:c r="C75" s="39" t="str">
         <x:v>充能格挡
-チャージガード</x:v>
+チャージガード
+Focus Block</x:v>
       </x:c>
       <x:c r="D75" s="7" t="s">
         <x:v>11</x:v>
@@ -2372,12 +2514,13 @@
       <x:c r="G75" s="29"/>
       <x:c r="H75" s="30"/>
     </x:row>
-    <x:row r="76" ht="40" customHeight="1">
+    <x:row r="76" ht="56" customHeight="1">
       <x:c r="A76" s="23"/>
       <x:c r="B76" s="23"/>
       <x:c r="C76" s="39" t="str">
         <x:v>恢复屏障
-レストアバリア</x:v>
+レストアバリア
+Renewal Barrier</x:v>
       </x:c>
       <x:c r="D76" s="7" t="s">
         <x:v>14</x:v>
@@ -2393,12 +2536,13 @@
       </x:c>
       <x:c r="H76" s="30"/>
     </x:row>
-    <x:row r="77" ht="40" customHeight="1">
+    <x:row r="77" ht="56" customHeight="1">
       <x:c r="A77" s="23"/>
       <x:c r="B77" s="23"/>
       <x:c r="C77" s="39" t="str">
         <x:v>充能屏障
-チャージバリア</x:v>
+チャージバリア
+Focus Barrier</x:v>
       </x:c>
       <x:c r="D77" s="7" t="s">
         <x:v>11</x:v>
@@ -2408,15 +2552,17 @@
       <x:c r="G77" s="29"/>
       <x:c r="H77" s="30"/>
     </x:row>
-    <x:row r="78" ht="40" customHeight="1">
+    <x:row r="78" ht="56" customHeight="1">
       <x:c r="A78" s="23"/>
       <x:c r="B78" s="39" t="str">
         <x:v>恢复
-ケアル</x:v>
+ケアル
+Cure</x:v>
       </x:c>
       <x:c r="C78" s="39" t="str">
         <x:v>祈愿之刃
-ウィッシュブレード</x:v>
+ウィッシュブレード
+Wishing Edge</x:v>
       </x:c>
       <x:c r="D78" s="7" t="s">
         <x:v>8</x:v>
@@ -2426,18 +2572,21 @@
       <x:c r="G78" s="29"/>
       <x:c r="H78" s="30"/>
     </x:row>
-    <x:row r="79" ht="40" customHeight="1">
+    <x:row r="79" ht="56" customHeight="1">
       <x:c r="A79" s="39" t="str">
         <x:v>火焰强击
-ファイアストライク</x:v>
+ファイアストライク
+Fire Strike</x:v>
       </x:c>
       <x:c r="B79" s="39" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="C79" s="39" t="str">
         <x:v>火焰
-ファイア</x:v>
+ファイア
+Fire</x:v>
       </x:c>
       <x:c r="D79" s="7" t="s">
         <x:v>10</x:v>
@@ -2453,15 +2602,17 @@
       </x:c>
       <x:c r="H79" s="30"/>
     </x:row>
-    <x:row r="80" ht="40" customHeight="1">
+    <x:row r="80" ht="56" customHeight="1">
       <x:c r="A80" s="23"/>
       <x:c r="B80" s="39" t="str">
         <x:v>剧毒之刃
-ポイズンブレード</x:v>
+ポイズンブレード
+Poison Edge</x:v>
       </x:c>
       <x:c r="C80" s="39" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="D80" s="7" t="s">
         <x:v>13</x:v>
@@ -2471,15 +2622,17 @@
       <x:c r="G80" s="29"/>
       <x:c r="H80" s="30"/>
     </x:row>
-    <x:row r="81" ht="40" customHeight="1">
+    <x:row r="81" ht="56" customHeight="1">
       <x:c r="A81" s="23"/>
       <x:c r="B81" s="39" t="str">
         <x:v>祈愿之刃
-ウィッシュブレード</x:v>
+ウィッシュブレード
+Wishing Edge</x:v>
       </x:c>
       <x:c r="C81" s="39" t="str">
         <x:v>点燃
-スナイプバーニング</x:v>
+スナイプバーニング
+Ignite</x:v>
       </x:c>
       <x:c r="D81" s="7" t="s">
         <x:v>16</x:v>
@@ -2493,18 +2646,21 @@
       <x:c r="G81" s="29"/>
       <x:c r="H81" s="30"/>
     </x:row>
-    <x:row r="82" ht="40" customHeight="1">
+    <x:row r="82" ht="56" customHeight="1">
       <x:c r="A82" s="39" t="str">
         <x:v>混乱强击
-コンフュストライク</x:v>
+コンフュストライク
+Confusion Strike</x:v>
       </x:c>
       <x:c r="B82" s="39" t="str">
         <x:v>混乱
-コンフュ</x:v>
+コンフュ
+Confuse</x:v>
       </x:c>
       <x:c r="C82" s="39" t="str">
         <x:v>空中破击
-エリアルブレイク</x:v>
+エリアルブレイク
+Quick Blitz</x:v>
       </x:c>
       <x:c r="D82" s="7" t="s">
         <x:v>8</x:v>
@@ -2520,12 +2676,13 @@
       </x:c>
       <x:c r="H82" s="30"/>
     </x:row>
-    <x:row r="83" ht="40" customHeight="1">
+    <x:row r="83" ht="56" customHeight="1">
       <x:c r="A83" s="23"/>
       <x:c r="B83" s="23"/>
       <x:c r="C83" s="39" t="str">
         <x:v>强击飞掷
-ストライクレイド</x:v>
+ストライクレイド
+Strike Raid</x:v>
       </x:c>
       <x:c r="D83" s="7" t="s">
         <x:v>23</x:v>
@@ -2535,15 +2692,17 @@
       <x:c r="G83" s="29"/>
       <x:c r="H83" s="30"/>
     </x:row>
-    <x:row r="84" ht="40" customHeight="1">
+    <x:row r="84" ht="56" customHeight="1">
       <x:c r="A84" s="23"/>
       <x:c r="B84" s="39" t="str">
         <x:v>滑行冲刺
-スライドダッシュ</x:v>
+スライドダッシュ
+Sliding Dash</x:v>
       </x:c>
       <x:c r="C84" s="39" t="str">
         <x:v>零重力
-ゼログラビデ</x:v>
+ゼログラビデ
+Zero Gravity</x:v>
       </x:c>
       <x:c r="D84" s="7" t="s">
         <x:v>10</x:v>
@@ -2553,18 +2712,21 @@
       <x:c r="G84" s="29"/>
       <x:c r="H84" s="30"/>
     </x:row>
-    <x:row r="85" ht="40" customHeight="1">
+    <x:row r="85" ht="56" customHeight="1">
       <x:c r="A85" s="39" t="str">
         <x:v>束缚强击
-バインドストライク</x:v>
+バインドストライク
+Binding Strike</x:v>
       </x:c>
       <x:c r="B85" s="39" t="str">
         <x:v>束缚
-バインド</x:v>
+バインド
+Bind</x:v>
       </x:c>
       <x:c r="C85" s="39" t="str">
         <x:v>空中破击
-エリアルブレイク</x:v>
+エリアルブレイク
+Quick Blitz</x:v>
       </x:c>
       <x:c r="D85" s="7" t="s">
         <x:v>10</x:v>
@@ -2580,12 +2742,13 @@
       </x:c>
       <x:c r="H85" s="30"/>
     </x:row>
-    <x:row r="86" ht="40" customHeight="1">
+    <x:row r="86" ht="56" customHeight="1">
       <x:c r="A86" s="23"/>
       <x:c r="B86" s="23"/>
       <x:c r="C86" s="39" t="str">
         <x:v>强击飞掷
-ストライクレイド</x:v>
+ストライクレイド
+Strike Raid</x:v>
       </x:c>
       <x:c r="D86" s="7" t="s">
         <x:v>8</x:v>
@@ -2595,15 +2758,17 @@
       <x:c r="G86" s="29"/>
       <x:c r="H86" s="30"/>
     </x:row>
-    <x:row r="87" ht="40" customHeight="1">
+    <x:row r="87" ht="56" customHeight="1">
       <x:c r="A87" s="23"/>
       <x:c r="B87" s="39" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="C87" s="39" t="str">
         <x:v>零重力
-ゼログラビデ</x:v>
+ゼログラビデ
+Zero Gravity</x:v>
       </x:c>
       <x:c r="D87" s="7" t="s">
         <x:v>19</x:v>
@@ -2613,18 +2778,21 @@
       <x:c r="G87" s="29"/>
       <x:c r="H87" s="30"/>
     </x:row>
-    <x:row r="88" ht="40" customHeight="1">
+    <x:row r="88" ht="56" customHeight="1">
       <x:c r="A88" s="39" t="str">
         <x:v>龙卷强击
-トルネドストライク</x:v>
+トルネドストライク
+Tornado Strike</x:v>
       </x:c>
       <x:c r="B88" s="39" t="str">
         <x:v>大劲风
-エアロガ</x:v>
+エアロガ
+Aeroga</x:v>
       </x:c>
       <x:c r="C88" s="39" t="str">
         <x:v>混乱强击
-コンフュストライク</x:v>
+コンフュストライク
+Confusion Strike</x:v>
       </x:c>
       <x:c r="D88" s="7" t="s">
         <x:v>23</x:v>
@@ -2640,12 +2808,13 @@
       </x:c>
       <x:c r="H88" s="30"/>
     </x:row>
-    <x:row r="89" ht="40" customHeight="1">
+    <x:row r="89" ht="56" customHeight="1">
       <x:c r="A89" s="23"/>
       <x:c r="B89" s="23"/>
       <x:c r="C89" s="39" t="str">
         <x:v>束缚强击
-バインドストライク</x:v>
+バインドストライク
+Binding Strike</x:v>
       </x:c>
       <x:c r="D89" s="7" t="s">
         <x:v>18</x:v>
@@ -2655,18 +2824,21 @@
       <x:c r="G89" s="29"/>
       <x:c r="H89" s="30"/>
     </x:row>
-    <x:row r="90" ht="40" customHeight="1">
+    <x:row r="90" ht="56" customHeight="1">
       <x:c r="A90" s="39" t="str">
         <x:v>残暴冲击
-ブルータルブラスト</x:v>
+ブルータルブラスト
+Brutal Blast</x:v>
       </x:c>
       <x:c r="B90" s="39" t="str">
         <x:v>束缚强击
-バインドストライク</x:v>
+バインドストライク
+Binding Strike</x:v>
       </x:c>
       <x:c r="C90" s="39" t="str">
         <x:v>爆破方阵
-デトネスクウェア</x:v>
+デトネスクウェア
+Mine Square</x:v>
       </x:c>
       <x:c r="D90" s="7" t="s">
         <x:v>22</x:v>
@@ -2682,15 +2854,17 @@
       </x:c>
       <x:c r="H90" s="30"/>
     </x:row>
-    <x:row r="91" ht="40" customHeight="1">
+    <x:row r="91" ht="56" customHeight="1">
       <x:c r="A91" s="23"/>
       <x:c r="B91" s="39" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="C91" s="39" t="str">
         <x:v>爆破护盾
-デトネシールド</x:v>
+デトネシールド
+Mine Shield</x:v>
       </x:c>
       <x:c r="D91" s="7" t="s">
         <x:v>8</x:v>
@@ -2700,18 +2874,21 @@
       <x:c r="G91" s="29"/>
       <x:c r="H91" s="30"/>
     </x:row>
-    <x:row r="92" ht="40" customHeight="1">
+    <x:row r="92" ht="56" customHeight="1">
       <x:c r="A92" s="39" t="str">
         <x:v>磁力螺旋
-マグネスパイラル</x:v>
+マグネスパイラル
+Magnet Spiral</x:v>
       </x:c>
       <x:c r="B92" s="39" t="str">
         <x:v>束缚强击
-バインドストライク</x:v>
+バインドストライク
+Binding Strike</x:v>
       </x:c>
       <x:c r="C92" s="39" t="str">
         <x:v>磁力粉碎
-マグネクラッシュ</x:v>
+マグネクラッシュ
+Collision Magnet</x:v>
       </x:c>
       <x:c r="D92" s="7" t="s">
         <x:v>10</x:v>
@@ -2727,12 +2904,13 @@
       </x:c>
       <x:c r="H92" s="30"/>
     </x:row>
-    <x:row r="93" ht="40" customHeight="1">
+    <x:row r="93" ht="56" customHeight="1">
       <x:c r="A93" s="23"/>
       <x:c r="B93" s="23"/>
       <x:c r="C93" s="39" t="str">
         <x:v>大磁力
-マグネガ</x:v>
+マグネガ
+Magnega</x:v>
       </x:c>
       <x:c r="D93" s="7" t="s">
         <x:v>20</x:v>
@@ -2742,15 +2920,17 @@
       <x:c r="G93" s="29"/>
       <x:c r="H93" s="30"/>
     </x:row>
-    <x:row r="94" ht="40" customHeight="1">
+    <x:row r="94" ht="56" customHeight="1">
       <x:c r="A94" s="23"/>
       <x:c r="B94" s="39" t="str">
         <x:v>空中破击
-エリアルブレイク</x:v>
+エリアルブレイク
+Quick Blitz</x:v>
       </x:c>
       <x:c r="C94" s="39" t="str">
         <x:v>中磁力
-マグネラ</x:v>
+マグネラ
+Magnera</x:v>
       </x:c>
       <x:c r="D94" s="7" t="s">
         <x:v>10</x:v>
@@ -2762,15 +2942,17 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="40" customHeight="1">
+    <x:row r="95" ht="56" customHeight="1">
       <x:c r="A95" s="23"/>
       <x:c r="B95" s="39" t="str">
         <x:v>中零重力
-ゼログラビラ</x:v>
+ゼログラビラ
+Zero Gravira</x:v>
       </x:c>
       <x:c r="C95" s="39" t="str">
         <x:v>磁力
-マグネ</x:v>
+マグネ
+Magnet</x:v>
       </x:c>
       <x:c r="D95" s="7" t="s">
         <x:v>19</x:v>
@@ -2780,18 +2962,21 @@
       <x:c r="G95" s="29"/>
       <x:c r="H95" s="30"/>
     </x:row>
-    <x:row r="96" ht="40" customHeight="1">
+    <x:row r="96" ht="56" customHeight="1">
       <x:c r="A96" s="39" t="str">
         <x:v>疾风斩
-ウインドカッター</x:v>
+ウインドカッター
+Windcutter</x:v>
       </x:c>
       <x:c r="B96" s="39" t="str">
         <x:v>混乱强击
-コンフュストライク</x:v>
+コンフュストライク
+Confusion Strike</x:v>
       </x:c>
       <x:c r="C96" s="39" t="str">
         <x:v>大劲风
-エアロガ</x:v>
+エアロガ
+Aeroga</x:v>
       </x:c>
       <x:c r="D96" s="7" t="s">
         <x:v>23</x:v>
@@ -2807,18 +2992,21 @@
       </x:c>
       <x:c r="H96" s="7"/>
     </x:row>
-    <x:row r="97" ht="40" customHeight="1">
+    <x:row r="97" ht="56" customHeight="1">
       <x:c r="A97" s="39" t="str">
         <x:v>极限风暴
-リミットストーム</x:v>
+リミットストーム
+Limit Storm</x:v>
       </x:c>
       <x:c r="B97" s="39" t="str">
         <x:v>残暴冲击
-ブルータルブラスト</x:v>
+ブルータルブラスト
+Brutal Blast</x:v>
       </x:c>
       <x:c r="C97" s="39" t="str">
         <x:v>混乱强击
-コンフュストライク</x:v>
+コンフュストライク
+Confusion Strike</x:v>
       </x:c>
       <x:c r="D97" s="7" t="s">
         <x:v>23</x:v>
@@ -2834,12 +3022,13 @@
       </x:c>
       <x:c r="H97" s="30"/>
     </x:row>
-    <x:row r="98" ht="40" customHeight="1">
+    <x:row r="98" ht="56" customHeight="1">
       <x:c r="A98" s="23"/>
       <x:c r="B98" s="23"/>
       <x:c r="C98" s="39" t="str">
         <x:v>束缚强击
-バインドストライク</x:v>
+バインドストライク
+Binding Strike</x:v>
       </x:c>
       <x:c r="D98" s="7" t="s">
         <x:v>13</x:v>
@@ -2849,18 +3038,21 @@
       <x:c r="G98" s="29"/>
       <x:c r="H98" s="30"/>
     </x:row>
-    <x:row r="99" ht="40" customHeight="1">
+    <x:row r="99" ht="56" customHeight="1">
       <x:c r="A99" s="39" t="str">
         <x:v>神圣升腾
-ホーリーライズ</x:v>
+ホーリーライズ
+Salvation</x:v>
       </x:c>
       <x:c r="B99" s="39" t="str">
         <x:v>疾风飞掷
-ウインドレイド</x:v>
+ウインドレイド
+Wind Raid</x:v>
       </x:c>
       <x:c r="C99" s="39" t="str">
         <x:v>大恢复
-ケアルガ</x:v>
+ケアルガ
+Curaga</x:v>
       </x:c>
       <x:c r="D99" s="7" t="s">
         <x:v>14</x:v>
@@ -2876,18 +3068,21 @@
       </x:c>
       <x:c r="H99" s="7"/>
     </x:row>
-    <x:row r="100" ht="40" customHeight="1">
+    <x:row r="100" ht="56" customHeight="1">
       <x:c r="A100" s="39" t="str">
         <x:v>磁力粉碎
-マグネクラッシュ</x:v>
+マグネクラッシュ
+Collision Magnet</x:v>
       </x:c>
       <x:c r="B100" s="39" t="str">
         <x:v>中磁力
-マグネラ</x:v>
+マグネラ
+Magnera</x:v>
       </x:c>
       <x:c r="C100" s="39" t="str">
         <x:v>空中破击
-エリアルブレイク</x:v>
+エリアルブレイク
+Quick Blitz</x:v>
       </x:c>
       <x:c r="D100" s="7" t="s">
         <x:v>10</x:v>
@@ -2903,12 +3098,13 @@
       </x:c>
       <x:c r="H100" s="30"/>
     </x:row>
-    <x:row r="101" ht="40" customHeight="1">
+    <x:row r="101" ht="56" customHeight="1">
       <x:c r="A101" s="23"/>
       <x:c r="B101" s="23"/>
       <x:c r="C101" s="39" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="D101" s="7" t="s">
         <x:v>22</x:v>
@@ -2918,15 +3114,17 @@
       <x:c r="G101" s="29"/>
       <x:c r="H101" s="30"/>
     </x:row>
-    <x:row r="102" ht="40" customHeight="1">
+    <x:row r="102" ht="56" customHeight="1">
       <x:c r="A102" s="23"/>
       <x:c r="B102" s="39" t="str">
         <x:v>中零重力
-ゼログラビラ</x:v>
+ゼログラビラ
+Zero Gravira</x:v>
       </x:c>
       <x:c r="C102" s="39" t="str">
         <x:v>磁力
-マグネ</x:v>
+マグネ
+Magnet</x:v>
       </x:c>
       <x:c r="D102" s="7" t="s">
         <x:v>19</x:v>
@@ -2936,18 +3134,21 @@
       <x:c r="G102" s="29"/>
       <x:c r="H102" s="30"/>
     </x:row>
-    <x:row r="103" ht="40" customHeight="1">
+    <x:row r="103" ht="56" customHeight="1">
       <x:c r="A103" s="39" t="str">
         <x:v>大地破击
-ガイアブレイク</x:v>
+ガイアブレイク
+Geo Impact</x:v>
       </x:c>
       <x:c r="B103" s="39" t="str">
         <x:v>残暴冲击
-ブルータルブラスト</x:v>
+ブルータルブラスト
+Brutal Blast</x:v>
       </x:c>
       <x:c r="C103" s="39" t="str">
         <x:v>残暴冲击
-ブルータルブラスト</x:v>
+ブルータルブラスト
+Brutal Blast</x:v>
       </x:c>
       <x:c r="D103" s="7" t="s">
         <x:v>14</x:v>
@@ -2963,18 +3164,21 @@
       </x:c>
       <x:c r="H103" s="7"/>
     </x:row>
-    <x:row r="104" ht="40" customHeight="1">
+    <x:row r="104" ht="56" customHeight="1">
       <x:c r="A104" s="39" t="str">
         <x:v>灵魂释放
-ソウルリリース</x:v>
+ソウルリリース
+Sacrifice</x:v>
       </x:c>
       <x:c r="B104" s="39" t="str">
         <x:v>驱逐
-デジョン</x:v>
+デジョン
+Warp</x:v>
       </x:c>
       <x:c r="C104" s="39" t="str">
         <x:v>黑暗迷雾
-ダークヘイズ</x:v>
+ダークヘイズ
+Dark Haze</x:v>
       </x:c>
       <x:c r="D104" s="7" t="s">
         <x:v>17</x:v>
@@ -2990,12 +3194,13 @@
       </x:c>
       <x:c r="H104" s="30"/>
     </x:row>
-    <x:row r="105" ht="40" customHeight="1">
+    <x:row r="105" ht="56" customHeight="1">
       <x:c r="A105" s="23"/>
       <x:c r="B105" s="23"/>
       <x:c r="C105" s="39" t="str">
         <x:v>剧毒之刃
-ポイズンブレード</x:v>
+ポイズンブレード
+Poison Edge</x:v>
       </x:c>
       <x:c r="D105" s="7" t="s">
         <x:v>13</x:v>
@@ -3005,18 +3210,21 @@
       <x:c r="G105" s="29"/>
       <x:c r="H105" s="30"/>
     </x:row>
-    <x:row r="106" ht="40" customHeight="1">
+    <x:row r="106" ht="56" customHeight="1">
       <x:c r="A106" s="39" t="str">
         <x:v>休息时间
-ブレイクタイム</x:v>
+ブレイクタイム
+Break Time</x:v>
       </x:c>
       <x:c r="B106" s="39" t="str">
         <x:v>大恢复
-ケアルガ</x:v>
+ケアルガ
+Curaga</x:v>
       </x:c>
       <x:c r="C106" s="39" t="str">
         <x:v>恢复格挡
-レストアガード</x:v>
+レストアガード
+Renewal Block</x:v>
       </x:c>
       <x:c r="D106" s="7" t="s">
         <x:v>14</x:v>
@@ -3034,12 +3242,13 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="40" customHeight="1">
+    <x:row r="107" ht="56" customHeight="1">
       <x:c r="A107" s="23"/>
       <x:c r="B107" s="23"/>
       <x:c r="C107" s="39" t="str">
         <x:v>充能格挡
-チャージガード</x:v>
+チャージガード
+Focus Block</x:v>
       </x:c>
       <x:c r="D107" s="7" t="s">
         <x:v>11</x:v>
@@ -3049,12 +3258,13 @@
       <x:c r="G107" s="29"/>
       <x:c r="H107" s="30"/>
     </x:row>
-    <x:row r="108" ht="40" customHeight="1">
+    <x:row r="108" ht="56" customHeight="1">
       <x:c r="A108" s="23"/>
       <x:c r="B108" s="23"/>
       <x:c r="C108" s="39" t="str">
         <x:v>恢复屏障
-レストアバリア</x:v>
+レストアバリア
+Renewal Barrier</x:v>
       </x:c>
       <x:c r="D108" s="7" t="s">
         <x:v>14</x:v>
@@ -3070,12 +3280,13 @@
       </x:c>
       <x:c r="H108" s="30"/>
     </x:row>
-    <x:row r="109" ht="40" customHeight="1">
+    <x:row r="109" ht="56" customHeight="1">
       <x:c r="A109" s="23"/>
       <x:c r="B109" s="23"/>
       <x:c r="C109" s="39" t="str">
         <x:v>充能屏障
-チャージバリア</x:v>
+チャージバリア
+Focus Barrier</x:v>
       </x:c>
       <x:c r="D109" s="7" t="s">
         <x:v>11</x:v>
@@ -3340,18 +3551,21 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="40" customHeight="1">
+    <x:row r="2" ht="56" customHeight="1">
       <x:c r="A2" s="42" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="B2" s="42" t="str">
         <x:v>火焰
-ファイア</x:v>
+ファイア
+Fire</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
         <x:v>火焰
-ファイア</x:v>
+ファイア
+Fire</x:v>
       </x:c>
       <x:c r="D2" s="7" t="s">
         <x:v>16</x:v>
@@ -3367,12 +3581,13 @@
       </x:c>
       <x:c r="H2" s="30"/>
     </x:row>
-    <x:row r="3" ht="40" customHeight="1">
+    <x:row r="3" ht="56" customHeight="1">
       <x:c r="A3" s="33"/>
       <x:c r="B3" s="33"/>
       <x:c r="C3" s="43" t="str">
         <x:v>火焰冲刺
-ファイアダッシュ</x:v>
+ファイアダッシュ
+Fire Dash</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
         <x:v>13</x:v>
@@ -3382,12 +3597,13 @@
       <x:c r="G3" s="29"/>
       <x:c r="H3" s="30"/>
     </x:row>
-    <x:row r="4" ht="40" customHeight="1">
+    <x:row r="4" ht="56" customHeight="1">
       <x:c r="A4" s="33"/>
       <x:c r="B4" s="33"/>
       <x:c r="C4" s="43" t="str">
         <x:v>火焰强击
-ファイアストライク</x:v>
+ファイアストライク
+Fire Strike</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
         <x:v>13</x:v>
@@ -3397,12 +3613,13 @@
       <x:c r="G4" s="29"/>
       <x:c r="H4" s="30"/>
     </x:row>
-    <x:row r="5" ht="40" customHeight="1">
+    <x:row r="5" ht="56" customHeight="1">
       <x:c r="A5" s="34"/>
       <x:c r="B5" s="34"/>
       <x:c r="C5" s="43" t="str">
         <x:v>点燃
-スナイプバーニング</x:v>
+スナイプバーニング
+Ignite</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
         <x:v>15</x:v>
@@ -3412,18 +3629,21 @@
       <x:c r="G5" s="29"/>
       <x:c r="H5" s="30"/>
     </x:row>
-    <x:row r="6" ht="40" customHeight="1">
+    <x:row r="6" ht="56" customHeight="1">
       <x:c r="A6" s="42" t="str">
         <x:v>大火焰
-ファイガ</x:v>
+ファイガ
+Firaga</x:v>
       </x:c>
       <x:c r="B6" s="42" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>火焰
-ファイア</x:v>
+ファイア
+Fire</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
         <x:v>16</x:v>
@@ -3439,12 +3659,13 @@
       </x:c>
       <x:c r="H6" s="30"/>
     </x:row>
-    <x:row r="7" ht="40" customHeight="1">
+    <x:row r="7" ht="56" customHeight="1">
       <x:c r="A7" s="33"/>
       <x:c r="B7" s="33"/>
       <x:c r="C7" s="43" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
         <x:v>17</x:v>
@@ -3454,12 +3675,13 @@
       <x:c r="G7" s="29"/>
       <x:c r="H7" s="30"/>
     </x:row>
-    <x:row r="8" ht="40" customHeight="1">
+    <x:row r="8" ht="56" customHeight="1">
       <x:c r="A8" s="34"/>
       <x:c r="B8" s="34"/>
       <x:c r="C8" s="43" t="str">
         <x:v>火焰冲刺
-ファイアダッシュ</x:v>
+ファイアダッシュ
+Fire Dash</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
         <x:v>13</x:v>
@@ -3469,18 +3691,21 @@
       <x:c r="G8" s="29"/>
       <x:c r="H8" s="30"/>
     </x:row>
-    <x:row r="9" ht="40" customHeight="1">
+    <x:row r="9" ht="56" customHeight="1">
       <x:c r="A9" s="42" t="str">
         <x:v>黑暗大火焰
-ダークファイガ</x:v>
+ダークファイガ
+Dark Firaga</x:v>
       </x:c>
       <x:c r="B9" s="42" t="str">
         <x:v>大火焰
-ファイガ</x:v>
+ファイガ
+Firaga</x:v>
       </x:c>
       <x:c r="C9" s="43" t="str">
         <x:v>黑暗迷雾
-ダークヘイズ</x:v>
+ダークヘイズ
+Dark Haze</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
         <x:v>13</x:v>
@@ -3496,12 +3721,13 @@
       </x:c>
       <x:c r="H9" s="30"/>
     </x:row>
-    <x:row r="10" ht="40" customHeight="1">
+    <x:row r="10" ht="56" customHeight="1">
       <x:c r="A10" s="34"/>
       <x:c r="B10" s="33"/>
       <x:c r="C10" s="43" t="str">
         <x:v>致盲
-ブラックアウト</x:v>
+ブラックアウト
+Blackout</x:v>
       </x:c>
       <x:c r="D10" s="7" t="s">
         <x:v>17</x:v>
@@ -3511,18 +3737,21 @@
       <x:c r="G10" s="29"/>
       <x:c r="H10" s="30"/>
     </x:row>
-    <x:row r="11" ht="40" customHeight="1">
+    <x:row r="11" ht="56" customHeight="1">
       <x:c r="A11" s="42" t="str">
         <x:v>爆裂大火焰
-クラッカーファイガ</x:v>
+クラッカーファイガ
+Fission Firaga</x:v>
       </x:c>
       <x:c r="B11" s="44" t="str">
         <x:v>大火焰
-ファイガ</x:v>
+ファイガ
+Firaga</x:v>
       </x:c>
       <x:c r="C11" s="43" t="str">
         <x:v>中劲风
-エアロラ</x:v>
+エアロラ
+Aerora</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
         <x:v>16</x:v>
@@ -3538,12 +3767,13 @@
       </x:c>
       <x:c r="H11" s="30"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="56" customHeight="1">
       <x:c r="A12" s="33"/>
       <x:c r="B12" s="34"/>
       <x:c r="C12" s="42" t="str">
         <x:v>大劲风
-エアロガ</x:v>
+エアロガ
+Aeroga</x:v>
       </x:c>
       <x:c r="D12" s="7" t="s">
         <x:v>17</x:v>
@@ -3553,11 +3783,12 @@
       <x:c r="G12" s="29"/>
       <x:c r="H12" s="30"/>
     </x:row>
-    <x:row r="13" ht="40" customHeight="1">
+    <x:row r="13" ht="56" customHeight="1">
       <x:c r="A13" s="34"/>
       <x:c r="B13" s="43" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="C13" s="34"/>
       <x:c r="D13" s="7" t="s">
@@ -3568,18 +3799,21 @@
       <x:c r="G13" s="29"/>
       <x:c r="H13" s="30"/>
     </x:row>
-    <x:row r="14" ht="40" customHeight="1">
+    <x:row r="14" ht="56" customHeight="1">
       <x:c r="A14" s="42" t="str">
         <x:v>三重大火焰
-トリプルファイガ</x:v>
+トリプルファイガ
+Triple Firaga</x:v>
       </x:c>
       <x:c r="B14" s="42" t="str">
         <x:v>大火焰
-ファイガ</x:v>
+ファイガ
+Firaga</x:v>
       </x:c>
       <x:c r="C14" s="43" t="str">
         <x:v>最终破击
-ファイナルブレイク</x:v>
+ファイナルブレイク
+Blitz</x:v>
       </x:c>
       <x:c r="D14" s="7" t="s">
         <x:v>13</x:v>
@@ -3595,12 +3829,13 @@
       </x:c>
       <x:c r="H14" s="30"/>
     </x:row>
-    <x:row r="15" ht="40" customHeight="1">
+    <x:row r="15" ht="56" customHeight="1">
       <x:c r="A15" s="33"/>
       <x:c r="B15" s="33"/>
       <x:c r="C15" s="43" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="D15" s="7" t="s">
         <x:v>16</x:v>
@@ -3610,12 +3845,13 @@
       <x:c r="G15" s="29"/>
       <x:c r="H15" s="30"/>
     </x:row>
-    <x:row r="16" ht="40" customHeight="1">
+    <x:row r="16" ht="56" customHeight="1">
       <x:c r="A16" s="34"/>
       <x:c r="B16" s="33"/>
       <x:c r="C16" s="43" t="str">
         <x:v>大火焰
-ファイガ</x:v>
+ファイガ
+Firaga</x:v>
       </x:c>
       <x:c r="D16" s="7" t="s">
         <x:v>17</x:v>
@@ -3625,18 +3861,21 @@
       <x:c r="G16" s="29"/>
       <x:c r="H16" s="30"/>
     </x:row>
-    <x:row r="17" ht="40" customHeight="1">
+    <x:row r="17" ht="56" customHeight="1">
       <x:c r="A17" s="42" t="str">
         <x:v>蔓延火焰
-バレッジファイア</x:v>
+バレッジファイア
+Crawling Fire</x:v>
       </x:c>
       <x:c r="B17" s="44" t="str">
         <x:v>大火焰
-ファイガ</x:v>
+ファイガ
+Firaga</x:v>
       </x:c>
       <x:c r="C17" s="43" t="str">
         <x:v>迟缓
-スロウ</x:v>
+スロウ
+Slow</x:v>
       </x:c>
       <x:c r="D17" s="7" t="s">
         <x:v>16</x:v>
@@ -3652,12 +3891,13 @@
       </x:c>
       <x:c r="H17" s="30"/>
     </x:row>
-    <x:row r="18" ht="40" customHeight="1">
+    <x:row r="18" ht="56" customHeight="1">
       <x:c r="A18" s="33"/>
       <x:c r="B18" s="33"/>
       <x:c r="C18" s="43" t="str">
         <x:v>中停止
-ストプラ</x:v>
+ストプラ
+Stopra</x:v>
       </x:c>
       <x:c r="D18" s="7" t="s">
         <x:v>13</x:v>
@@ -3667,12 +3907,13 @@
       <x:c r="G18" s="29"/>
       <x:c r="H18" s="30"/>
     </x:row>
-    <x:row r="19" ht="40" customHeight="1">
+    <x:row r="19" ht="56" customHeight="1">
       <x:c r="A19" s="34"/>
       <x:c r="B19" s="34"/>
       <x:c r="C19" s="43" t="str">
         <x:v>大停止
-ストプガ</x:v>
+ストプガ
+Stopga</x:v>
       </x:c>
       <x:c r="D19" s="7" t="s">
         <x:v>17</x:v>
@@ -3682,18 +3923,21 @@
       <x:c r="G19" s="29"/>
       <x:c r="H19" s="30"/>
     </x:row>
-    <x:row r="20" ht="40" customHeight="1">
+    <x:row r="20" ht="56" customHeight="1">
       <x:c r="A20" s="42" t="str">
         <x:v>中冰雪
-ブリザラ</x:v>
+ブリザラ
+Blizzara</x:v>
       </x:c>
       <x:c r="B20" s="45" t="str">
         <x:v>冰雪
-ブリザド</x:v>
+ブリザド
+Blizzard</x:v>
       </x:c>
       <x:c r="C20" s="43" t="str">
         <x:v>冰雪
-ブリザド</x:v>
+ブリザド
+Blizzard</x:v>
       </x:c>
       <x:c r="D20" s="7" t="s">
         <x:v>24</x:v>
@@ -3709,12 +3953,13 @@
       </x:c>
       <x:c r="H20" s="30"/>
     </x:row>
-    <x:row r="21" ht="40" customHeight="1">
+    <x:row r="21" ht="56" customHeight="1">
       <x:c r="A21" s="33"/>
       <x:c r="B21" s="36"/>
       <x:c r="C21" s="43" t="str">
         <x:v>劲风
-エアロ</x:v>
+エアロ
+Aero</x:v>
       </x:c>
       <x:c r="D21" s="7" t="s">
         <x:v>25</x:v>
@@ -3724,12 +3969,13 @@
       <x:c r="G21" s="29"/>
       <x:c r="H21" s="30"/>
     </x:row>
-    <x:row r="22" ht="40" customHeight="1">
+    <x:row r="22" ht="56" customHeight="1">
       <x:c r="A22" s="33"/>
       <x:c r="B22" s="36"/>
       <x:c r="C22" s="43" t="str">
         <x:v>强击飞掷
-ストライクレイド</x:v>
+ストライクレイド
+Strike Raid</x:v>
       </x:c>
       <x:c r="D22" s="7" t="s">
         <x:v>23</x:v>
@@ -3739,12 +3985,13 @@
       <x:c r="G22" s="29"/>
       <x:c r="H22" s="30"/>
     </x:row>
-    <x:row r="23" ht="40" customHeight="1">
+    <x:row r="23" ht="56" customHeight="1">
       <x:c r="A23" s="34"/>
       <x:c r="B23" s="37"/>
       <x:c r="C23" s="43" t="str">
         <x:v>冰雪之刃
-ブリザドブレード</x:v>
+ブリザドブレード
+Blizzard Edge</x:v>
       </x:c>
       <x:c r="D23" s="7" t="s">
         <x:v>23</x:v>
@@ -3754,18 +4001,21 @@
       <x:c r="G23" s="29"/>
       <x:c r="H23" s="30"/>
     </x:row>
-    <x:row r="24" ht="40" customHeight="1">
+    <x:row r="24" ht="56" customHeight="1">
       <x:c r="A24" s="42" t="str">
         <x:v>大冰雪
-ブリザガ</x:v>
+ブリザガ
+Blizzaga</x:v>
       </x:c>
       <x:c r="B24" s="42" t="str">
         <x:v>中冰雪
-ブリザラ</x:v>
+ブリザラ
+Blizzara</x:v>
       </x:c>
       <x:c r="C24" s="43" t="str">
         <x:v>冰雪
-ブリザド</x:v>
+ブリザド
+Blizzard</x:v>
       </x:c>
       <x:c r="D24" s="7" t="s">
         <x:v>24</x:v>
@@ -3781,12 +4031,13 @@
       </x:c>
       <x:c r="H24" s="30"/>
     </x:row>
-    <x:row r="25" ht="40" customHeight="1">
+    <x:row r="25" ht="56" customHeight="1">
       <x:c r="A25" s="33"/>
       <x:c r="B25" s="33"/>
       <x:c r="C25" s="43" t="str">
         <x:v>中冰雪
-ブリザラ</x:v>
+ブリザラ
+Blizzara</x:v>
       </x:c>
       <x:c r="D25" s="7" t="s">
         <x:v>18</x:v>
@@ -3796,12 +4047,13 @@
       <x:c r="G25" s="29"/>
       <x:c r="H25" s="30"/>
     </x:row>
-    <x:row r="26" ht="40" customHeight="1">
+    <x:row r="26" ht="56" customHeight="1">
       <x:c r="A26" s="34"/>
       <x:c r="B26" s="34"/>
       <x:c r="C26" s="43" t="str">
         <x:v>冰雪之刃
-ブリザドブレード</x:v>
+ブリザドブレード
+Blizzard Edge</x:v>
       </x:c>
       <x:c r="D26" s="7" t="s">
         <x:v>23</x:v>
@@ -3811,18 +4063,21 @@
       <x:c r="G26" s="29"/>
       <x:c r="H26" s="30"/>
     </x:row>
-    <x:row r="27" ht="40" customHeight="1">
+    <x:row r="27" ht="56" customHeight="1">
       <x:c r="A27" s="42" t="str">
         <x:v>三重大冰雪
-トリプルブリザガ</x:v>
+トリプルブリザガ
+Triple Blizzaga</x:v>
       </x:c>
       <x:c r="B27" s="42" t="str">
         <x:v>大冰雪
-ブリザガ</x:v>
+ブリザガ
+Blizzaga</x:v>
       </x:c>
       <x:c r="C27" s="43" t="str">
         <x:v>中冰雪
-ブリザラ</x:v>
+ブリザラ
+Blizzara</x:v>
       </x:c>
       <x:c r="D27" s="7" t="s">
         <x:v>24</x:v>
@@ -3838,12 +4093,13 @@
       </x:c>
       <x:c r="H27" s="30"/>
     </x:row>
-    <x:row r="28" ht="40" customHeight="1">
+    <x:row r="28" ht="56" customHeight="1">
       <x:c r="A28" s="33"/>
       <x:c r="B28" s="33"/>
       <x:c r="C28" s="43" t="str">
         <x:v>大冰雪
-ブリザガ</x:v>
+ブリザガ
+Blizzaga</x:v>
       </x:c>
       <x:c r="D28" s="7" t="s">
         <x:v>18</x:v>
@@ -3853,12 +4109,13 @@
       <x:c r="G28" s="29"/>
       <x:c r="H28" s="30"/>
     </x:row>
-    <x:row r="29" ht="40" customHeight="1">
+    <x:row r="29" ht="56" customHeight="1">
       <x:c r="A29" s="34"/>
       <x:c r="B29" s="34"/>
       <x:c r="C29" s="43" t="str">
         <x:v>最终破击
-ファイナルブレイク</x:v>
+ファイナルブレイク
+Blitz</x:v>
       </x:c>
       <x:c r="D29" s="7" t="s">
         <x:v>23</x:v>
@@ -3868,18 +4125,21 @@
       <x:c r="G29" s="29"/>
       <x:c r="H29" s="30"/>
     </x:row>
-    <x:row r="30" ht="40" customHeight="1">
+    <x:row r="30" ht="56" customHeight="1">
       <x:c r="A30" s="42" t="str">
         <x:v>中雷电
-サンダラ</x:v>
+サンダラ
+Thundara</x:v>
       </x:c>
       <x:c r="B30" s="42" t="str">
         <x:v>雷电
-サンダー</x:v>
+サンダー
+Thunder</x:v>
       </x:c>
       <x:c r="C30" s="43" t="str">
         <x:v>雷电
-サンダー</x:v>
+サンダー
+Thunder</x:v>
       </x:c>
       <x:c r="D30" s="7" t="s">
         <x:v>19</x:v>
@@ -3895,12 +4155,13 @@
       </x:c>
       <x:c r="H30" s="30"/>
     </x:row>
-    <x:row r="31" ht="40" customHeight="1">
+    <x:row r="31" ht="56" customHeight="1">
       <x:c r="A31" s="33"/>
       <x:c r="B31" s="34"/>
       <x:c r="C31" s="43" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="D31" s="7" t="s">
         <x:v>10</x:v>
@@ -3910,15 +4171,17 @@
       <x:c r="G31" s="29"/>
       <x:c r="H31" s="30"/>
     </x:row>
-    <x:row r="32" ht="40" customHeight="1">
+    <x:row r="32" ht="56" customHeight="1">
       <x:c r="A32" s="34"/>
       <x:c r="B32" s="43" t="str">
         <x:v>零重力
-ゼログラビデ</x:v>
+ゼログラビデ
+Zero Gravity</x:v>
       </x:c>
       <x:c r="C32" s="43" t="str">
         <x:v>磁力
-マグネ</x:v>
+マグネ
+Magnet</x:v>
       </x:c>
       <x:c r="D32" s="7" t="s">
         <x:v>22</x:v>
@@ -3928,18 +4191,21 @@
       <x:c r="G32" s="29"/>
       <x:c r="H32" s="30"/>
     </x:row>
-    <x:row r="33" ht="40" customHeight="1">
+    <x:row r="33" ht="56" customHeight="1">
       <x:c r="A33" s="42" t="str">
         <x:v>大雷电
-サンダガ</x:v>
+サンダガ
+Thundaga</x:v>
       </x:c>
       <x:c r="B33" s="42" t="str">
         <x:v>中雷电
-サンダラ</x:v>
+サンダラ
+Thundara</x:v>
       </x:c>
       <x:c r="C33" s="43" t="str">
         <x:v>雷电
-サンダー</x:v>
+サンダー
+Thunder</x:v>
       </x:c>
       <x:c r="D33" s="7" t="s">
         <x:v>19</x:v>
@@ -3955,12 +4221,13 @@
       </x:c>
       <x:c r="H33" s="30"/>
     </x:row>
-    <x:row r="34" ht="40" customHeight="1">
+    <x:row r="34" ht="56" customHeight="1">
       <x:c r="A34" s="33"/>
       <x:c r="B34" s="33"/>
       <x:c r="C34" s="43" t="str">
         <x:v>中雷电
-サンダラ</x:v>
+サンダラ
+Thundara</x:v>
       </x:c>
       <x:c r="D34" s="7" t="s">
         <x:v>20</x:v>
@@ -3970,12 +4237,13 @@
       <x:c r="G34" s="29"/>
       <x:c r="H34" s="30"/>
     </x:row>
-    <x:row r="35" ht="40" customHeight="1">
+    <x:row r="35" ht="56" customHeight="1">
       <x:c r="A35" s="34"/>
       <x:c r="B35" s="34"/>
       <x:c r="C35" s="43" t="str">
         <x:v>束缚强击
-バインドストライク</x:v>
+バインドストライク
+Binding Strike</x:v>
       </x:c>
       <x:c r="D35" s="7" t="s">
         <x:v>10</x:v>
@@ -3985,18 +4253,21 @@
       <x:c r="G35" s="29"/>
       <x:c r="H35" s="30"/>
     </x:row>
-    <x:row r="36" ht="40" customHeight="1">
+    <x:row r="36" ht="56" customHeight="1">
       <x:c r="A36" s="42" t="str">
         <x:v>大雷电射击
-サンダガショット</x:v>
+サンダガショット
+Thundaga Shot</x:v>
       </x:c>
       <x:c r="B36" s="42" t="str">
         <x:v>大雷电
-サンダガ</x:v>
+サンダガ
+Thundaga</x:v>
       </x:c>
       <x:c r="C36" s="43" t="str">
         <x:v>大火焰
-ファイガ</x:v>
+ファイガ
+Firaga</x:v>
       </x:c>
       <x:c r="D36" s="7" t="s">
         <x:v>16</x:v>
@@ -4012,12 +4283,13 @@
       </x:c>
       <x:c r="H36" s="30"/>
     </x:row>
-    <x:row r="37" ht="40" customHeight="1">
+    <x:row r="37" ht="56" customHeight="1">
       <x:c r="A37" s="33"/>
       <x:c r="B37" s="33"/>
       <x:c r="C37" s="43" t="str">
         <x:v>强击飞掷
-ストライクレイド</x:v>
+ストライクレイド
+Strike Raid</x:v>
       </x:c>
       <x:c r="D37" s="7" t="s">
         <x:v>19</x:v>
@@ -4027,12 +4299,13 @@
       <x:c r="G37" s="29"/>
       <x:c r="H37" s="30"/>
     </x:row>
-    <x:row r="38" ht="40" customHeight="1">
+    <x:row r="38" ht="56" customHeight="1">
       <x:c r="A38" s="34"/>
       <x:c r="B38" s="34"/>
       <x:c r="C38" s="43" t="str">
         <x:v>冰冻飞掷
-フリーズレイド</x:v>
+フリーズレイド
+Freeze Raid</x:v>
       </x:c>
       <x:c r="D38" s="7" t="s">
         <x:v>24</x:v>
@@ -4042,18 +4315,21 @@
       <x:c r="G38" s="29"/>
       <x:c r="H38" s="30"/>
     </x:row>
-    <x:row r="39" ht="40" customHeight="1">
+    <x:row r="39" ht="56" customHeight="1">
       <x:c r="A39" s="42" t="str">
         <x:v>中恢复
-ケアルラ</x:v>
+ケアルラ
+Cura</x:v>
       </x:c>
       <x:c r="B39" s="42" t="str">
         <x:v>恢复
-ケアル</x:v>
+ケアル
+Cure</x:v>
       </x:c>
       <x:c r="C39" s="43" t="str">
         <x:v>恢复
-ケアル</x:v>
+ケアル
+Cure</x:v>
       </x:c>
       <x:c r="D39" s="7" t="s">
         <x:v>26</x:v>
@@ -4069,12 +4345,13 @@
       </x:c>
       <x:c r="H39" s="30"/>
     </x:row>
-    <x:row r="40" ht="40" customHeight="1">
+    <x:row r="40" ht="56" customHeight="1">
       <x:c r="A40" s="33"/>
       <x:c r="B40" s="33"/>
       <x:c r="C40" s="43" t="str">
         <x:v>雷电
-サンダー</x:v>
+サンダー
+Thunder</x:v>
       </x:c>
       <x:c r="D40" s="7" t="s">
         <x:v>19</x:v>
@@ -4084,12 +4361,13 @@
       <x:c r="G40" s="29"/>
       <x:c r="H40" s="30"/>
     </x:row>
-    <x:row r="41" ht="40" customHeight="1">
+    <x:row r="41" ht="56" customHeight="1">
       <x:c r="A41" s="34"/>
       <x:c r="B41" s="34"/>
       <x:c r="C41" s="43" t="str">
         <x:v>劲风
-エアロ</x:v>
+エアロ
+Aero</x:v>
       </x:c>
       <x:c r="D41" s="7" t="s">
         <x:v>8</x:v>
@@ -4099,18 +4377,21 @@
       <x:c r="G41" s="29"/>
       <x:c r="H41" s="30"/>
     </x:row>
-    <x:row r="42" ht="40" customHeight="1">
+    <x:row r="42" ht="56" customHeight="1">
       <x:c r="A42" s="42" t="str">
         <x:v>大恢复
-ケアルガ</x:v>
+ケアルガ
+Curaga</x:v>
       </x:c>
       <x:c r="B42" s="42" t="str">
         <x:v>中恢复
-ケアルラ</x:v>
+ケアルラ
+Cura</x:v>
       </x:c>
       <x:c r="C42" s="43" t="str">
         <x:v>恢复
-ケアル</x:v>
+ケアル
+Cure</x:v>
       </x:c>
       <x:c r="D42" s="7" t="s">
         <x:v>26</x:v>
@@ -4126,12 +4407,13 @@
       </x:c>
       <x:c r="H42" s="30"/>
     </x:row>
-    <x:row r="43" ht="40" customHeight="1">
+    <x:row r="43" ht="56" customHeight="1">
       <x:c r="A43" s="34"/>
       <x:c r="B43" s="34"/>
       <x:c r="C43" s="43" t="str">
         <x:v>中恢复
-ケアルラ</x:v>
+ケアルラ
+Cura</x:v>
       </x:c>
       <x:c r="D43" s="7" t="s">
         <x:v>14</x:v>
@@ -4141,18 +4423,21 @@
       <x:c r="G43" s="29"/>
       <x:c r="H43" s="30"/>
     </x:row>
-    <x:row r="44" ht="40" customHeight="1">
+    <x:row r="44" ht="56" customHeight="1">
       <x:c r="A44" s="42" t="str">
         <x:v>爆破护盾
-デトネシールド</x:v>
+デトネシールド
+Mine Shield</x:v>
       </x:c>
       <x:c r="B44" s="43" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="C44" s="43" t="str">
         <x:v>零重力
-ゼログラビデ</x:v>
+ゼログラビデ
+Zero Gravity</x:v>
       </x:c>
       <x:c r="D44" s="7" t="s">
         <x:v>16</x:v>
@@ -4168,15 +4453,17 @@
       </x:c>
       <x:c r="H44" s="30"/>
     </x:row>
-    <x:row r="45" ht="40" customHeight="1">
+    <x:row r="45" ht="56" customHeight="1">
       <x:c r="A45" s="33"/>
       <x:c r="B45" s="43" t="str">
         <x:v>点燃
-スナイプバーニング</x:v>
+スナイプバーニング
+Ignite</x:v>
       </x:c>
       <x:c r="C45" s="43" t="str">
         <x:v>停止
-ストップ</x:v>
+ストップ
+Stop</x:v>
       </x:c>
       <x:c r="D45" s="7" t="s">
         <x:v>13</x:v>
@@ -4186,15 +4473,17 @@
       <x:c r="G45" s="29"/>
       <x:c r="H45" s="30"/>
     </x:row>
-    <x:row r="46" ht="40" customHeight="1">
+    <x:row r="46" ht="56" customHeight="1">
       <x:c r="A46" s="33"/>
       <x:c r="B46" s="42" t="str">
         <x:v>反射格挡
-リフレクトガード</x:v>
+リフレクトガード
+Block</x:v>
       </x:c>
       <x:c r="C46" s="43" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="D46" s="7" t="s">
         <x:v>15</x:v>
@@ -4206,12 +4495,13 @@
       </x:c>
       <x:c r="H46" s="30"/>
     </x:row>
-    <x:row r="47" ht="40" customHeight="1">
+    <x:row r="47" ht="56" customHeight="1">
       <x:c r="A47" s="34"/>
       <x:c r="B47" s="34"/>
       <x:c r="C47" s="43" t="str">
         <x:v>中停止
-ストプラ</x:v>
+ストプラ
+Stopra</x:v>
       </x:c>
       <x:c r="D47" s="7" t="s">
         <x:v>26</x:v>
@@ -4221,18 +4511,21 @@
       <x:c r="G47" s="29"/>
       <x:c r="H47" s="30"/>
     </x:row>
-    <x:row r="48" ht="40" customHeight="1">
+    <x:row r="48" ht="56" customHeight="1">
       <x:c r="A48" s="42" t="str">
         <x:v>爆破方阵
-デトネスクウェア</x:v>
+デトネスクウェア
+Mine Square</x:v>
       </x:c>
       <x:c r="B48" s="43" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="C48" s="43" t="str">
         <x:v>停止
-ストップ</x:v>
+ストップ
+Stop</x:v>
       </x:c>
       <x:c r="D48" s="7" t="s">
         <x:v>16</x:v>
@@ -4248,15 +4541,17 @@
       </x:c>
       <x:c r="H48" s="30"/>
     </x:row>
-    <x:row r="49" ht="40" customHeight="1">
+    <x:row r="49" ht="56" customHeight="1">
       <x:c r="A49" s="33"/>
       <x:c r="B49" s="43" t="str">
         <x:v>中劲风
-エアロラ</x:v>
+エアロラ
+Aerora</x:v>
       </x:c>
       <x:c r="C49" s="43" t="str">
         <x:v>点燃
-スナイプバーニング</x:v>
+スナイプバーニング
+Ignite</x:v>
       </x:c>
       <x:c r="D49" s="7" t="s">
         <x:v>13</x:v>
@@ -4266,15 +4561,17 @@
       <x:c r="G49" s="29"/>
       <x:c r="H49" s="30"/>
     </x:row>
-    <x:row r="50" ht="40" customHeight="1">
+    <x:row r="50" ht="56" customHeight="1">
       <x:c r="A50" s="33"/>
       <x:c r="B50" s="42" t="str">
         <x:v>反射
-リフレク</x:v>
+リフレク
+Barrier</x:v>
       </x:c>
       <x:c r="C50" s="43" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="D50" s="7" t="s">
         <x:v>15</x:v>
@@ -4288,12 +4585,13 @@
       <x:c r="G50" s="29"/>
       <x:c r="H50" s="30"/>
     </x:row>
-    <x:row r="51" ht="40" customHeight="1">
+    <x:row r="51" ht="56" customHeight="1">
       <x:c r="A51" s="34"/>
       <x:c r="B51" s="34"/>
       <x:c r="C51" s="43" t="str">
         <x:v>中停止
-ストプラ</x:v>
+ストプラ
+Stopra</x:v>
       </x:c>
       <x:c r="D51" s="7" t="s">
         <x:v>26</x:v>
@@ -4303,18 +4601,21 @@
       <x:c r="G51" s="29"/>
       <x:c r="H51" s="30"/>
     </x:row>
-    <x:row r="52" ht="40" customHeight="1">
+    <x:row r="52" ht="56" customHeight="1">
       <x:c r="A52" s="42" t="str">
         <x:v>爆破追踪
-デトネチェイサー</x:v>
+デトネチェイサー
+Seeker Mine</x:v>
       </x:c>
       <x:c r="B52" s="42" t="str">
         <x:v>爆破护盾
-デトネシールド</x:v>
+デトネシールド
+Mine Shield</x:v>
       </x:c>
       <x:c r="C52" s="43" t="str">
         <x:v>爆破方阵
-デトネスクウェア</x:v>
+デトネスクウェア
+Mine Square</x:v>
       </x:c>
       <x:c r="D52" s="7" t="s">
         <x:v>17</x:v>
@@ -4330,12 +4631,13 @@
       </x:c>
       <x:c r="H52" s="30"/>
     </x:row>
-    <x:row r="53" ht="40" customHeight="1">
+    <x:row r="53" ht="56" customHeight="1">
       <x:c r="A53" s="33"/>
       <x:c r="B53" s="34"/>
       <x:c r="C53" s="42" t="str">
         <x:v>大磁力
-マグネガ</x:v>
+マグネガ
+Magnega</x:v>
       </x:c>
       <x:c r="D53" s="7" t="s">
         <x:v>15</x:v>
@@ -4345,11 +4647,12 @@
       <x:c r="G53" s="29"/>
       <x:c r="H53" s="30"/>
     </x:row>
-    <x:row r="54" ht="40" customHeight="1">
+    <x:row r="54" ht="56" customHeight="1">
       <x:c r="A54" s="34"/>
       <x:c r="B54" s="43" t="str">
         <x:v>爆破方阵
-デトネスクウェア</x:v>
+デトネスクウェア
+Mine Square</x:v>
       </x:c>
       <x:c r="C54" s="34"/>
       <x:c r="D54" s="7" t="s">
@@ -4360,18 +4663,21 @@
       <x:c r="G54" s="29"/>
       <x:c r="H54" s="30"/>
     </x:row>
-    <x:row r="55" ht="40" customHeight="1">
+    <x:row r="55" ht="56" customHeight="1">
       <x:c r="A55" s="42" t="str">
         <x:v>中零重力
-ゼログラビラ</x:v>
+ゼログラビラ
+Zero Gravira</x:v>
       </x:c>
       <x:c r="B55" s="42" t="str">
         <x:v>零重力
-ゼログラビデ</x:v>
+ゼログラビデ
+Zero Gravity</x:v>
       </x:c>
       <x:c r="C55" s="43" t="str">
         <x:v>雷电
-サンダー</x:v>
+サンダー
+Thunder</x:v>
       </x:c>
       <x:c r="D55" s="7" t="s">
         <x:v>19</x:v>
@@ -4387,12 +4693,13 @@
       </x:c>
       <x:c r="H55" s="30"/>
     </x:row>
-    <x:row r="56" ht="40" customHeight="1">
+    <x:row r="56" ht="56" customHeight="1">
       <x:c r="A56" s="33"/>
       <x:c r="B56" s="34"/>
       <x:c r="C56" s="43" t="str">
         <x:v>零重力
-ゼログラビデ</x:v>
+ゼログラビデ
+Zero Gravity</x:v>
       </x:c>
       <x:c r="D56" s="7" t="s">
         <x:v>26</x:v>
@@ -4402,15 +4709,17 @@
       <x:c r="G56" s="29"/>
       <x:c r="H56" s="30"/>
     </x:row>
-    <x:row r="57" ht="40" customHeight="1">
+    <x:row r="57" ht="56" customHeight="1">
       <x:c r="A57" s="34"/>
       <x:c r="B57" s="43" t="str">
         <x:v>磁力
-マグネ</x:v>
+マグネ
+Magnet</x:v>
       </x:c>
       <x:c r="C57" s="43" t="str">
         <x:v>劲风
-エアロ</x:v>
+エアロ
+Aero</x:v>
       </x:c>
       <x:c r="D57" s="7" t="s">
         <x:v>11</x:v>
@@ -4420,18 +4729,21 @@
       <x:c r="G57" s="29"/>
       <x:c r="H57" s="30"/>
     </x:row>
-    <x:row r="58" ht="40" customHeight="1">
+    <x:row r="58" ht="56" customHeight="1">
       <x:c r="A58" s="42" t="str">
         <x:v>大零重力
-ゼログラビガ</x:v>
+ゼログラビガ
+Zero Graviga</x:v>
       </x:c>
       <x:c r="B58" s="42" t="str">
         <x:v>中零重力
-ゼログラビラ</x:v>
+ゼログラビラ
+Zero Gravira</x:v>
       </x:c>
       <x:c r="C58" s="43" t="str">
         <x:v>零重力
-ゼログラビデ</x:v>
+ゼログラビデ
+Zero Gravity</x:v>
       </x:c>
       <x:c r="D58" s="7" t="s">
         <x:v>26</x:v>
@@ -4447,12 +4759,13 @@
       </x:c>
       <x:c r="H58" s="30"/>
     </x:row>
-    <x:row r="59" ht="40" customHeight="1">
+    <x:row r="59" ht="56" customHeight="1">
       <x:c r="A59" s="33"/>
       <x:c r="B59" s="33"/>
       <x:c r="C59" s="43" t="str">
         <x:v>中零重力
-ゼログラビラ</x:v>
+ゼログラビラ
+Zero Gravira</x:v>
       </x:c>
       <x:c r="D59" s="7" t="s">
         <x:v>14</x:v>
@@ -4462,12 +4775,13 @@
       <x:c r="G59" s="29"/>
       <x:c r="H59" s="30"/>
     </x:row>
-    <x:row r="60" ht="40" customHeight="1">
+    <x:row r="60" ht="56" customHeight="1">
       <x:c r="A60" s="34"/>
       <x:c r="B60" s="34"/>
       <x:c r="C60" s="43" t="str">
         <x:v>中雷电
-サンダラ</x:v>
+サンダラ
+Thundara</x:v>
       </x:c>
       <x:c r="D60" s="7" t="s">
         <x:v>19</x:v>
@@ -4477,18 +4791,21 @@
       <x:c r="G60" s="29"/>
       <x:c r="H60" s="30"/>
     </x:row>
-    <x:row r="61" ht="40" customHeight="1">
+    <x:row r="61" ht="56" customHeight="1">
       <x:c r="A61" s="42" t="str">
         <x:v>中磁力
-マグネラ</x:v>
+マグネラ
+Magnera</x:v>
       </x:c>
       <x:c r="B61" s="42" t="str">
         <x:v>磁力
-マグネ</x:v>
+マグネ
+Magnet</x:v>
       </x:c>
       <x:c r="C61" s="43" t="str">
         <x:v>雷电
-サンダー</x:v>
+サンダー
+Thunder</x:v>
       </x:c>
       <x:c r="D61" s="7" t="s">
         <x:v>19</x:v>
@@ -4504,12 +4821,13 @@
       </x:c>
       <x:c r="H61" s="30"/>
     </x:row>
-    <x:row r="62" ht="40" customHeight="1">
+    <x:row r="62" ht="56" customHeight="1">
       <x:c r="A62" s="33"/>
       <x:c r="B62" s="33"/>
       <x:c r="C62" s="43" t="str">
         <x:v>磁力
-マグネ</x:v>
+マグネ
+Magnet</x:v>
       </x:c>
       <x:c r="D62" s="7" t="s">
         <x:v>26</x:v>
@@ -4519,12 +4837,13 @@
       <x:c r="G62" s="29"/>
       <x:c r="H62" s="30"/>
     </x:row>
-    <x:row r="63" ht="40" customHeight="1">
+    <x:row r="63" ht="56" customHeight="1">
       <x:c r="A63" s="34"/>
       <x:c r="B63" s="34"/>
       <x:c r="C63" s="43" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="D63" s="7" t="s">
         <x:v>10</x:v>
@@ -4534,18 +4853,21 @@
       <x:c r="G63" s="29"/>
       <x:c r="H63" s="30"/>
     </x:row>
-    <x:row r="64" ht="40" customHeight="1">
+    <x:row r="64" ht="56" customHeight="1">
       <x:c r="A64" s="42" t="str">
         <x:v>大磁力
-マグネガ</x:v>
+マグネガ
+Magnega</x:v>
       </x:c>
       <x:c r="B64" s="42" t="str">
         <x:v>中磁力
-マグネラ</x:v>
+マグネラ
+Magnera</x:v>
       </x:c>
       <x:c r="C64" s="43" t="str">
         <x:v>磁力
-マグネ</x:v>
+マグネ
+Magnet</x:v>
       </x:c>
       <x:c r="D64" s="7" t="s">
         <x:v>19</x:v>
@@ -4561,12 +4883,13 @@
       </x:c>
       <x:c r="H64" s="30"/>
     </x:row>
-    <x:row r="65" ht="40" customHeight="1">
+    <x:row r="65" ht="56" customHeight="1">
       <x:c r="A65" s="34"/>
       <x:c r="B65" s="34"/>
       <x:c r="C65" s="43" t="str">
         <x:v>中磁力
-マグネラ</x:v>
+マグネラ
+Magnera</x:v>
       </x:c>
       <x:c r="D65" s="7" t="s">
         <x:v>20</x:v>
@@ -4576,18 +4899,21 @@
       <x:c r="G65" s="29"/>
       <x:c r="H65" s="30"/>
     </x:row>
-    <x:row r="66" ht="40" customHeight="1">
+    <x:row r="66" ht="56" customHeight="1">
       <x:c r="A66" s="42" t="str">
         <x:v>金钱磁力
-マニーマグネ</x:v>
+マニーマグネ
+Munny Magnet</x:v>
       </x:c>
       <x:c r="B66" s="42" t="str">
         <x:v>中磁力
-マグネラ</x:v>
+マグネラ
+Magnera</x:v>
       </x:c>
       <x:c r="C66" s="43" t="str">
         <x:v>中雷电
-サンダラ</x:v>
+サンダラ
+Thundara</x:v>
       </x:c>
       <x:c r="D66" s="7" t="s">
         <x:v>19</x:v>
@@ -4603,12 +4929,13 @@
       </x:c>
       <x:c r="H66" s="30"/>
     </x:row>
-    <x:row r="67" ht="40" customHeight="1">
+    <x:row r="67" ht="56" customHeight="1">
       <x:c r="A67" s="34"/>
       <x:c r="B67" s="34"/>
       <x:c r="C67" s="43" t="str">
         <x:v>祈愿之刃
-ウィッシュブレード</x:v>
+ウィッシュブレード
+Wishing Edge</x:v>
       </x:c>
       <x:c r="D67" s="7" t="s">
         <x:v>10</x:v>
@@ -4618,18 +4945,21 @@
       <x:c r="G67" s="29"/>
       <x:c r="H67" s="30"/>
     </x:row>
-    <x:row r="68" ht="40" customHeight="1">
+    <x:row r="68" ht="56" customHeight="1">
       <x:c r="A68" s="42" t="str">
         <x:v>能量磁力
-エナジーマグネ</x:v>
+エナジーマグネ
+Energy Magnet</x:v>
       </x:c>
       <x:c r="B68" s="42" t="str">
         <x:v>中磁力
-マグネラ</x:v>
+マグネラ
+Magnera</x:v>
       </x:c>
       <x:c r="C68" s="43" t="str">
         <x:v>恢复
-ケアル</x:v>
+ケアル
+Cure</x:v>
       </x:c>
       <x:c r="D68" s="7" t="s">
         <x:v>26</x:v>
@@ -4645,12 +4975,13 @@
       </x:c>
       <x:c r="H68" s="30"/>
     </x:row>
-    <x:row r="69" ht="40" customHeight="1">
+    <x:row r="69" ht="56" customHeight="1">
       <x:c r="A69" s="34"/>
       <x:c r="B69" s="34"/>
       <x:c r="C69" s="43" t="str">
         <x:v>中恢复
-ケアルラ</x:v>
+ケアルラ
+Cura</x:v>
       </x:c>
       <x:c r="D69" s="7" t="s">
         <x:v>14</x:v>
@@ -4660,18 +4991,21 @@
       <x:c r="G69" s="29"/>
       <x:c r="H69" s="30"/>
     </x:row>
-    <x:row r="70" ht="40" customHeight="1">
+    <x:row r="70" ht="56" customHeight="1">
       <x:c r="A70" s="42" t="str">
         <x:v>D-Link磁力
-Ｄリンクマグネ</x:v>
+Ｄリンクマグネ
+D-Link Magnet</x:v>
       </x:c>
       <x:c r="B70" s="42" t="str">
         <x:v>中磁力
-マグネラ</x:v>
+マグネラ
+Magnera</x:v>
       </x:c>
       <x:c r="C70" s="43" t="str">
         <x:v>中零重力
-ゼログラビラ</x:v>
+ゼログラビラ
+Zero Gravira</x:v>
       </x:c>
       <x:c r="D70" s="7" t="s">
         <x:v>22</x:v>
@@ -4687,12 +5021,13 @@
       </x:c>
       <x:c r="H70" s="30"/>
     </x:row>
-    <x:row r="71" ht="40" customHeight="1">
+    <x:row r="71" ht="56" customHeight="1">
       <x:c r="A71" s="34"/>
       <x:c r="B71" s="34"/>
       <x:c r="C71" s="43" t="str">
         <x:v>中停止
-ストプラ</x:v>
+ストプラ
+Stopra</x:v>
       </x:c>
       <x:c r="D71" s="7" t="s">
         <x:v>19</x:v>
@@ -4702,18 +5037,21 @@
       <x:c r="G71" s="29"/>
       <x:c r="H71" s="30"/>
     </x:row>
-    <x:row r="72" ht="40" customHeight="1">
+    <x:row r="72" ht="56" customHeight="1">
       <x:c r="A72" s="42" t="str">
         <x:v>中劲风
-エアロラ</x:v>
+エアロラ
+Aerora</x:v>
       </x:c>
       <x:c r="B72" s="42" t="str">
         <x:v>劲风
-エアロ</x:v>
+エアロ
+Aero</x:v>
       </x:c>
       <x:c r="C72" s="43" t="str">
         <x:v>雷电
-サンダー</x:v>
+サンダー
+Thunder</x:v>
       </x:c>
       <x:c r="D72" s="7" t="s">
         <x:v>19</x:v>
@@ -4729,12 +5067,13 @@
       </x:c>
       <x:c r="H72" s="30"/>
     </x:row>
-    <x:row r="73" ht="40" customHeight="1">
+    <x:row r="73" ht="56" customHeight="1">
       <x:c r="A73" s="33"/>
       <x:c r="B73" s="33"/>
       <x:c r="C73" s="43" t="str">
         <x:v>劲风
-エアロ</x:v>
+エアロ
+Aero</x:v>
       </x:c>
       <x:c r="D73" s="7" t="s">
         <x:v>24</x:v>
@@ -4744,12 +5083,13 @@
       <x:c r="G73" s="29"/>
       <x:c r="H73" s="30"/>
     </x:row>
-    <x:row r="74" ht="40" customHeight="1">
+    <x:row r="74" ht="56" customHeight="1">
       <x:c r="A74" s="34"/>
       <x:c r="B74" s="34"/>
       <x:c r="C74" s="43" t="str">
         <x:v>空中破击
-エリアルブレイク</x:v>
+エリアルブレイク
+Quick Blitz</x:v>
       </x:c>
       <x:c r="D74" s="7" t="s">
         <x:v>23</x:v>
@@ -4759,18 +5099,21 @@
       <x:c r="G74" s="29"/>
       <x:c r="H74" s="30"/>
     </x:row>
-    <x:row r="75" ht="40" customHeight="1">
+    <x:row r="75" ht="56" customHeight="1">
       <x:c r="A75" s="42" t="str">
         <x:v>大劲风
-エアロガ</x:v>
+エアロガ
+Aeroga</x:v>
       </x:c>
       <x:c r="B75" s="42" t="str">
         <x:v>中劲风
-エアロラ</x:v>
+エアロラ
+Aerora</x:v>
       </x:c>
       <x:c r="C75" s="43" t="str">
         <x:v>劲风
-エアロ</x:v>
+エアロ
+Aero</x:v>
       </x:c>
       <x:c r="D75" s="7" t="s">
         <x:v>26</x:v>
@@ -4786,12 +5129,13 @@
       </x:c>
       <x:c r="H75" s="30"/>
     </x:row>
-    <x:row r="76" ht="40" customHeight="1">
+    <x:row r="76" ht="56" customHeight="1">
       <x:c r="A76" s="33"/>
       <x:c r="B76" s="33"/>
       <x:c r="C76" s="43" t="str">
         <x:v>中劲风
-エアロラ</x:v>
+エアロラ
+Aerora</x:v>
       </x:c>
       <x:c r="D76" s="7" t="s">
         <x:v>14</x:v>
@@ -4801,12 +5145,13 @@
       <x:c r="G76" s="29"/>
       <x:c r="H76" s="30"/>
     </x:row>
-    <x:row r="77" ht="40" customHeight="1">
+    <x:row r="77" ht="56" customHeight="1">
       <x:c r="A77" s="34"/>
       <x:c r="B77" s="34"/>
       <x:c r="C77" s="43" t="str">
         <x:v>空中破击
-エリアルブレイク</x:v>
+エリアルブレイク
+Quick Blitz</x:v>
       </x:c>
       <x:c r="D77" s="7" t="s">
         <x:v>8</x:v>
@@ -4816,18 +5161,21 @@
       <x:c r="G77" s="29"/>
       <x:c r="H77" s="30"/>
     </x:row>
-    <x:row r="78" ht="40" customHeight="1">
+    <x:row r="78" ht="56" customHeight="1">
       <x:c r="A78" s="43" t="str">
         <x:v>神圣
-ホーリー</x:v>
+ホーリー
+Faith</x:v>
       </x:c>
       <x:c r="B78" s="43" t="str">
         <x:v>疾风飞掷
-ウインドレイド</x:v>
+ウインドレイド
+Wind Raid</x:v>
       </x:c>
       <x:c r="C78" s="43" t="str">
         <x:v>休息时间
-ブレイクタイム</x:v>
+ブレイクタイム
+Break Time</x:v>
       </x:c>
       <x:c r="D78" s="7" t="s">
         <x:v>14</x:v>
@@ -4843,18 +5191,21 @@
       </x:c>
       <x:c r="H78" s="7"/>
     </x:row>
-    <x:row r="79" ht="40" customHeight="1">
+    <x:row r="79" ht="56" customHeight="1">
       <x:c r="A79" s="42" t="str">
         <x:v>冰冻
-フリーズ</x:v>
+フリーズ
+Deep Freeze</x:v>
       </x:c>
       <x:c r="B79" s="42" t="str">
         <x:v>大冰雪
-ブリザガ</x:v>
+ブリザガ
+Blizzaga</x:v>
       </x:c>
       <x:c r="C79" s="43" t="str">
         <x:v>冰冻飞掷
-フリーズレイド</x:v>
+フリーズレイド
+Freeze Raid</x:v>
       </x:c>
       <x:c r="D79" s="7" t="s">
         <x:v>23</x:v>
@@ -4870,12 +5221,13 @@
       </x:c>
       <x:c r="H79" s="30"/>
     </x:row>
-    <x:row r="80" ht="40" customHeight="1">
+    <x:row r="80" ht="56" customHeight="1">
       <x:c r="A80" s="33"/>
       <x:c r="B80" s="33"/>
       <x:c r="C80" s="43" t="str">
         <x:v>束缚强击
-バインドストライク</x:v>
+バインドストライク
+Binding Strike</x:v>
       </x:c>
       <x:c r="D80" s="7" t="s">
         <x:v>25</x:v>
@@ -4885,12 +5237,13 @@
       <x:c r="G80" s="29"/>
       <x:c r="H80" s="30"/>
     </x:row>
-    <x:row r="81" ht="40" customHeight="1">
+    <x:row r="81" ht="56" customHeight="1">
       <x:c r="A81" s="34"/>
       <x:c r="B81" s="34"/>
       <x:c r="C81" s="43" t="str">
         <x:v>三重大冰雪
-トリプルブリザガ</x:v>
+トリプルブリザガ
+Triple Blizzaga</x:v>
       </x:c>
       <x:c r="D81" s="7" t="s">
         <x:v>18</x:v>
@@ -4904,18 +5257,21 @@
       <x:c r="G81" s="29"/>
       <x:c r="H81" s="30"/>
     </x:row>
-    <x:row r="82" ht="40" customHeight="1">
+    <x:row r="82" ht="56" customHeight="1">
       <x:c r="A82" s="42" t="str">
         <x:v>冰川战艺
-グレイシャルアーツ</x:v>
+グレイシャルアーツ
+Glacier</x:v>
       </x:c>
       <x:c r="B82" s="42" t="str">
         <x:v>冰冻
-フリーズ</x:v>
+フリーズ
+Deep Freeze</x:v>
       </x:c>
       <x:c r="C82" s="43" t="str">
         <x:v>大冰雪
-ブリザガ</x:v>
+ブリザガ
+Blizzaga</x:v>
       </x:c>
       <x:c r="D82" s="7" t="s">
         <x:v>24</x:v>
@@ -4931,12 +5287,13 @@
       </x:c>
       <x:c r="H82" s="30"/>
     </x:row>
-    <x:row r="83" ht="40" customHeight="1">
+    <x:row r="83" ht="56" customHeight="1">
       <x:c r="A83" s="34"/>
       <x:c r="B83" s="34"/>
       <x:c r="C83" s="43" t="str">
         <x:v>三重大冰雪
-トリプルブリザガ</x:v>
+トリプルブリザガ
+Triple Blizzaga</x:v>
       </x:c>
       <x:c r="D83" s="7" t="s">
         <x:v>18</x:v>
@@ -4946,18 +5303,21 @@
       <x:c r="G83" s="29"/>
       <x:c r="H83" s="30"/>
     </x:row>
-    <x:row r="84" ht="40" customHeight="1">
+    <x:row r="84" ht="56" customHeight="1">
       <x:c r="A84" s="42" t="str">
         <x:v>寒冰齐射
-アイスバラージュ</x:v>
+アイスバラージュ
+Ice Barrage</x:v>
       </x:c>
       <x:c r="B84" s="42" t="str">
         <x:v>大冰雪
-ブリザガ</x:v>
+ブリザガ
+Blizzaga</x:v>
       </x:c>
       <x:c r="C84" s="43" t="str">
         <x:v>爆破护盾
-デトネシールド</x:v>
+デトネシールド
+Mine Shield</x:v>
       </x:c>
       <x:c r="D84" s="7" t="s">
         <x:v>18</x:v>
@@ -4973,12 +5333,13 @@
       </x:c>
       <x:c r="H84" s="30"/>
     </x:row>
-    <x:row r="85" ht="40" customHeight="1">
+    <x:row r="85" ht="56" customHeight="1">
       <x:c r="A85" s="34"/>
       <x:c r="B85" s="34"/>
       <x:c r="C85" s="43" t="str">
         <x:v>爆破方阵
-デトネスクウェア</x:v>
+デトネスクウェア
+Mine Square</x:v>
       </x:c>
       <x:c r="D85" s="7" t="s">
         <x:v>25</x:v>
@@ -4988,18 +5349,21 @@
       <x:c r="G85" s="29"/>
       <x:c r="H85" s="30"/>
     </x:row>
-    <x:row r="86" ht="40" customHeight="1">
+    <x:row r="86" ht="56" customHeight="1">
       <x:c r="A86" s="42" t="str">
         <x:v>大火焰爆发
-ファイガバースト</x:v>
+ファイガバースト
+Firaga Burst</x:v>
       </x:c>
       <x:c r="B86" s="42" t="str">
         <x:v>大火焰
-ファイガ</x:v>
+ファイガ
+Firaga</x:v>
       </x:c>
       <x:c r="C86" s="43" t="str">
         <x:v>中劲风
-エアロラ</x:v>
+エアロラ
+Aerora</x:v>
       </x:c>
       <x:c r="D86" s="7" t="s">
         <x:v>16</x:v>
@@ -5017,12 +5381,13 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="40" customHeight="1">
+    <x:row r="87" ht="56" customHeight="1">
       <x:c r="A87" s="33"/>
       <x:c r="B87" s="33"/>
       <x:c r="C87" s="43" t="str">
         <x:v>中停止
-ストプラ</x:v>
+ストプラ
+Stopra</x:v>
       </x:c>
       <x:c r="D87" s="7" t="s">
         <x:v>13</x:v>
@@ -5032,12 +5397,13 @@
       <x:c r="G87" s="29"/>
       <x:c r="H87" s="30"/>
     </x:row>
-    <x:row r="88" ht="40" customHeight="1">
+    <x:row r="88" ht="56" customHeight="1">
       <x:c r="A88" s="33"/>
       <x:c r="B88" s="33"/>
       <x:c r="C88" s="43" t="str">
         <x:v>迟缓
-スロウ</x:v>
+スロウ
+Slow</x:v>
       </x:c>
       <x:c r="D88" s="7" t="s">
         <x:v>16</x:v>
@@ -5047,12 +5413,13 @@
       <x:c r="G88" s="29"/>
       <x:c r="H88" s="30"/>
     </x:row>
-    <x:row r="89" ht="40" customHeight="1">
+    <x:row r="89" ht="56" customHeight="1">
       <x:c r="A89" s="33"/>
       <x:c r="B89" s="34"/>
       <x:c r="C89" s="42" t="str">
         <x:v>大劲风
-エアロガ</x:v>
+エアロガ
+Aeroga</x:v>
       </x:c>
       <x:c r="D89" s="7" t="s">
         <x:v>17</x:v>
@@ -5062,11 +5429,12 @@
       <x:c r="G89" s="29"/>
       <x:c r="H89" s="30"/>
     </x:row>
-    <x:row r="90" ht="40" customHeight="1">
+    <x:row r="90" ht="56" customHeight="1">
       <x:c r="A90" s="34"/>
       <x:c r="B90" s="43" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="C90" s="34"/>
       <x:c r="D90" s="7" t="s">
@@ -5077,18 +5445,21 @@
       <x:c r="G90" s="29"/>
       <x:c r="H90" s="30"/>
     </x:row>
-    <x:row r="91" ht="40" customHeight="1">
+    <x:row r="91" ht="56" customHeight="1">
       <x:c r="A91" s="42" t="str">
         <x:v>怒焰风暴
-レイジングストーム</x:v>
+レイジングストーム
+Raging Storm</x:v>
       </x:c>
       <x:c r="B91" s="43" t="str">
         <x:v>爆裂大火焰
-クラッカーファイガ</x:v>
+クラッカーファイガ
+Fission Firaga</x:v>
       </x:c>
       <x:c r="C91" s="43" t="str">
         <x:v>大火焰爆发
-ファイガバースト</x:v>
+ファイガバースト
+Firaga Burst</x:v>
       </x:c>
       <x:c r="D91" s="7" t="s">
         <x:v>17</x:v>
@@ -5104,15 +5475,17 @@
       </x:c>
       <x:c r="H91" s="7"/>
     </x:row>
-    <x:row r="92" ht="40" customHeight="1">
+    <x:row r="92" ht="56" customHeight="1">
       <x:c r="A92" s="33"/>
       <x:c r="B92" s="42" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="C92" s="43" t="str">
         <x:v>火焰
-ファイア</x:v>
+ファイア
+Fire</x:v>
       </x:c>
       <x:c r="D92" s="7" t="s">
         <x:v>16</x:v>
@@ -5124,12 +5497,13 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="40" customHeight="1">
+    <x:row r="93" ht="56" customHeight="1">
       <x:c r="A93" s="33"/>
       <x:c r="B93" s="34"/>
       <x:c r="C93" s="43" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="D93" s="7" t="s">
         <x:v>17</x:v>
@@ -5139,15 +5513,17 @@
       <x:c r="G93" s="29"/>
       <x:c r="H93" s="30"/>
     </x:row>
-    <x:row r="94" ht="40" customHeight="1">
+    <x:row r="94" ht="56" customHeight="1">
       <x:c r="A94" s="34"/>
       <x:c r="B94" s="43" t="str">
         <x:v>最终破击
-ファイナルブレイク</x:v>
+ファイナルブレイク
+Blitz</x:v>
       </x:c>
       <x:c r="C94" s="43" t="str">
         <x:v>大火焰
-ファイガ</x:v>
+ファイガ
+Firaga</x:v>
       </x:c>
       <x:c r="D94" s="7" t="s">
         <x:v>13</x:v>
@@ -5157,18 +5533,21 @@
       <x:c r="G94" s="29"/>
       <x:c r="H94" s="30"/>
     </x:row>
-    <x:row r="95" ht="40" customHeight="1">
+    <x:row r="95" ht="56" customHeight="1">
       <x:c r="A95" s="43" t="str">
         <x:v>百万核爆
-メガフレア</x:v>
+メガフレア
+Mega Flare</x:v>
       </x:c>
       <x:c r="B95" s="43" t="str">
         <x:v>爆裂大火焰
-クラッカーファイガ</x:v>
+クラッカーファイガ
+Fission Firaga</x:v>
       </x:c>
       <x:c r="C95" s="43" t="str">
         <x:v>蔓延火焰
-バレッジファイア</x:v>
+バレッジファイア
+Crawling Fire</x:v>
       </x:c>
       <x:c r="D95" s="7" t="s">
         <x:v>17</x:v>
@@ -5184,18 +5563,21 @@
       </x:c>
       <x:c r="H95" s="7"/>
     </x:row>
-    <x:row r="96" ht="40" customHeight="1">
+    <x:row r="96" ht="56" customHeight="1">
       <x:c r="A96" s="42" t="str">
         <x:v>龙卷
-トルネド</x:v>
+トルネド
+Tornado</x:v>
       </x:c>
       <x:c r="B96" s="43" t="str">
         <x:v>大劲风
-エアロガ</x:v>
+エアロガ
+Aeroga</x:v>
       </x:c>
       <x:c r="C96" s="43" t="str">
         <x:v>大磁力
-マグネガ</x:v>
+マグネガ
+Magnega</x:v>
       </x:c>
       <x:c r="D96" s="7" t="s">
         <x:v>14</x:v>
@@ -5211,15 +5593,17 @@
       </x:c>
       <x:c r="H96" s="7"/>
     </x:row>
-    <x:row r="97" ht="40" customHeight="1">
+    <x:row r="97" ht="56" customHeight="1">
       <x:c r="A97" s="33"/>
       <x:c r="B97" s="43" t="str">
         <x:v>中劲风
-エアロラ</x:v>
+エアロラ
+Aerora</x:v>
       </x:c>
       <x:c r="C97" s="42" t="str">
         <x:v>中劲风
-エアロラ</x:v>
+エアロラ
+Aerora</x:v>
       </x:c>
       <x:c r="D97" s="7" t="s">
         <x:v>14</x:v>
@@ -5231,11 +5615,12 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="40" customHeight="1">
+    <x:row r="98" ht="56" customHeight="1">
       <x:c r="A98" s="33"/>
       <x:c r="B98" s="42" t="str">
         <x:v>劲风
-エアロ</x:v>
+エアロ
+Aero</x:v>
       </x:c>
       <x:c r="C98" s="34"/>
       <x:c r="D98" s="7" t="s">
@@ -5246,12 +5631,13 @@
       <x:c r="G98" s="29"/>
       <x:c r="H98" s="30"/>
     </x:row>
-    <x:row r="99" ht="40" customHeight="1">
+    <x:row r="99" ht="56" customHeight="1">
       <x:c r="A99" s="33"/>
       <x:c r="B99" s="33"/>
       <x:c r="C99" s="43" t="str">
         <x:v>劲风
-エアロ</x:v>
+エアロ
+Aero</x:v>
       </x:c>
       <x:c r="D99" s="7" t="s">
         <x:v>24</x:v>
@@ -5261,12 +5647,13 @@
       <x:c r="G99" s="29"/>
       <x:c r="H99" s="30"/>
     </x:row>
-    <x:row r="100" ht="40" customHeight="1">
+    <x:row r="100" ht="56" customHeight="1">
       <x:c r="A100" s="34"/>
       <x:c r="B100" s="34"/>
       <x:c r="C100" s="43" t="str">
         <x:v>雷电
-サンダー</x:v>
+サンダー
+Thunder</x:v>
       </x:c>
       <x:c r="D100" s="7" t="s">
         <x:v>19</x:v>
@@ -5276,18 +5663,21 @@
       <x:c r="G100" s="29"/>
       <x:c r="H100" s="30"/>
     </x:row>
-    <x:row r="101" ht="40" customHeight="1">
+    <x:row r="101" ht="56" customHeight="1">
       <x:c r="A101" s="42" t="str">
         <x:v>驱逐
-デジョン</x:v>
+デジョン
+Warp</x:v>
       </x:c>
       <x:c r="B101" s="42" t="str">
         <x:v>零重力
-ゼログラビデ</x:v>
+ゼログラビデ
+Zero Gravity</x:v>
       </x:c>
       <x:c r="C101" s="43" t="str">
         <x:v>零重力
-ゼログラビデ</x:v>
+ゼログラビデ
+Zero Gravity</x:v>
       </x:c>
       <x:c r="D101" s="7" t="s">
         <x:v>26</x:v>
@@ -5305,12 +5695,13 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="40" customHeight="1">
+    <x:row r="102" ht="56" customHeight="1">
       <x:c r="A102" s="34"/>
       <x:c r="B102" s="34"/>
       <x:c r="C102" s="43" t="str">
         <x:v>中零重力
-ゼログラビラ</x:v>
+ゼログラビラ
+Zero Gravira</x:v>
       </x:c>
       <x:c r="D102" s="7" t="s">
         <x:v>26</x:v>
@@ -5320,18 +5711,21 @@
       <x:c r="G102" s="29"/>
       <x:c r="H102" s="30"/>
     </x:row>
-    <x:row r="103" ht="40" customHeight="1">
+    <x:row r="103" ht="56" customHeight="1">
       <x:c r="A103" s="42" t="str">
         <x:v>地震
-クエイク</x:v>
+クエイク
+Quake</x:v>
       </x:c>
       <x:c r="B103" s="42" t="str">
         <x:v>残暴冲击
-ブルータルブラスト</x:v>
+ブルータルブラスト
+Brutal Blast</x:v>
       </x:c>
       <x:c r="C103" s="43" t="str">
         <x:v>大零重力
-ゼログラビガ</x:v>
+ゼログラビガ
+Zero Graviga</x:v>
       </x:c>
       <x:c r="D103" s="7" t="s">
         <x:v>17</x:v>
@@ -5347,12 +5741,13 @@
       </x:c>
       <x:c r="H103" s="30"/>
     </x:row>
-    <x:row r="104" ht="40" customHeight="1">
+    <x:row r="104" ht="56" customHeight="1">
       <x:c r="A104" s="33"/>
       <x:c r="B104" s="33"/>
       <x:c r="C104" s="43" t="str">
         <x:v>大磁力
-マグネガ</x:v>
+マグネガ
+Magnega</x:v>
       </x:c>
       <x:c r="D104" s="7" t="s">
         <x:v>15</x:v>
@@ -5362,12 +5757,13 @@
       <x:c r="G104" s="29"/>
       <x:c r="H104" s="30"/>
     </x:row>
-    <x:row r="105" ht="40" customHeight="1">
+    <x:row r="105" ht="56" customHeight="1">
       <x:c r="A105" s="33"/>
       <x:c r="B105" s="34"/>
       <x:c r="C105" s="43" t="str">
         <x:v>残暴冲击
-ブルータルブラスト</x:v>
+ブルータルブラスト
+Brutal Blast</x:v>
       </x:c>
       <x:c r="D105" s="7" t="s">
         <x:v>14</x:v>
@@ -5379,15 +5775,17 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="40" customHeight="1">
+    <x:row r="106" ht="56" customHeight="1">
       <x:c r="A106" s="33"/>
       <x:c r="B106" s="43" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="C106" s="43" t="str">
         <x:v>爆破护盾
-デトネシールド</x:v>
+デトネシールド
+Mine Shield</x:v>
       </x:c>
       <x:c r="D106" s="7" t="s">
         <x:v>8</x:v>
@@ -5397,15 +5795,17 @@
       <x:c r="G106" s="29"/>
       <x:c r="H106" s="30"/>
     </x:row>
-    <x:row r="107" ht="40" customHeight="1">
+    <x:row r="107" ht="56" customHeight="1">
       <x:c r="A107" s="34"/>
       <x:c r="B107" s="43" t="str">
         <x:v>束缚强击
-バインドストライク</x:v>
+バインドストライク
+Binding Strike</x:v>
       </x:c>
       <x:c r="C107" s="43" t="str">
         <x:v>爆破方阵
-デトネスクウェア</x:v>
+デトネスクウェア
+Mine Square</x:v>
       </x:c>
       <x:c r="D107" s="7" t="s">
         <x:v>22</x:v>
@@ -5415,18 +5815,21 @@
       <x:c r="G107" s="29"/>
       <x:c r="H107" s="30"/>
     </x:row>
-    <x:row r="108" ht="40" customHeight="1">
+    <x:row r="108" ht="56" customHeight="1">
       <x:c r="A108" s="42" t="str">
         <x:v>陨石
-メテオ</x:v>
+メテオ
+Meteor</x:v>
       </x:c>
       <x:c r="B108" s="43" t="str">
         <x:v>大地破击
-ガイアブレイク</x:v>
+ガイアブレイク
+Geo Impact</x:v>
       </x:c>
       <x:c r="C108" s="43" t="str">
         <x:v>地震
-クエイク</x:v>
+クエイク
+Quake</x:v>
       </x:c>
       <x:c r="D108" s="7" t="s">
         <x:v>17</x:v>
@@ -5442,15 +5845,17 @@
       </x:c>
       <x:c r="H108" s="7"/>
     </x:row>
-    <x:row r="109" ht="40" customHeight="1">
+    <x:row r="109" ht="56" customHeight="1">
       <x:c r="A109" s="33"/>
       <x:c r="B109" s="42" t="str">
         <x:v>残暴冲击
-ブルータルブラスト</x:v>
+ブルータルブラスト
+Brutal Blast</x:v>
       </x:c>
       <x:c r="C109" s="43" t="str">
         <x:v>大磁力
-マグネガ</x:v>
+マグネガ
+Magnega</x:v>
       </x:c>
       <x:c r="D109" s="7" t="s">
         <x:v>15</x:v>
@@ -5462,12 +5867,13 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="40" customHeight="1">
+    <x:row r="110" ht="56" customHeight="1">
       <x:c r="A110" s="34"/>
       <x:c r="B110" s="34"/>
       <x:c r="C110" s="43" t="str">
         <x:v>大零重力
-ゼログラビガ</x:v>
+ゼログラビガ
+Zero Graviga</x:v>
       </x:c>
       <x:c r="D110" s="7" t="s">
         <x:v>17</x:v>
@@ -5477,18 +5883,21 @@
       <x:c r="G110" s="29"/>
       <x:c r="H110" s="30"/>
     </x:row>
-    <x:row r="111" ht="40" customHeight="1">
+    <x:row r="111" ht="56" customHeight="1">
       <x:c r="A111" s="43" t="str">
         <x:v>大气破碎
-アトモスブレイク</x:v>
+アトモスブレイク
+Transcendence</x:v>
       </x:c>
       <x:c r="B111" s="43" t="str">
         <x:v>磁力螺旋
-マグネスパイラル</x:v>
+マグネスパイラル
+Magnet Spiral</x:v>
       </x:c>
       <x:c r="C111" s="43" t="str">
         <x:v>大零重力
-ゼログラビガ</x:v>
+ゼログラビガ
+Zero Graviga</x:v>
       </x:c>
       <x:c r="D111" s="7" t="s">
         <x:v>20</x:v>
@@ -5504,18 +5913,21 @@
       </x:c>
       <x:c r="H111" s="7"/>
     </x:row>
-    <x:row r="112" ht="40" customHeight="1">
+    <x:row r="112" ht="56" customHeight="1">
       <x:c r="A112" s="42" t="str">
         <x:v>缩小
-ミニマム</x:v>
+ミニマム
+Mini</x:v>
       </x:c>
       <x:c r="B112" s="42" t="str">
         <x:v>大磁力
-マグネガ</x:v>
+マグネガ
+Magnega</x:v>
       </x:c>
       <x:c r="C112" s="43" t="str">
         <x:v>束缚
-バインド</x:v>
+バインド
+Bind</x:v>
       </x:c>
       <x:c r="D112" s="7" t="s">
         <x:v>19</x:v>
@@ -5531,12 +5943,13 @@
       </x:c>
       <x:c r="H112" s="30"/>
     </x:row>
-    <x:row r="113" ht="40" customHeight="1">
+    <x:row r="113" ht="56" customHeight="1">
       <x:c r="A113" s="33"/>
       <x:c r="B113" s="34"/>
       <x:c r="C113" s="43" t="str">
         <x:v>大磁力
-マグネガ</x:v>
+マグネガ
+Magnega</x:v>
       </x:c>
       <x:c r="D113" s="7" t="s">
         <x:v>20</x:v>
@@ -5546,15 +5959,17 @@
       <x:c r="G113" s="29"/>
       <x:c r="H113" s="30"/>
     </x:row>
-    <x:row r="114" ht="40" customHeight="1">
+    <x:row r="114" ht="56" customHeight="1">
       <x:c r="A114" s="34"/>
       <x:c r="B114" s="43" t="str">
         <x:v>驱逐
-デジョン</x:v>
+デジョン
+Warp</x:v>
       </x:c>
       <x:c r="C114" s="43" t="str">
         <x:v>中磁力
-マグネラ</x:v>
+マグネラ
+Magnera</x:v>
       </x:c>
       <x:c r="D114" s="7" t="s">
         <x:v>14</x:v>
@@ -5568,18 +5983,21 @@
       </x:c>
       <x:c r="H114" s="30"/>
     </x:row>
-    <x:row r="115" ht="40" customHeight="1">
+    <x:row r="115" ht="56" customHeight="1">
       <x:c r="A115" s="42" t="str">
         <x:v>致盲
-ブラックアウト</x:v>
+ブラックアウト
+Blackout</x:v>
       </x:c>
       <x:c r="B115" s="43" t="str">
         <x:v>零重力
-ゼログラビデ</x:v>
+ゼログラビデ
+Zero Gravity</x:v>
       </x:c>
       <x:c r="C115" s="42" t="str">
         <x:v>混乱
-コンフュ</x:v>
+コンフュ
+Confuse</x:v>
       </x:c>
       <x:c r="D115" s="7" t="s">
         <x:v>26</x:v>
@@ -5595,11 +6013,12 @@
       </x:c>
       <x:c r="H115" s="30"/>
     </x:row>
-    <x:row r="116" ht="40" customHeight="1">
+    <x:row r="116" ht="56" customHeight="1">
       <x:c r="A116" s="33"/>
       <x:c r="B116" s="42" t="str">
         <x:v>中零重力
-ゼログラビラ</x:v>
+ゼログラビラ
+Zero Gravira</x:v>
       </x:c>
       <x:c r="C116" s="34"/>
       <x:c r="D116" s="7" t="s">
@@ -5610,12 +6029,13 @@
       <x:c r="G116" s="29"/>
       <x:c r="H116" s="30"/>
     </x:row>
-    <x:row r="117" ht="40" customHeight="1">
+    <x:row r="117" ht="56" customHeight="1">
       <x:c r="A117" s="34"/>
       <x:c r="B117" s="34"/>
       <x:c r="C117" s="43" t="str">
         <x:v>剧毒
-ポイズン</x:v>
+ポイズン
+Poison</x:v>
       </x:c>
       <x:c r="D117" s="7" t="s">
         <x:v>11</x:v>
@@ -5625,18 +6045,21 @@
       <x:c r="G117" s="29"/>
       <x:c r="H117" s="30"/>
     </x:row>
-    <x:row r="118" ht="40" customHeight="1">
+    <x:row r="118" ht="56" customHeight="1">
       <x:c r="A118" s="42" t="str">
         <x:v>点燃
-スナイプバーニング</x:v>
+スナイプバーニング
+Ignite</x:v>
       </x:c>
       <x:c r="B118" s="42" t="str">
         <x:v>束缚
-バインド</x:v>
+バインド
+Bind</x:v>
       </x:c>
       <x:c r="C118" s="43" t="str">
         <x:v>火焰
-ファイア</x:v>
+ファイア
+Fire</x:v>
       </x:c>
       <x:c r="D118" s="7" t="s">
         <x:v>16</x:v>
@@ -5652,12 +6075,13 @@
       </x:c>
       <x:c r="H118" s="30"/>
     </x:row>
-    <x:row r="119" ht="40" customHeight="1">
+    <x:row r="119" ht="56" customHeight="1">
       <x:c r="A119" s="34"/>
       <x:c r="B119" s="34"/>
       <x:c r="C119" s="43" t="str">
         <x:v>中火焰
-ファイラ</x:v>
+ファイラ
+Fira</x:v>
       </x:c>
       <x:c r="D119" s="7" t="s">
         <x:v>15</x:v>
@@ -5667,18 +6091,21 @@
       <x:c r="G119" s="29"/>
       <x:c r="H119" s="30"/>
     </x:row>
-    <x:row r="120" ht="40" customHeight="1">
+    <x:row r="120" ht="56" customHeight="1">
       <x:c r="A120" s="42" t="str">
         <x:v>中停止
-ストプラ</x:v>
+ストプラ
+Stopra</x:v>
       </x:c>
       <x:c r="B120" s="42" t="str">
         <x:v>停止
-ストップ</x:v>
+ストップ
+Stop</x:v>
       </x:c>
       <x:c r="C120" s="43" t="str">
         <x:v>停止
-ストップ</x:v>
+ストップ
+Stop</x:v>
       </x:c>
       <x:c r="D120" s="7" t="s">
         <x:v>19</x:v>
@@ -5694,12 +6121,13 @@
       </x:c>
       <x:c r="H120" s="30"/>
     </x:row>
-    <x:row r="121" ht="40" customHeight="1">
+    <x:row r="121" ht="56" customHeight="1">
       <x:c r="A121" s="33"/>
       <x:c r="B121" s="34"/>
       <x:c r="C121" s="42" t="str">
         <x:v>迟缓
-スロウ</x:v>
+スロウ
+Slow</x:v>
       </x:c>
       <x:c r="D121" s="7" t="s">
         <x:v>10</x:v>
@@ -5709,11 +6137,12 @@
       <x:c r="G121" s="29"/>
       <x:c r="H121" s="30"/>
     </x:row>
-    <x:row r="122" ht="40" customHeight="1">
+    <x:row r="122" ht="56" customHeight="1">
       <x:c r="A122" s="34"/>
       <x:c r="B122" s="43" t="str">
         <x:v>迟缓
-スロウ</x:v>
+スロウ
+Slow</x:v>
       </x:c>
       <x:c r="C122" s="34"/>
       <x:c r="D122" s="7" t="s">
@@ -5724,18 +6153,21 @@
       <x:c r="G122" s="29"/>
       <x:c r="H122" s="30"/>
     </x:row>
-    <x:row r="123" ht="40" customHeight="1">
+    <x:row r="123" ht="56" customHeight="1">
       <x:c r="A123" s="42" t="str">
         <x:v>大停止
-ストプガ</x:v>
+ストプガ
+Stopga</x:v>
       </x:c>
       <x:c r="B123" s="42" t="str">
         <x:v>中停止
-ストプラ</x:v>
+ストプラ
+Stopra</x:v>
       </x:c>
       <x:c r="C123" s="43" t="str">
         <x:v>停止
-ストップ</x:v>
+ストップ
+Stop</x:v>
       </x:c>
       <x:c r="D123" s="7" t="s">
         <x:v>19</x:v>
@@ -5751,12 +6183,13 @@
       </x:c>
       <x:c r="H123" s="30"/>
     </x:row>
-    <x:row r="124" ht="40" customHeight="1">
+    <x:row r="124" ht="56" customHeight="1">
       <x:c r="A124" s="34"/>
       <x:c r="B124" s="34"/>
       <x:c r="C124" s="43" t="str">
         <x:v>中停止
-ストプラ</x:v>
+ストプラ
+Stopra</x:v>
       </x:c>
       <x:c r="D124" s="7" t="s">
         <x:v>20</x:v>
@@ -6062,18 +6495,21 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="40" customHeight="1">
+    <x:row r="2" ht="56" customHeight="1">
       <x:c r="A2" s="42" t="str">
         <x:v>连击滑行
-コンボスライド</x:v>
+コンボスライド
+Homing Slide</x:v>
       </x:c>
       <x:c r="B2" s="42" t="str">
         <x:v>滑行冲刺
-スライドダッシュ</x:v>
+スライドダッシュ
+Sliding Dash</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
         <x:v>中磁力
-マグネラ</x:v>
+マグネラ
+Magnera</x:v>
       </x:c>
       <x:c r="D2" s="7" t="s">
         <x:v>11</x:v>
@@ -6089,12 +6525,13 @@
       </x:c>
       <x:c r="H2" s="30"/>
     </x:row>
-    <x:row r="3" ht="40" customHeight="1">
+    <x:row r="3" ht="56" customHeight="1">
       <x:c r="A3" s="33"/>
       <x:c r="B3" s="34"/>
       <x:c r="C3" s="42" t="str">
         <x:v>空中滑行
-エアスライド</x:v>
+エアスライド
+Air Slide</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
         <x:v>15</x:v>
@@ -6104,11 +6541,12 @@
       <x:c r="G3" s="29"/>
       <x:c r="H3" s="30"/>
     </x:row>
-    <x:row r="4" ht="40" customHeight="1">
+    <x:row r="4" ht="56" customHeight="1">
       <x:c r="A4" s="34"/>
       <x:c r="B4" s="43" t="str">
         <x:v>磁力
-マグネ</x:v>
+マグネ
+Magnet</x:v>
       </x:c>
       <x:c r="C4" s="34"/>
       <x:c r="D4" s="7" t="s">
@@ -6119,18 +6557,21 @@
       <x:c r="G4" s="29"/>
       <x:c r="H4" s="30"/>
     </x:row>
-    <x:row r="5" ht="40" customHeight="1">
+    <x:row r="5" ht="56" customHeight="1">
       <x:c r="A5" s="42" t="str">
         <x:v>冰霜滑行
-アイススライド</x:v>
+アイススライド
+Ice Slide</x:v>
       </x:c>
       <x:c r="B5" s="42" t="str">
         <x:v>空中滑行
-エアスライド</x:v>
+エアスライド
+Air Slide</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>冰雪之刃
-ブリザドブレード</x:v>
+ブリザドブレード
+Blizzard Edge</x:v>
       </x:c>
       <x:c r="D5" s="7" t="s">
         <x:v>18</x:v>
@@ -6146,12 +6587,13 @@
       </x:c>
       <x:c r="H5" s="30"/>
     </x:row>
-    <x:row r="6" ht="40" customHeight="1">
+    <x:row r="6" ht="56" customHeight="1">
       <x:c r="A6" s="34"/>
       <x:c r="B6" s="34"/>
       <x:c r="C6" s="43" t="str">
         <x:v>大冰雪
-ブリザガ</x:v>
+ブリザガ
+Blizzaga</x:v>
       </x:c>
       <x:c r="D6" s="7" t="s">
         <x:v>25</x:v>
@@ -6161,18 +6603,21 @@
       <x:c r="G6" s="29"/>
       <x:c r="H6" s="30"/>
     </x:row>
-    <x:row r="7" ht="40" customHeight="1">
+    <x:row r="7" ht="56" customHeight="1">
       <x:c r="A7" s="42" t="str">
         <x:v>火焰滑翔
-ファイアグライド</x:v>
+ファイアグライド
+Fire Glide</x:v>
       </x:c>
       <x:c r="B7" s="42" t="str">
         <x:v>滑翔
-グライド</x:v>
+グライド
+Glide</x:v>
       </x:c>
       <x:c r="C7" s="43" t="str">
         <x:v>火焰闪击
-ファイアブリッツ</x:v>
+ファイアブリッツ
+Fire Surge</x:v>
       </x:c>
       <x:c r="D7" s="7" t="s">
         <x:v>15</x:v>
@@ -6188,12 +6633,13 @@
       </x:c>
       <x:c r="H7" s="30"/>
     </x:row>
-    <x:row r="8" ht="40" customHeight="1">
+    <x:row r="8" ht="56" customHeight="1">
       <x:c r="A8" s="34"/>
       <x:c r="B8" s="34"/>
       <x:c r="C8" s="43" t="str">
         <x:v>大火焰
-ファイガ</x:v>
+ファイガ
+Firaga</x:v>
       </x:c>
       <x:c r="D8" s="7" t="s">
         <x:v>17</x:v>
@@ -6203,18 +6649,21 @@
       <x:c r="G8" s="29"/>
       <x:c r="H8" s="30"/>
     </x:row>
-    <x:row r="9" ht="40" customHeight="1">
+    <x:row r="9" ht="56" customHeight="1">
       <x:c r="A9" s="42" t="str">
         <x:v>火焰翻滚
-ファイアロール</x:v>
+ファイアロール
+Firewheel</x:v>
       </x:c>
       <x:c r="B9" s="42" t="str">
         <x:v>轮式翻滚
-ホイールロール</x:v>
+ホイールロール
+Cartwheel</x:v>
       </x:c>
       <x:c r="C9" s="43" t="str">
         <x:v>火焰闪击
-ファイアブリッツ</x:v>
+ファイアブリッツ
+Fire Surge</x:v>
       </x:c>
       <x:c r="D9" s="7" t="s">
         <x:v>15</x:v>
@@ -6230,12 +6679,13 @@
       </x:c>
       <x:c r="H9" s="30"/>
     </x:row>
-    <x:row r="10" ht="40" customHeight="1">
+    <x:row r="10" ht="56" customHeight="1">
       <x:c r="A10" s="33"/>
       <x:c r="B10" s="33"/>
       <x:c r="C10" s="43" t="str">
         <x:v>大火焰
-ファイガ</x:v>
+ファイガ
+Firaga</x:v>
       </x:c>
       <x:c r="D10" s="7" t="s">
         <x:v>17</x:v>
@@ -6245,12 +6695,13 @@
       <x:c r="G10" s="29"/>
       <x:c r="H10" s="30"/>
     </x:row>
-    <x:row r="11" ht="40" customHeight="1">
+    <x:row r="11" ht="56" customHeight="1">
       <x:c r="A11" s="34"/>
       <x:c r="B11" s="34"/>
       <x:c r="C11" s="43" t="str">
         <x:v>爆裂大火焰
-クラッカーファイガ</x:v>
+クラッカーファイガ
+Fission Firaga</x:v>
       </x:c>
       <x:c r="D11" s="7" t="s">
         <x:v>17</x:v>
@@ -6260,18 +6711,21 @@
       <x:c r="G11" s="29"/>
       <x:c r="H11" s="30"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="56" customHeight="1">
       <x:c r="A12" s="42" t="str">
         <x:v>雷电翻滚
-サンダーロール</x:v>
+サンダーロール
+Thunder Roll</x:v>
       </x:c>
       <x:c r="B12" s="42" t="str">
         <x:v>闪避翻滚
-ドッジロール</x:v>
+ドッジロール
+Dodge Roll</x:v>
       </x:c>
       <x:c r="C12" s="43" t="str">
         <x:v>雷电闪击
-サンダーブリッツ</x:v>
+サンダーブリッツ
+Thunder Surge</x:v>
       </x:c>
       <x:c r="D12" s="7" t="s">
         <x:v>11</x:v>
@@ -6287,12 +6741,13 @@
       </x:c>
       <x:c r="H12" s="30"/>
     </x:row>
-    <x:row r="13" ht="40" customHeight="1">
+    <x:row r="13" ht="56" customHeight="1">
       <x:c r="A13" s="34"/>
       <x:c r="B13" s="34"/>
       <x:c r="C13" s="43" t="str">
         <x:v>大雷电
-サンダガ</x:v>
+サンダガ
+Thundaga</x:v>
       </x:c>
       <x:c r="D13" s="7" t="s">
         <x:v>22</x:v>
@@ -6328,18 +6783,21 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="40" customHeight="1">
+    <x:row r="18" ht="56" customHeight="1">
       <x:c r="A18" s="42" t="str">
         <x:v>恢复格挡
-レストアガード</x:v>
+レストアガード
+Renewal Block</x:v>
       </x:c>
       <x:c r="B18" s="42" t="str">
         <x:v>反射格挡
-リフレクトガード</x:v>
+リフレクトガード
+Block</x:v>
       </x:c>
       <x:c r="C18" s="43" t="str">
         <x:v>大恢复
-ケアルガ</x:v>
+ケアルガ
+Curaga</x:v>
       </x:c>
       <x:c r="D18" s="7" t="s">
         <x:v>11</x:v>
@@ -6355,12 +6813,13 @@
       </x:c>
       <x:c r="H18" s="30"/>
     </x:row>
-    <x:row r="19" ht="40" customHeight="1">
+    <x:row r="19" ht="56" customHeight="1">
       <x:c r="A19" s="34"/>
       <x:c r="B19" s="33"/>
       <x:c r="C19" s="43" t="str">
         <x:v>净化
-エスナ</x:v>
+エスナ
+Esuna</x:v>
       </x:c>
       <x:c r="D19" s="7" t="s">
         <x:v>15</x:v>
@@ -6370,18 +6829,21 @@
       <x:c r="G19" s="29"/>
       <x:c r="H19" s="30"/>
     </x:row>
-    <x:row r="20" ht="40" customHeight="1">
+    <x:row r="20" ht="56" customHeight="1">
       <x:c r="A20" s="42" t="str">
         <x:v>眩晕格挡
-スタンガード</x:v>
+スタンガード
+Stun Block</x:v>
       </x:c>
       <x:c r="B20" s="44" t="str">
         <x:v>反射格挡
-リフレクトガード</x:v>
+リフレクトガード
+Block</x:v>
       </x:c>
       <x:c r="C20" s="43" t="str">
         <x:v>眩晕之刃
-スタンブレード</x:v>
+スタンブレード
+Stun Edge</x:v>
       </x:c>
       <x:c r="D20" s="7" t="s">
         <x:v>22</x:v>
@@ -6397,12 +6859,13 @@
       </x:c>
       <x:c r="H20" s="30"/>
     </x:row>
-    <x:row r="21" ht="40" customHeight="1">
+    <x:row r="21" ht="56" customHeight="1">
       <x:c r="A21" s="34"/>
       <x:c r="B21" s="33"/>
       <x:c r="C21" s="43" t="str">
         <x:v>大雷电
-サンダガ</x:v>
+サンダガ
+Thundaga</x:v>
       </x:c>
       <x:c r="D21" s="7" t="s">
         <x:v>19</x:v>
@@ -6412,18 +6875,21 @@
       <x:c r="G21" s="29"/>
       <x:c r="H21" s="30"/>
     </x:row>
-    <x:row r="22" ht="40" customHeight="1">
+    <x:row r="22" ht="56" customHeight="1">
       <x:c r="A22" s="42" t="str">
         <x:v>剧毒格挡
-ポイズンガード</x:v>
+ポイズンガード
+Poison Block</x:v>
       </x:c>
       <x:c r="B22" s="44" t="str">
         <x:v>反射格挡
-リフレクトガード</x:v>
+リフレクトガード
+Block</x:v>
       </x:c>
       <x:c r="C22" s="43" t="str">
         <x:v>剧毒之刃
-ポイズンブレード</x:v>
+ポイズンブレード
+Poison Edge</x:v>
       </x:c>
       <x:c r="D22" s="7" t="s">
         <x:v>25</x:v>
@@ -6439,12 +6905,13 @@
       </x:c>
       <x:c r="H22" s="30"/>
     </x:row>
-    <x:row r="23" ht="40" customHeight="1">
+    <x:row r="23" ht="56" customHeight="1">
       <x:c r="A23" s="34"/>
       <x:c r="B23" s="34"/>
       <x:c r="C23" s="43" t="str">
         <x:v>剧毒
-ポイズン</x:v>
+ポイズン
+Poison</x:v>
       </x:c>
       <x:c r="D23" s="7" t="s">
         <x:v>11</x:v>
@@ -6454,18 +6921,21 @@
       <x:c r="G23" s="29"/>
       <x:c r="H23" s="30"/>
     </x:row>
-    <x:row r="24" ht="40" customHeight="1">
+    <x:row r="24" ht="56" customHeight="1">
       <x:c r="A24" s="42" t="str">
         <x:v>恢复屏障
-レストアバリア</x:v>
+レストアバリア
+Renewal Barrier</x:v>
       </x:c>
       <x:c r="B24" s="42" t="str">
         <x:v>反射
-リフレク</x:v>
+リフレク
+Barrier</x:v>
       </x:c>
       <x:c r="C24" s="43" t="str">
         <x:v>大恢复
-ケアルガ</x:v>
+ケアルガ
+Curaga</x:v>
       </x:c>
       <x:c r="D24" s="7" t="s">
         <x:v>11</x:v>
@@ -6481,12 +6951,13 @@
       </x:c>
       <x:c r="H24" s="30"/>
     </x:row>
-    <x:row r="25" ht="40" customHeight="1">
+    <x:row r="25" ht="56" customHeight="1">
       <x:c r="A25" s="34"/>
       <x:c r="B25" s="33"/>
       <x:c r="C25" s="43" t="str">
         <x:v>净化
-エスナ</x:v>
+エスナ
+Esuna</x:v>
       </x:c>
       <x:c r="D25" s="7" t="s">
         <x:v>14</x:v>
@@ -6496,18 +6967,21 @@
       <x:c r="G25" s="29"/>
       <x:c r="H25" s="30"/>
     </x:row>
-    <x:row r="26" ht="40" customHeight="1">
+    <x:row r="26" ht="56" customHeight="1">
       <x:c r="A26" s="42" t="str">
         <x:v>混乱屏障
-コンフュバリア</x:v>
+コンフュバリア
+Confuse Barrier</x:v>
       </x:c>
       <x:c r="B26" s="44" t="str">
         <x:v>反射
-リフレク</x:v>
+リフレク
+Barrier</x:v>
       </x:c>
       <x:c r="C26" s="43" t="str">
         <x:v>混乱强击
-コンフュストライク</x:v>
+コンフュストライク
+Confusion Strike</x:v>
       </x:c>
       <x:c r="D26" s="7" t="s">
         <x:v>15</x:v>
@@ -6525,12 +6999,13 @@
         <x:v>27</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="40" customHeight="1">
+    <x:row r="27" ht="56" customHeight="1">
       <x:c r="A27" s="34"/>
       <x:c r="B27" s="33"/>
       <x:c r="C27" s="43" t="str">
         <x:v>混乱
-コンフュ</x:v>
+コンフュ
+Confuse</x:v>
       </x:c>
       <x:c r="D27" s="7" t="s">
         <x:v>22</x:v>
@@ -6540,18 +7015,21 @@
       <x:c r="G27" s="29"/>
       <x:c r="H27" s="30"/>
     </x:row>
-    <x:row r="28" ht="40" customHeight="1">
+    <x:row r="28" ht="56" customHeight="1">
       <x:c r="A28" s="43" t="str">
         <x:v>停止屏障
-ストップバリア</x:v>
+ストップバリア
+Stop Barrier</x:v>
       </x:c>
       <x:c r="B28" s="46" t="str">
         <x:v>反射
-リフレク</x:v>
+リフレク
+Barrier</x:v>
       </x:c>
       <x:c r="C28" s="43" t="str">
         <x:v>大停止
-ストプガ</x:v>
+ストプガ
+Stopga</x:v>
       </x:c>
       <x:c r="D28" s="7" t="s">
         <x:v>15</x:v>
@@ -6653,109 +7131,138 @@
     <x:col min="10" max="10" width="27" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="40" customHeight="1">
+    <x:row r="1" ht="56" customHeight="1">
       <x:c r="A1" s="1"/>
       <x:c r="B1" s="47" t="str">
         <x:v>闪耀结晶
-きらめく結晶</x:v>
+きらめく結晶
+Shimmering Crystal</x:v>
       </x:c>
       <x:c r="C1" s="47" t="str">
         <x:v>时光结晶
-時の結晶</x:v>
+時の結晶
+Fleeting Crystal</x:v>
       </x:c>
       <x:c r="D1" s="47" t="str">
         <x:v>力量结晶
-力の結晶</x:v>
+力の結晶
+Pulsing Crystal</x:v>
       </x:c>
       <x:c r="E1" s="47" t="str">
         <x:v>充盈结晶
-みなぎる結晶</x:v>
+みなぎる結晶
+Wellspring Crystal</x:v>
       </x:c>
       <x:c r="F1" s="47" t="str">
         <x:v>润泽结晶
-うるおいの結晶</x:v>
+うるおいの結晶
+Soothing Crystal</x:v>
       </x:c>
       <x:c r="G1" s="47" t="str">
         <x:v>饱满结晶
-満たされる結晶</x:v>
+満たされる結晶
+Hungry Crystal</x:v>
       </x:c>
       <x:c r="H1" s="47" t="str">
         <x:v>轮回结晶
-めぐりくる結晶</x:v>
+めぐりくる結晶
+Abounding Crystal</x:v>
       </x:c>
       <x:c r="I1" s="48" t="str">
         <x:v>混沌结晶
-混沌の結晶</x:v>
+混沌の結晶
+Chaos Crystal</x:v>
       </x:c>
       <x:c r="J1" s="48" t="str">
         <x:v>秘藏原石
-秘められし原石</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="40" customHeight="1">
-      <x:c r="A2" s="1"/>
-      <x:c r="B2" s="47" t="str">
-        <x:v>闪耀块矿
-きらめく塊鉱</x:v>
-      </x:c>
-      <x:c r="C2" s="47" t="str">
-        <x:v>时光块矿
-時の塊鉱</x:v>
-      </x:c>
-      <x:c r="D2" s="47" t="str">
-        <x:v>力量块矿
-力の塊鉱</x:v>
-      </x:c>
-      <x:c r="E2" s="47" t="str">
-        <x:v>充盈块矿
-みなぎる塊鉱</x:v>
-      </x:c>
-      <x:c r="F2" s="47" t="str">
-        <x:v>润泽块矿
-うるおいの塊鉱</x:v>
-      </x:c>
-      <x:c r="G2" s="47" t="str">
-        <x:v>饱满块矿
-満たされる塊鉱</x:v>
-      </x:c>
-      <x:c r="H2" s="47" t="str">
-        <x:v>轮回块矿
-めぐりくる塊鉱</x:v>
-      </x:c>
-      <x:c r="I2" s="21"/>
-      <x:c r="J2" s="21"/>
-    </x:row>
-    <x:row r="3" ht="40" customHeight="1">
+秘められし原石
+Secret Gem</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="56" customHeight="1">
+      <x:c r="A2" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B2" s="43" t="str">
+        <x:v>火焰提升
+ファイアアップ
+Fire Boost</x:v>
+      </x:c>
+      <x:c r="C2" s="43" t="str">
+        <x:v>魔法加速
+マジックヘイスト
+Magic Haste</x:v>
+      </x:c>
+      <x:c r="D2" s="43" t="str">
+        <x:v>绿叶庇护
+リーフベール
+Leaf Bracer</x:v>
+      </x:c>
+      <x:c r="E2" s="43" t="str">
+        <x:v>空中连击加成
+エアコンボプラス
+Air Combo Plus</x:v>
+      </x:c>
+      <x:c r="F2" s="43" t="str">
+        <x:v>HP提升
+ＨＰアップ
+HP Boost</x:v>
+      </x:c>
+      <x:c r="G2" s="43" t="str">
+        <x:v>HP奖球提升
+ＨＰプライズアップ
+HP Prize Plus</x:v>
+      </x:c>
+      <x:c r="H2" s="43" t="str">
+        <x:v>链接奖球提升
+リンクプライズアップ
+Link Prize Plus</x:v>
+      </x:c>
+      <x:c r="I2" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="56" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="43" t="str">
         <x:v>火焰提升
-ファイアアップ</x:v>
+ファイアアップ
+Fire Boost</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
-        <x:v>魔法加速
-マジックヘイスト</x:v>
+        <x:v>装填增强
+リロードブースト
+Reload Boost</x:v>
       </x:c>
       <x:c r="D3" s="43" t="str">
-        <x:v>绿叶庇护
-リーフベール</x:v>
+        <x:v>指令终结提升
+コマンドＦアップ
+Finish Boost</x:v>
       </x:c>
       <x:c r="E3" s="43" t="str">
-        <x:v>空中连击加成
-エアコンボプラス</x:v>
+        <x:v>连击生还
+コンボリーヴ
+Once More</x:v>
       </x:c>
       <x:c r="F3" s="43" t="str">
-        <x:v>HP提升
-ＨＰアップ</x:v>
+        <x:v>受伤汲取
+ダメージアスピル
+Damage Syphon</x:v>
       </x:c>
       <x:c r="G3" s="43" t="str">
         <x:v>HP奖球提升
-ＨＰプライズアップ</x:v>
+ＨＰプライズアップ
+HP Prize Plus</x:v>
       </x:c>
       <x:c r="H3" s="43" t="str">
-        <x:v>链接奖球提升
-リンクプライズアップ</x:v>
+        <x:v>EXP良机
+ＥＸＰチャンス
+EXP Chance</x:v>
       </x:c>
       <x:c r="I3" s="3" t="s">
         <x:v>29</x:v>
@@ -6764,37 +7271,44 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="40" customHeight="1">
+    <x:row r="4" ht="56" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="43" t="str">
-        <x:v>火焰提升
-ファイアアップ</x:v>
+        <x:v>火焰防护
+ファイアガード
+Fire Screen</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
-        <x:v>装填增强
-リロードブースト</x:v>
+        <x:v>攻击加速
+アタックヘイスト
+Attack Haste</x:v>
       </x:c>
       <x:c r="D4" s="43" t="str">
         <x:v>指令终结提升
-コマンドＦアップ</x:v>
+コマンドＦアップ
+Finish Boost</x:v>
       </x:c>
       <x:c r="E4" s="43" t="str">
-        <x:v>连击生还
-コンボリーヴ</x:v>
+        <x:v>连击加成
+コンボプラス
+Combo Plus</x:v>
       </x:c>
       <x:c r="F4" s="43" t="str">
-        <x:v>受伤汲取
-ダメージアスピル</x:v>
+        <x:v>HP提升
+ＨＰアップ
+HP Boost</x:v>
       </x:c>
       <x:c r="G4" s="43" t="str">
         <x:v>HP奖球提升
-ＨＰプライズアップ</x:v>
+ＨＰプライズアップ
+HP Prize Plus</x:v>
       </x:c>
       <x:c r="H4" s="43" t="str">
-        <x:v>EXP良机
-ＥＸＰチャンス</x:v>
+        <x:v>链接奖球提升
+リンクプライズアップ
+Link Prize Plus</x:v>
       </x:c>
       <x:c r="I4" s="3" t="s">
         <x:v>29</x:v>
@@ -6803,37 +7317,44 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="40" customHeight="1">
+    <x:row r="5" ht="56" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="43" t="str">
         <x:v>火焰防护
-ファイアガード</x:v>
+ファイアガード
+Fire Screen</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>攻击加速
-アタックヘイスト</x:v>
+アタックヘイスト
+Attack Haste</x:v>
       </x:c>
       <x:c r="D5" s="43" t="str">
-        <x:v>指令终结提升
-コマンドＦアップ</x:v>
+        <x:v>绿叶庇护
+リーフベール
+Leaf Bracer</x:v>
       </x:c>
       <x:c r="E5" s="43" t="str">
         <x:v>连击加成
-コンボプラス</x:v>
+コンボプラス
+Combo Plus</x:v>
       </x:c>
       <x:c r="F5" s="43" t="str">
         <x:v>HP提升
-ＨＰアップ</x:v>
+ＨＰアップ
+HP Boost</x:v>
       </x:c>
       <x:c r="G5" s="43" t="str">
         <x:v>HP奖球提升
-ＨＰプライズアップ</x:v>
+ＨＰプライズアップ
+HP Prize Plus</x:v>
       </x:c>
       <x:c r="H5" s="43" t="str">
         <x:v>链接奖球提升
-リンクプライズアップ</x:v>
+リンクプライズアップ
+Link Prize Plus</x:v>
       </x:c>
       <x:c r="I5" s="3" t="s">
         <x:v>29</x:v>
@@ -6842,88 +7363,102 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="40" customHeight="1">
-      <x:c r="A6" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B6" s="43" t="str">
-        <x:v>火焰防护
-ファイアガード</x:v>
-      </x:c>
-      <x:c r="C6" s="43" t="str">
-        <x:v>攻击加速
-アタックヘイスト</x:v>
-      </x:c>
-      <x:c r="D6" s="43" t="str">
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="17"/>
+      <x:c r="B6" s="18"/>
+      <x:c r="C6" s="18"/>
+      <x:c r="D6" s="18"/>
+      <x:c r="E6" s="18"/>
+      <x:c r="F6" s="18"/>
+      <x:c r="G6" s="18"/>
+      <x:c r="H6" s="18"/>
+      <x:c r="I6" s="18"/>
+      <x:c r="J6" s="19"/>
+    </x:row>
+    <x:row r="7" ht="56" customHeight="1">
+      <x:c r="A7" s="3" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B7" s="43" t="str">
+        <x:v>冰雪提升
+ブリザドアップ
+Blizzard Boost</x:v>
+      </x:c>
+      <x:c r="C7" s="43" t="str">
+        <x:v>魔法加速
+マジックヘイスト
+Magic Haste</x:v>
+      </x:c>
+      <x:c r="D7" s="43" t="str">
         <x:v>绿叶庇护
-リーフベール</x:v>
-      </x:c>
-      <x:c r="E6" s="43" t="str">
+リーフベール
+Leaf Bracer</x:v>
+      </x:c>
+      <x:c r="E7" s="43" t="str">
         <x:v>连击加成
-コンボプラス</x:v>
-      </x:c>
-      <x:c r="F6" s="43" t="str">
-        <x:v>HP提升
-ＨＰアップ</x:v>
-      </x:c>
-      <x:c r="G6" s="43" t="str">
+コンボプラス
+Combo Plus</x:v>
+      </x:c>
+      <x:c r="F7" s="43" t="str">
+        <x:v>道具提升
+アイテムアップ
+Item Boost</x:v>
+      </x:c>
+      <x:c r="G7" s="43" t="str">
         <x:v>HP奖球提升
-ＨＰプライズアップ</x:v>
-      </x:c>
-      <x:c r="H6" s="43" t="str">
-        <x:v>链接奖球提升
-リンクプライズアップ</x:v>
-      </x:c>
-      <x:c r="I6" s="3" t="s">
+ＨＰプライズアップ
+HP Prize Plus</x:v>
+      </x:c>
+      <x:c r="H7" s="43" t="str">
+        <x:v>幸运提升
+ラックアップ
+Lucky Strike</x:v>
+      </x:c>
+      <x:c r="I7" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="J6" s="3" t="s">
+      <x:c r="J7" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="17"/>
-      <x:c r="B7" s="18"/>
-      <x:c r="C7" s="18"/>
-      <x:c r="D7" s="18"/>
-      <x:c r="E7" s="18"/>
-      <x:c r="F7" s="18"/>
-      <x:c r="G7" s="18"/>
-      <x:c r="H7" s="18"/>
-      <x:c r="I7" s="18"/>
-      <x:c r="J7" s="19"/>
-    </x:row>
-    <x:row r="8" ht="40" customHeight="1">
+    <x:row r="8" ht="56" customHeight="1">
       <x:c r="A8" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="43" t="str">
         <x:v>冰雪提升
-ブリザドアップ</x:v>
+ブリザドアップ
+Blizzard Boost</x:v>
       </x:c>
       <x:c r="C8" s="43" t="str">
-        <x:v>魔法加速
-マジックヘイスト</x:v>
+        <x:v>装填增强
+リロードブースト
+Reload Boost</x:v>
       </x:c>
       <x:c r="D8" s="43" t="str">
-        <x:v>绿叶庇护
-リーフベール</x:v>
+        <x:v>绝处逢生
+ラストリーヴ
+Second Chance</x:v>
       </x:c>
       <x:c r="E8" s="43" t="str">
-        <x:v>连击加成
-コンボプラス</x:v>
+        <x:v>空中连击加成
+エアコンボプラス
+Air Combo Plus</x:v>
       </x:c>
       <x:c r="F8" s="43" t="str">
-        <x:v>道具提升
-アイテムアップ</x:v>
+        <x:v>受伤汲取
+ダメージアスピル
+Damage Syphon</x:v>
       </x:c>
       <x:c r="G8" s="43" t="str">
         <x:v>HP奖球提升
-ＨＰプライズアップ</x:v>
+ＨＰプライズアップ
+HP Prize Plus</x:v>
       </x:c>
       <x:c r="H8" s="43" t="str">
         <x:v>幸运提升
-ラックアップ</x:v>
+ラックアップ
+Lucky Strike</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
         <x:v>29</x:v>
@@ -6932,37 +7467,44 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="40" customHeight="1">
+    <x:row r="9" ht="56" customHeight="1">
       <x:c r="A9" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="43" t="str">
-        <x:v>冰雪提升
-ブリザドアップ</x:v>
+        <x:v>冰雪防护
+ブリザドガード
+Blizzard Screen</x:v>
       </x:c>
       <x:c r="C9" s="43" t="str">
-        <x:v>装填增强
-リロードブースト</x:v>
+        <x:v>攻击加速
+アタックヘイスト
+Attack Haste</x:v>
       </x:c>
       <x:c r="D9" s="43" t="str">
-        <x:v>绝处逢生
-ラストリーヴ</x:v>
+        <x:v>绿叶庇护
+リーフベール
+Leaf Bracer</x:v>
       </x:c>
       <x:c r="E9" s="43" t="str">
         <x:v>空中连击加成
-エアコンボプラス</x:v>
+エアコンボプラス
+Air Combo Plus</x:v>
       </x:c>
       <x:c r="F9" s="43" t="str">
-        <x:v>受伤汲取
-ダメージアスピル</x:v>
+        <x:v>道具提升
+アイテムアップ
+Item Boost</x:v>
       </x:c>
       <x:c r="G9" s="43" t="str">
         <x:v>HP奖球提升
-ＨＰプライズアップ</x:v>
+ＨＰプライズアップ
+HP Prize Plus</x:v>
       </x:c>
       <x:c r="H9" s="43" t="str">
         <x:v>幸运提升
-ラックアップ</x:v>
+ラックアップ
+Lucky Strike</x:v>
       </x:c>
       <x:c r="I9" s="3" t="s">
         <x:v>29</x:v>
@@ -6971,37 +7513,44 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="40" customHeight="1">
+    <x:row r="10" ht="56" customHeight="1">
       <x:c r="A10" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="43" t="str">
         <x:v>冰雪防护
-ブリザドガード</x:v>
+ブリザドガード
+Blizzard Screen</x:v>
       </x:c>
       <x:c r="C10" s="43" t="str">
-        <x:v>攻击加速
-アタックヘイスト</x:v>
+        <x:v>魔法加速
+マジックヘイスト
+Magic Haste</x:v>
       </x:c>
       <x:c r="D10" s="43" t="str">
-        <x:v>绿叶庇护
-リーフベール</x:v>
+        <x:v>连击终结提升
+コンボＦアップ
+Combo F Boost</x:v>
       </x:c>
       <x:c r="E10" s="43" t="str">
         <x:v>空中连击加成
-エアコンボプラス</x:v>
+エアコンボプラス
+Air Combo Plus</x:v>
       </x:c>
       <x:c r="F10" s="43" t="str">
         <x:v>道具提升
-アイテムアップ</x:v>
+アイテムアップ
+Item Boost</x:v>
       </x:c>
       <x:c r="G10" s="43" t="str">
         <x:v>HP奖球提升
-ＨＰプライズアップ</x:v>
+ＨＰプライズアップ
+HP Prize Plus</x:v>
       </x:c>
       <x:c r="H10" s="43" t="str">
-        <x:v>幸运提升
-ラックアップ</x:v>
+        <x:v>EXP漫步
+ＥＸＰウォーク
+EXP Walker</x:v>
       </x:c>
       <x:c r="I10" s="3" t="s">
         <x:v>29</x:v>
@@ -7010,88 +7559,102 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="40" customHeight="1">
-      <x:c r="A11" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B11" s="43" t="str">
-        <x:v>冰雪防护
-ブリザドガード</x:v>
-      </x:c>
-      <x:c r="C11" s="43" t="str">
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="17"/>
+      <x:c r="B11" s="18"/>
+      <x:c r="C11" s="18"/>
+      <x:c r="D11" s="18"/>
+      <x:c r="E11" s="18"/>
+      <x:c r="F11" s="18"/>
+      <x:c r="G11" s="18"/>
+      <x:c r="H11" s="18"/>
+      <x:c r="I11" s="18"/>
+      <x:c r="J11" s="19"/>
+    </x:row>
+    <x:row r="12" ht="56" customHeight="1">
+      <x:c r="A12" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B12" s="43" t="str">
+        <x:v>雷电提升
+サンダーアップ
+Thunder Boost</x:v>
+      </x:c>
+      <x:c r="C12" s="43" t="str">
         <x:v>魔法加速
-マジックヘイスト</x:v>
-      </x:c>
-      <x:c r="D11" s="43" t="str">
+マジックヘイスト
+Magic Haste</x:v>
+      </x:c>
+      <x:c r="D12" s="43" t="str">
         <x:v>连击终结提升
-コンボＦアップ</x:v>
-      </x:c>
-      <x:c r="E11" s="43" t="str">
+コンボＦアップ
+Combo F Boost</x:v>
+      </x:c>
+      <x:c r="E12" s="43" t="str">
         <x:v>空中连击加成
-エアコンボプラス</x:v>
-      </x:c>
-      <x:c r="F11" s="43" t="str">
-        <x:v>道具提升
-アイテムアップ</x:v>
-      </x:c>
-      <x:c r="G11" s="43" t="str">
-        <x:v>HP奖球提升
-ＨＰプライズアップ</x:v>
-      </x:c>
-      <x:c r="H11" s="43" t="str">
-        <x:v>EXP漫步
-ＥＸＰウォーク</x:v>
-      </x:c>
-      <x:c r="I11" s="3" t="s">
+エアコンボプラス
+Air Combo Plus</x:v>
+      </x:c>
+      <x:c r="F12" s="43" t="str">
+        <x:v>HP提升
+ＨＰアップ
+HP Boost</x:v>
+      </x:c>
+      <x:c r="G12" s="43" t="str">
+        <x:v>吸引
+ドロー
+Treasure Magnet</x:v>
+      </x:c>
+      <x:c r="H12" s="43" t="str">
+        <x:v>链接奖球提升
+リンクプライズアップ
+Link Prize Plus</x:v>
+      </x:c>
+      <x:c r="I12" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="J11" s="3" t="s">
+      <x:c r="J12" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="17"/>
-      <x:c r="B12" s="18"/>
-      <x:c r="C12" s="18"/>
-      <x:c r="D12" s="18"/>
-      <x:c r="E12" s="18"/>
-      <x:c r="F12" s="18"/>
-      <x:c r="G12" s="18"/>
-      <x:c r="H12" s="18"/>
-      <x:c r="I12" s="18"/>
-      <x:c r="J12" s="19"/>
-    </x:row>
-    <x:row r="13" ht="40" customHeight="1">
+    <x:row r="13" ht="56" customHeight="1">
       <x:c r="A13" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B13" s="43" t="str">
         <x:v>雷电提升
-サンダーアップ</x:v>
+サンダーアップ
+Thunder Boost</x:v>
       </x:c>
       <x:c r="C13" s="43" t="str">
-        <x:v>魔法加速
-マジックヘイスト</x:v>
+        <x:v>装填增强
+リロードブースト
+Reload Boost</x:v>
       </x:c>
       <x:c r="D13" s="43" t="str">
         <x:v>连击终结提升
-コンボＦアップ</x:v>
+コンボＦアップ
+Combo F Boost</x:v>
       </x:c>
       <x:c r="E13" s="43" t="str">
-        <x:v>空中连击加成
-エアコンボプラス</x:v>
+        <x:v>连击生还
+コンボリーヴ
+Once More</x:v>
       </x:c>
       <x:c r="F13" s="43" t="str">
-        <x:v>HP提升
-ＨＰアップ</x:v>
+        <x:v>防御者
+ディフェンダー
+Defender</x:v>
       </x:c>
       <x:c r="G13" s="43" t="str">
         <x:v>吸引
-ドロー</x:v>
+ドロー
+Treasure Magnet</x:v>
       </x:c>
       <x:c r="H13" s="43" t="str">
-        <x:v>链接奖球提升
-リンクプライズアップ</x:v>
+        <x:v>EXP良机
+ＥＸＰチャンス
+EXP Chance</x:v>
       </x:c>
       <x:c r="I13" s="3" t="s">
         <x:v>29</x:v>
@@ -7100,37 +7663,44 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="40" customHeight="1">
+    <x:row r="14" ht="56" customHeight="1">
       <x:c r="A14" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="43" t="str">
-        <x:v>雷电提升
-サンダーアップ</x:v>
+        <x:v>雷电防护
+サンダーガード
+Thunder Screen</x:v>
       </x:c>
       <x:c r="C14" s="43" t="str">
-        <x:v>装填增强
-リロードブースト</x:v>
+        <x:v>攻击加速
+アタックヘイスト
+Attack Haste</x:v>
       </x:c>
       <x:c r="D14" s="43" t="str">
-        <x:v>连击终结提升
-コンボＦアップ</x:v>
+        <x:v>指令终结提升
+コマンドＦアップ
+Finish Boost</x:v>
       </x:c>
       <x:c r="E14" s="43" t="str">
-        <x:v>连击生还
-コンボリーヴ</x:v>
+        <x:v>连击加成
+コンボプラス
+Combo Plus</x:v>
       </x:c>
       <x:c r="F14" s="43" t="str">
-        <x:v>防御者
-ディフェンダー</x:v>
+        <x:v>HP提升
+ＨＰアップ
+HP Boost</x:v>
       </x:c>
       <x:c r="G14" s="43" t="str">
         <x:v>吸引
-ドロー</x:v>
+ドロー
+Treasure Magnet</x:v>
       </x:c>
       <x:c r="H14" s="43" t="str">
-        <x:v>EXP良机
-ＥＸＰチャンス</x:v>
+        <x:v>链接奖球提升
+リンクプライズアップ
+Link Prize Plus</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
         <x:v>29</x:v>
@@ -7139,37 +7709,44 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="40" customHeight="1">
+    <x:row r="15" ht="56" customHeight="1">
       <x:c r="A15" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B15" s="43" t="str">
         <x:v>雷电防护
-サンダーガード</x:v>
+サンダーガード
+Thunder Screen</x:v>
       </x:c>
       <x:c r="C15" s="43" t="str">
         <x:v>攻击加速
-アタックヘイスト</x:v>
+アタックヘイスト
+Attack Haste</x:v>
       </x:c>
       <x:c r="D15" s="43" t="str">
         <x:v>指令终结提升
-コマンドＦアップ</x:v>
+コマンドＦアップ
+Finish Boost</x:v>
       </x:c>
       <x:c r="E15" s="43" t="str">
         <x:v>连击加成
-コンボプラス</x:v>
+コンボプラス
+Combo Plus</x:v>
       </x:c>
       <x:c r="F15" s="43" t="str">
         <x:v>HP提升
-ＨＰアップ</x:v>
+ＨＰアップ
+HP Boost</x:v>
       </x:c>
       <x:c r="G15" s="43" t="str">
         <x:v>吸引
-ドロー</x:v>
+ドロー
+Treasure Magnet</x:v>
       </x:c>
       <x:c r="H15" s="43" t="str">
-        <x:v>链接奖球提升
-リンクプライズアップ</x:v>
+        <x:v>幸运提升
+ラックアップ
+Lucky Strike</x:v>
       </x:c>
       <x:c r="I15" s="3" t="s">
         <x:v>29</x:v>
@@ -7178,88 +7755,102 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="40" customHeight="1">
-      <x:c r="A16" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B16" s="43" t="str">
-        <x:v>雷电防护
-サンダーガード</x:v>
-      </x:c>
-      <x:c r="C16" s="43" t="str">
-        <x:v>攻击加速
-アタックヘイスト</x:v>
-      </x:c>
-      <x:c r="D16" s="43" t="str">
-        <x:v>指令终结提升
-コマンドＦアップ</x:v>
-      </x:c>
-      <x:c r="E16" s="43" t="str">
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="17"/>
+      <x:c r="B16" s="18"/>
+      <x:c r="C16" s="18"/>
+      <x:c r="D16" s="18"/>
+      <x:c r="E16" s="18"/>
+      <x:c r="F16" s="18"/>
+      <x:c r="G16" s="18"/>
+      <x:c r="H16" s="18"/>
+      <x:c r="I16" s="18"/>
+      <x:c r="J16" s="19"/>
+    </x:row>
+    <x:row r="17" ht="56" customHeight="1">
+      <x:c r="A17" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B17" s="43" t="str">
+        <x:v>恢复提升
+ケアルアップ
+Cure Boost</x:v>
+      </x:c>
+      <x:c r="C17" s="43" t="str">
+        <x:v>魔法加速
+マジックヘイスト
+Magic Haste</x:v>
+      </x:c>
+      <x:c r="D17" s="43" t="str">
+        <x:v>连击终结提升
+コンボＦアップ
+Combo F Boost</x:v>
+      </x:c>
+      <x:c r="E17" s="43" t="str">
         <x:v>连击加成
-コンボプラス</x:v>
-      </x:c>
-      <x:c r="F16" s="43" t="str">
-        <x:v>HP提升
-ＨＰアップ</x:v>
-      </x:c>
-      <x:c r="G16" s="43" t="str">
+コンボプラス
+Combo Plus</x:v>
+      </x:c>
+      <x:c r="F17" s="43" t="str">
+        <x:v>道具提升
+アイテムアップ
+Item Boost</x:v>
+      </x:c>
+      <x:c r="G17" s="43" t="str">
         <x:v>吸引
-ドロー</x:v>
-      </x:c>
-      <x:c r="H16" s="43" t="str">
+ドロー
+Treasure Magnet</x:v>
+      </x:c>
+      <x:c r="H17" s="43" t="str">
         <x:v>幸运提升
-ラックアップ</x:v>
-      </x:c>
-      <x:c r="I16" s="3" t="s">
+ラックアップ
+Lucky Strike</x:v>
+      </x:c>
+      <x:c r="I17" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="J16" s="3" t="s">
+      <x:c r="J17" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="17"/>
-      <x:c r="B17" s="18"/>
-      <x:c r="C17" s="18"/>
-      <x:c r="D17" s="18"/>
-      <x:c r="E17" s="18"/>
-      <x:c r="F17" s="18"/>
-      <x:c r="G17" s="18"/>
-      <x:c r="H17" s="18"/>
-      <x:c r="I17" s="18"/>
-      <x:c r="J17" s="19"/>
-    </x:row>
-    <x:row r="18" ht="40" customHeight="1">
+    <x:row r="18" ht="56" customHeight="1">
       <x:c r="A18" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B18" s="43" t="str">
         <x:v>恢复提升
-ケアルアップ</x:v>
+ケアルアップ
+Cure Boost</x:v>
       </x:c>
       <x:c r="C18" s="43" t="str">
-        <x:v>魔法加速
-マジックヘイスト</x:v>
+        <x:v>装填增强
+リロードブースト
+Reload Boost</x:v>
       </x:c>
       <x:c r="D18" s="43" t="str">
-        <x:v>连击终结提升
-コンボＦアップ</x:v>
+        <x:v>绝处逢生
+ラストリーヴ
+Second Chance</x:v>
       </x:c>
       <x:c r="E18" s="43" t="str">
         <x:v>连击加成
-コンボプラス</x:v>
+コンボプラス
+Combo Plus</x:v>
       </x:c>
       <x:c r="F18" s="43" t="str">
-        <x:v>道具提升
-アイテムアップ</x:v>
+        <x:v>防御者
+ディフェンダー
+Defender</x:v>
       </x:c>
       <x:c r="G18" s="43" t="str">
         <x:v>吸引
-ドロー</x:v>
+ドロー
+Treasure Magnet</x:v>
       </x:c>
       <x:c r="H18" s="43" t="str">
         <x:v>幸运提升
-ラックアップ</x:v>
+ラックアップ
+Lucky Strike</x:v>
       </x:c>
       <x:c r="I18" s="3" t="s">
         <x:v>29</x:v>
@@ -7268,88 +7859,102 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="40" customHeight="1">
-      <x:c r="A19" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B19" s="43" t="str">
-        <x:v>恢复提升
-ケアルアップ</x:v>
-      </x:c>
-      <x:c r="C19" s="43" t="str">
-        <x:v>装填增强
-リロードブースト</x:v>
-      </x:c>
-      <x:c r="D19" s="43" t="str">
-        <x:v>绝处逢生
-ラストリーヴ</x:v>
-      </x:c>
-      <x:c r="E19" s="43" t="str">
-        <x:v>连击加成
-コンボプラス</x:v>
-      </x:c>
-      <x:c r="F19" s="43" t="str">
-        <x:v>防御者
-ディフェンダー</x:v>
-      </x:c>
-      <x:c r="G19" s="43" t="str">
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="17"/>
+      <x:c r="B19" s="18"/>
+      <x:c r="C19" s="18"/>
+      <x:c r="D19" s="18"/>
+      <x:c r="E19" s="18"/>
+      <x:c r="F19" s="18"/>
+      <x:c r="G19" s="18"/>
+      <x:c r="H19" s="18"/>
+      <x:c r="I19" s="18"/>
+      <x:c r="J19" s="19"/>
+    </x:row>
+    <x:row r="20" ht="56" customHeight="1">
+      <x:c r="A20" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B20" s="43" t="str">
+        <x:v>黑暗防护
+ダークガード
+Dark Screen</x:v>
+      </x:c>
+      <x:c r="C20" s="43" t="str">
+        <x:v>攻击加速
+アタックヘイスト
+Attack Haste</x:v>
+      </x:c>
+      <x:c r="D20" s="43" t="str">
+        <x:v>指令终结提升
+コマンドＦアップ
+Finish Boost</x:v>
+      </x:c>
+      <x:c r="E20" s="43" t="str">
+        <x:v>空中连击加成
+エアコンボプラス
+Air Combo Plus</x:v>
+      </x:c>
+      <x:c r="F20" s="43" t="str">
+        <x:v>道具提升
+アイテムアップ
+Item Boost</x:v>
+      </x:c>
+      <x:c r="G20" s="43" t="str">
         <x:v>吸引
-ドロー</x:v>
-      </x:c>
-      <x:c r="H19" s="43" t="str">
+ドロー
+Treasure Magnet</x:v>
+      </x:c>
+      <x:c r="H20" s="43" t="str">
         <x:v>幸运提升
-ラックアップ</x:v>
-      </x:c>
-      <x:c r="I19" s="3" t="s">
+ラックアップ
+Lucky Strike</x:v>
+      </x:c>
+      <x:c r="I20" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="J19" s="3" t="s">
+      <x:c r="J20" s="3" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="17"/>
-      <x:c r="B20" s="18"/>
-      <x:c r="C20" s="18"/>
-      <x:c r="D20" s="18"/>
-      <x:c r="E20" s="18"/>
-      <x:c r="F20" s="18"/>
-      <x:c r="G20" s="18"/>
-      <x:c r="H20" s="18"/>
-      <x:c r="I20" s="18"/>
-      <x:c r="J20" s="19"/>
-    </x:row>
-    <x:row r="21" ht="40" customHeight="1">
+    <x:row r="21" ht="56" customHeight="1">
       <x:c r="A21" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B21" s="43" t="str">
         <x:v>黑暗防护
-ダークガード</x:v>
+ダークガード
+Dark Screen</x:v>
       </x:c>
       <x:c r="C21" s="43" t="str">
-        <x:v>攻击加速
-アタックヘイスト</x:v>
+        <x:v>魔法加速
+マジックヘイスト
+Magic Haste</x:v>
       </x:c>
       <x:c r="D21" s="43" t="str">
-        <x:v>指令终结提升
-コマンドＦアップ</x:v>
+        <x:v>连击终结提升
+コンボＦアップ
+Combo F Boost</x:v>
       </x:c>
       <x:c r="E21" s="43" t="str">
         <x:v>空中连击加成
-エアコンボプラス</x:v>
+エアコンボプラス
+Air Combo Plus</x:v>
       </x:c>
       <x:c r="F21" s="43" t="str">
         <x:v>道具提升
-アイテムアップ</x:v>
+アイテムアップ
+Item Boost</x:v>
       </x:c>
       <x:c r="G21" s="43" t="str">
         <x:v>吸引
-ドロー</x:v>
+ドロー
+Treasure Magnet</x:v>
       </x:c>
       <x:c r="H21" s="43" t="str">
-        <x:v>幸运提升
-ラックアップ</x:v>
+        <x:v>EXP漫步
+ＥＸＰウォーク
+EXP Walker</x:v>
       </x:c>
       <x:c r="I21" s="3" t="s">
         <x:v>29</x:v>
@@ -7358,53 +7963,12 @@
         <x:v>29</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="40" customHeight="1">
-      <x:c r="A22" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B22" s="43" t="str">
-        <x:v>黑暗防护
-ダークガード</x:v>
-      </x:c>
-      <x:c r="C22" s="43" t="str">
-        <x:v>魔法加速
-マジックヘイスト</x:v>
-      </x:c>
-      <x:c r="D22" s="43" t="str">
-        <x:v>连击终结提升
-コンボＦアップ</x:v>
-      </x:c>
-      <x:c r="E22" s="43" t="str">
-        <x:v>空中连击加成
-エアコンボプラス</x:v>
-      </x:c>
-      <x:c r="F22" s="43" t="str">
-        <x:v>道具提升
-アイテムアップ</x:v>
-      </x:c>
-      <x:c r="G22" s="43" t="str">
-        <x:v>吸引
-ドロー</x:v>
-      </x:c>
-      <x:c r="H22" s="43" t="str">
-        <x:v>EXP漫步
-ＥＸＰウォーク</x:v>
-      </x:c>
-      <x:c r="I22" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J22" s="3" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A7:J7"/>
-    <x:mergeCell ref="A12:J12"/>
-    <x:mergeCell ref="A17:J17"/>
-    <x:mergeCell ref="A20:J20"/>
-    <x:mergeCell ref="I1:I2"/>
-    <x:mergeCell ref="J1:J2"/>
+    <x:mergeCell ref="A6:J6"/>
+    <x:mergeCell ref="A11:J11"/>
+    <x:mergeCell ref="A16:J16"/>
+    <x:mergeCell ref="A19:J19"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
